--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,58 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>narrativeplace/castello</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_gandolfo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lettura del censimento: la «stazione di Castello» (QP 279) come Castel Gandolfo, lettura immediata del toponimo. Identificazione contesa (DC-04): Manzotti 2010, p. 293 legge Castel Savello; la sua lettura entra in fase 3. Non adottata finché DC-04 non è deciso.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sostituisce owl:sameAs gaz_castello &lt;-&gt; gaz_castel_gandolfo (D-044)</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,66 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Sostituisce owl:sameAs gaz_castello &lt;-&gt; gaz_castel_gandolfo (D-044)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>narrativeplace/castello</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_savello</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>293</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>La «stazione di Castello» (QP 279) è la stazione dei carabinieri di Castel Savello: Manzotti scioglie così la dizione, contro la lettura immediata Castel Gandolfo (Cap. 4, § 4.4). Lettura adottata dal progetto (LS, 9/10/2026, DC-04).</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Lettura alternativa non adottata: A-0001 (Castel Gandolfo, LS)</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,16 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale_Type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Review_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,6 +544,16 @@
           <t>Sostituisce owl:sameAs gaz_castello &lt;-&gt; gaz_castel_gandolfo (D-044)</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,6 +612,3198 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>Lettura alternativa non adottata: A-0001 (Castel Gandolfo, LS)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S-area_oltre_tevere</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>narrativeplace/area_oltre_tevere</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Area paesaggistica vaga e analogica, delimitata dal Tevere e costruita per accumulo descrittivo (castelli, vigne, colli, monti, piane)».</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S-barbiere</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>narrativeplace/barbiere</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Luogo generico: barbiere».</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S-bottega_ceccherelli</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>narrativeplace/bottega_ceccherelli</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S-buco_a_santignazio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>narrativeplace/buco_a_santignazio</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S-ca_francesi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>narrativeplace/ca_francesi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S-camera_casello</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>narrativeplace/camera_casello</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «camera da letto della Camilla Mattonari».</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S-cantinone_albano</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>narrativeplace/cantinone_albano</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Ristorante non identificato nel territorio di Albano Laziale».</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S-casa_crocchiapani</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>narrativeplace/casa_crocchiapani</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Parte di tor_di_gheppio nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Abitazione immaginaria di Assunta (Tina) Crocchiapani».</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S-casa_del_butiro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>narrativeplace/casa_del_butiro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>chora:Imagined</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Casa immaginata nella zona dei Due Santi».</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S-casal_bruciato</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>narrativeplace/casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>chora:Imported</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Casale reale dell'Agro romano, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569); posizione adottata TCI, alternativa IGM (D-037). Cap. 4, § 4.4 (r. 107): il disaccordo «non contrappone due differenti interpreti, bensì due distinti repertori cartografici». L'incertezza della posizione è SpatialDetermination, non statuto.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S-casello_km_20_25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>narrativeplace/casello_km_20_25</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «casello ferroviario in prossimità di Casal Bruciato».</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S-cassero</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>narrativeplace/cassero</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S-castel_porcano</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>chora:Imagined</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>273, 276</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): la denominazione è una «deformazione paraetimologica d'un toponimo reale» (Castelporziano, «il che penderebbe verso il luogo trasformato»), mentre la festa notturna «appartiene a uno spazio onirico e destrutturato, privo di collocazione metrica e dunque ascrivibile alla categoria dell'immaginato». Perimetro d'identità da dichiarare (H3, DC-09, DC-11).</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S-castello</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>narrativeplace/castello</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>293</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Luogo testuale della «stazione di Castello» (QP 279), bersaglio di due identificazioni concorrenti (Cap. 4, § 4.3, r. 93; § 4.4, r. 107): Castel Gandolfo (LS, A-0001) e Castel Savello (Manzotti 2010, p. 293, A-0002, adottata). Statuto da rivedere alla luce della lettura adottata (REVIEW_2).</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S-casuccia_zamira</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>narrativeplace/casuccia_zamira</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S-cobianchi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>narrativeplace/cobianchi</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-colli_saluberrimi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>narrativeplace/colli_saluberrimi</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S-ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S-edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>narrativeplace/edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>chora:Imported</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>246</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S-gioielliere_catellani</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>narrativeplace/gioielliere_catellani</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «negozio non identificabile».</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S-grotta_de_sor_pippo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>narrativeplace/grotta_de_sor_pippo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S-laboratorio_zamira</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>narrativeplace/laboratorio_zamira</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S-montagne_degli_equi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>narrativeplace/montagne_degli_equi</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S-monte_circeo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>narrativeplace/monte_circeo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S-monte_nuncupale</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>narrativeplace/monte_nuncupale</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>chora:Imagined</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): «il Monte Nuncupale, posto a chiusura d'un orizzonte che spazia «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su» (QP 173)», fra i luoghi inventati. NB: nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S-orto_vigna_due_santi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>narrativeplace/orto_vigna_due_santi</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S-palazzo_219</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_219</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QP 16, 25) in fase 2 (T-41).</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S-palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S-palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pinotti 2025</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>78</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QP 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S-passaggio_livello_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S-pensione_burgess</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>narrativeplace/pensione_burgess</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S-piani_alti_219</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>narrativeplace/piani_alti_219</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S-piccarozzi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>narrativeplace/piccarozzi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S-ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>narrativeplace/ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S-ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>narrativeplace/ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S-porta_borgo_marino</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>narrativeplace/porta_borgo_marino</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S-pozzofondo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>narrativeplace/pozzofondo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S-robine_vecchie</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>narrativeplace/robine_vecchie</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Terzoli 2015</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>491</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QP 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S-roccafringoli</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>narrativeplace/roccafringoli</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>chora:Imagined</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati con «una precisa collocazione topografica», «Roccafringoli, situata «su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio» (QP 107)». NB: il capitolo lo dice inventato; nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S-scale</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>narrativeplace/scale</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S-scala_a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>narrativeplace/scala_a</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S-scala_b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>narrativeplace/scala_b</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S-scerpure</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>narrativeplace/scerpure</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>chora:Imagined</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): «Scerpure, la favolosa città del maharajah posizionata «sulle rive, più o meno, del nativo Brahmaputra» (QP 141)», fra i luoghi inventati; «Scerpure esibisce un nome inventato a fronte d'una collocazione geografica nota». NB: nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S-stazione_carabinieri_castello</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>narrativeplace/stazione_carabinieri_castello</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S-stazione_pavona</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>narrativeplace/stazione_pavona</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S-strada_di_campagna_celio</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>narrativeplace/strada_di_campagna_celio</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S-tenenza_carabinieri_marino</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>239, 293</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S-terzo_piano_219</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>narrativeplace/terzo_piano_219</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S-tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>narrativeplace/tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortellessa 2023</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>679</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S-via_delle_oche</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>narrativeplace/via_delle_oche</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Descrizione del censimento: «via topograficamente non precisata».</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S-villino_lungotevere</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>narrativeplace/villino_lungotevere</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>bozza</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,16 @@
           <t>Review_Status</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Uncertainty_Axis</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Uncertainty_Origin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3804,6 +3814,608 @@
       <c r="O54" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>U-0001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>narrativeplace/casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>chora:Confusion</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>U-0002</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>narrativeplace/castello</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>chora:ContestedIdentification</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>293</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Due identificazioni concorrenti della «stazione di Castello» (QP 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>costruttiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>U-0003</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>chora:ContestedIdentification</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Pinotti 2025</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>78</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QP 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>U-0004</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>narrativeplace/robine_vecchie</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>chora:Discrepancy</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Terzoli 2015</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>491</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>«Robine Vecchie» (QP 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>U-0005</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>narrativeplace/edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>chora:Incompleteness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>246</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>costruttiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>U-0006</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>narrativeplace/monti_ernici</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>chora:NonSpecificity</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>290</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QP 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>U-0007</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>narrativeplace/carsoli</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>chora:Oversight</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>254</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>«Càrsoli» (QP 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>U-0008</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>narrativeplace/direttissima_roma_napoli</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>chora:Anachronism</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>annotator/lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>270</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>documentaria</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4419,6 +4419,434 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>M-0001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00168</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>chora:AuthorMemory</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>perosa</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Perosa 2023a</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>103–104</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QP 61, Dosso Faiti).</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>M-0002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00168</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>chora:CharacterMemory</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>lugnani</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lugnani, cit. in Perosa 2023a</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>104, n. 97</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QP 61, Dosso Faiti).</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>M-0003</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00168</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>cortellessa</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortellessa 2023</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>669</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QP 61, Dosso Faiti).</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>M-0004</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00169</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>chora:AuthorMemory</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>perosa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Perosa 2023a</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>103–104</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QP 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>M-0005</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00169</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>chora:CharacterMemory</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>lugnani</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lugnani, cit. in Perosa 2023a</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>104, n. 97</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QP 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>M-0006</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>interpretation/interp_00169</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>cortellessa</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortellessa 2023</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>669</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QP 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4847,6 +4847,78 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P-0001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>partition</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>partition/citta_campagna</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>zone/roma_citta|zone/campagna_romana</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Capitolo 4</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>§ 4.1, § 4.6 (R20)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1793,11 @@
           <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>C-edicola_due_santi</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2416,6 +2421,11 @@
           <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QP 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>C-palazzo_simonetti</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4916,6 +4926,264 @@
       <c r="O69" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C-edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>narrativeplace/edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>chora:Invented</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Censimento GaddAtlas</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C-palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>chora:Imported</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Censimento GaddAtlas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QP 177.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>narrativeplace/casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Censimento GaddAtlas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>I-casal_bruciato</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>narrativeplace/casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Manzotti 2010</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>validata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5187,6 +5187,270 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>V-0001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>narrativeplace/frattocchie</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>reference/ref_00588|reference/ref_00724</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>QP (Adelphi 2018)</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>241</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Fattocchie (RR II 219, stampa Garzanti) / Frattocchie (QP 241): emendamento dell'editore. Le occorrenze si annotano sulla lezione del testo di riferimento.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>V-0002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>narrativeplace/via_lanza</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>reference/ref_00436|reference/ref_00725</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pinotti 2025</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>78</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>via Lata (dtsFG) / via Lanza (QP 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>V-0003</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_219</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>reference/ref_00007|reference/ref_00036|reference/ref_00726|reference/ref_00727</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>matt|pinotti</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Matt e Pinotti 2022</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Civico 119 (QPL 285, 293: «quer gran palazzo del centodicinnove») / 219 (QP 16, 25: «ducentodicinnove»): il palazzo si ricolloca solo nell'edizione in volume.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>V-0004</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_219</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>reference/ref_00008|reference/ref_00038|reference/ref_00726|reference/ref_00727</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>matt|pinotti</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Matt e Pinotti 2022</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>«palazzo degli ori» (QPL 285, 293) / «palazzo dell'Oro» (QP 16, 25).</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5451,6 +5451,1455 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>R-0001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>297</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»), non un punto attraversato: da rivedere.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R-0002</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>chora:InferredRoute</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>169</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Separato dal tragitto di QP 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>R-0003</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>route/tragitto_tenenza_due_santi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>208–215</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>R-0004</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>292</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R-0005</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>route/tragitto_viminale_merulana</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>25</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R-0006</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>route/tragitto_appia_falcognana</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>chora:IndicatedRoute</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>238</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QP 237).</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>R-0007</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>route/tragitto_agostino_aquiro</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>40</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>R-0008</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>route/tragitto_cecchina_anziate</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>173</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>R-0009</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>route/tragitto_colonna_treccani</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>40</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R-0010</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>route/tragitto_frattocchie_ciampino</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>chora:InferredRoute</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>174</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Come QP 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R-0011</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>route/tragitto_monti_piazza_esedra</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>182</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>R-0012</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>173</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>R-0013</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>route/tragitto_chiara_pantheon</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>41</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>R-0014</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>route/tragitto_duesanti_frattocchie</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>56</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>R-0015</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>R-0016</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>route/tragitto_marino_albano_laziale</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>chora:DirectionalRoute</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>278</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>R-0017</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>route/tragitto_marino_due_santi</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>206</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>R-0018</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>route/tragitto_marino_santo_stefano</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>153</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>La partenza dalla Tenenza è inferita dal rapporto. L'ordine dei nodi è invertito (1 Santo Stefano, 2 Tenenza): da correggere.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>R-0019</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>route/tragitto_merulana_policlinico</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>chora:CompletedRoute</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>93</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Il focalizzatore registrato è Liliana, ma chi si sposta è il giudice istruttore; se il percorso è quello del corpo, è un oggetto (DM-03, escluso).</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>R-0020</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>chora:DreamedRoute</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>212</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» (2010, p. 269) è una nota attribuita di fase 3.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>R-0021</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>chora:IndicatedRoute</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>QP</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>237</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Luogo testuale della «stazione di Castello» (QP 279), bersaglio di due identificazioni concorrenti (Cap. 4, § 4.3, r. 93; § 4.4, r. 107): Castel Gandolfo (LS, A-0001) e Castel Savello (Manzotti 2010, p. 293, A-0002, adottata). Statuto da rivedere alla luce della lettura adottata (REVIEW_2).</t>
+          <t>La «stazione di Castello» (QP 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -5507,7 +5507,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»), non un punto attraversato: da rivedere.</t>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>La partenza dalla Tenenza è inferita dal rapporto. L'ordine dei nodi è invertito (1 Santo Stefano, 2 Tenenza): da correggere.</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Il focalizzatore registrato è Liliana, ma chi si sposta è il giudice istruttore; se il percorso è quello del corpo, è un oggetto (DM-03, escluso).</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -534,6 +534,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,7 +603,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -666,6 +671,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>si</t>
@@ -728,6 +738,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>si</t>
@@ -961,6 +976,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>si</t>
@@ -1023,6 +1043,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>si</t>
@@ -1085,6 +1110,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>si</t>
@@ -1147,6 +1177,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>si</t>
@@ -1211,7 +1246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1281,6 +1316,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>si</t>
@@ -1402,7 +1442,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1474,7 +1514,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1599,6 +1639,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>si</t>
@@ -1777,7 +1822,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1850,6 +1895,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>si</t>
@@ -1912,6 +1962,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>si</t>
@@ -1974,6 +2029,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>si</t>
@@ -2036,6 +2096,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>si</t>
@@ -2098,6 +2163,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>si</t>
@@ -2160,6 +2230,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>si</t>
@@ -2222,6 +2297,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>si</t>
@@ -2284,6 +2364,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>si</t>
@@ -2405,7 +2490,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pinotti 2025</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2478,6 +2563,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>si</t>
@@ -2540,6 +2630,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>si</t>
@@ -2602,6 +2697,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>si</t>
@@ -2664,6 +2764,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>si</t>
@@ -2783,6 +2888,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>si</t>
@@ -2845,6 +2955,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>si</t>
@@ -2907,6 +3022,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>si</t>
@@ -2971,7 +3091,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Terzoli 2015</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3039,6 +3159,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>si</t>
@@ -3101,6 +3226,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>si</t>
@@ -3163,6 +3293,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>si</t>
@@ -3225,6 +3360,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>si</t>
@@ -3287,6 +3427,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>si</t>
@@ -3349,6 +3494,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>si</t>
@@ -3411,6 +3561,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>si</t>
@@ -3473,6 +3628,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>si</t>
@@ -3537,7 +3697,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3607,6 +3767,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>si</t>
@@ -3671,7 +3836,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortellessa 2023</t>
+          <t>cortellessa_2023</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -3739,6 +3904,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>si</t>
@@ -3860,7 +4030,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3937,7 +4107,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -4012,7 +4182,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pinotti 2025</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -4087,7 +4257,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Terzoli 2015</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -4162,7 +4332,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -4237,7 +4407,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -4312,7 +4482,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -4387,7 +4557,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -4462,7 +4632,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Perosa 2023a</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4534,12 +4704,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lugnani, cit. in Perosa 2023a</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>104, n. 97</t>
+          <t>104, n. 97 (Lugnani 2001, cit.)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4606,7 +4776,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortellessa 2023</t>
+          <t>cortellessa_2023</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -4676,7 +4846,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perosa 2023a</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4748,12 +4918,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lugnani, cit. in Perosa 2023a</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>104, n. 97</t>
+          <t>104, n. 97 (Lugnani 2001, cit.)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4820,7 +4990,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortellessa 2023</t>
+          <t>cortellessa_2023</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -4890,7 +5060,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Capitolo 4</t>
+          <t>sabatino_cap4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4962,7 +5132,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Censimento GaddAtlas</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5024,7 +5194,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Censimento GaddAtlas</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5086,7 +5256,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Censimento GaddAtlas</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5148,7 +5318,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Manzotti 2010</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5220,7 +5390,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>QP (Adelphi 2018)</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -5285,7 +5455,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pinotti 2025</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -5350,7 +5520,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Matt e Pinotti 2022</t>
+          <t>matt_pinotti_2022</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5417,7 +5587,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Matt e Pinotti 2022</t>
+          <t>matt_pinotti_2022</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5484,7 +5654,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -5554,7 +5724,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -5624,7 +5794,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5691,7 +5861,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -5761,7 +5931,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -5826,7 +5996,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -5896,7 +6066,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -5966,7 +6136,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -6036,7 +6206,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -6106,7 +6276,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -6176,7 +6346,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -6246,7 +6416,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -6316,7 +6486,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -6386,7 +6556,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -6451,7 +6621,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6518,7 +6688,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -6588,7 +6758,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -6653,7 +6823,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -6723,7 +6893,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -6793,7 +6963,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -6863,7 +7033,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>QP</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="H98" t="n">

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7070,6 +7070,150 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>geometry/L-0001</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Posizione adottata (D-037).</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>geometry/L-0002</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Posizione alternativa (D-037).</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>Uncertainty_Origin</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Grounded_In</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +574,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -639,6 +649,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1550,6 +1565,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4010,7 +4030,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4148,6 +4168,11 @@
           <t>costruttiva</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4223,6 +4248,11 @@
           <t>documentaria</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4237,7 +4267,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>narrativeplace/robine_vecchie</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4312,7 +4342,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>gazetteer/gaz_edicola_due_santi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4448,6 +4478,11 @@
           <t>documentaria</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>ref_00541</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4462,7 +4497,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>narrativeplace/carsoli</t>
+          <t>reference/ref_00523</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4598,6 +4633,11 @@
           <t>documentaria</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>ref_00535|ref_00635|ref_00703</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4612,7 +4652,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>interpretation/interp_00168</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4684,7 +4724,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>interpretation/interp_00168</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4756,7 +4796,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>interpretation/interp_00168</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4826,7 +4866,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>interpretation/interp_00169</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4898,7 +4938,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>interpretation/interp_00169</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4970,7 +5010,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>interpretation/interp_00169</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5370,12 +5410,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>narrativeplace/frattocchie</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>reference/ref_00588|reference/ref_00724</t>
+          <t>reference/ref_00724</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5435,12 +5475,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>narrativeplace/via_lanza</t>
+          <t>reference/ref_00436</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>reference/ref_00436|reference/ref_00725</t>
+          <t>reference/ref_00725</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5490,7 +5530,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V-0003</t>
+          <t>V-0003a</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5500,12 +5540,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_219</t>
+          <t>reference/ref_00007</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>reference/ref_00007|reference/ref_00036|reference/ref_00726|reference/ref_00727</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5530,7 +5570,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285, 293: «quer gran palazzo del centodicinnove») / 219 (QP 16, 25: «ducentodicinnove»): il palazzo si ricolloca solo nell'edizione in volume.</t>
+          <t>Civico 119 (QPL 285) / 219 (QP 16).</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5540,7 +5580,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 285 ↔ QP 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5557,7 +5597,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V-0004</t>
+          <t>V-0003b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5567,12 +5607,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_219</t>
+          <t>reference/ref_00036</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>reference/ref_00008|reference/ref_00038|reference/ref_00726|reference/ref_00727</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5597,7 +5637,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285, 293) / «palazzo dell'Oro» (QP 16, 25).</t>
+          <t>Civico 119 (QPL 293) / 219 (QP 25).</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5607,7 +5647,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 293 ↔ QP 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5624,50 +5664,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R-0001</t>
+          <t>V-0004a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>reference/ref_00008</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>matt|pinotti</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>qp</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>297</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QP 16).</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5677,7 +5714,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
+          <t>Corrispondenza QPL 285 ↔ QP 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5687,57 +5724,54 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R-0002</t>
+          <t>V-0004b</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+          <t>reference/ref_00038</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>matt|pinotti</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>qp</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>169</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QP 25).</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5747,7 +5781,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QP 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Corrispondenza QPL 293 ↔ QP 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5757,14 +5791,14 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R-0003</t>
+          <t>R-0001</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5774,7 +5808,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>route/tragitto_tenenza_due_santi</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5797,10 +5831,8 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>208–215</t>
-        </is>
+      <c r="H80" t="n">
+        <v>297</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5809,12 +5841,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5831,7 +5868,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R-0004</t>
+          <t>R-0002</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5841,12 +5878,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5865,7 +5902,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>292</v>
+        <v>169</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5874,7 +5911,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5884,7 +5921,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+          <t>Separato dal tragitto di QP 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5901,7 +5938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R-0005</t>
+          <t>R-0003</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5911,7 +5948,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>route/tragitto_viminale_merulana</t>
+          <t>route/tragitto_tenenza_due_santi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5934,8 +5971,10 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="H82" t="n">
-        <v>25</v>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>208–215</t>
+        </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5944,7 +5983,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5966,7 +6005,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R-0006</t>
+          <t>R-0004</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5976,12 +6015,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>route/tragitto_appia_falcognana</t>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6000,7 +6039,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6009,7 +6048,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QP 237).</t>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6019,7 +6058,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6036,7 +6075,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R-0007</t>
+          <t>R-0005</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6046,7 +6085,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>route/tragitto_agostino_aquiro</t>
+          <t>route/tragitto_viminale_merulana</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6070,7 +6109,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6079,17 +6118,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6106,7 +6140,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R-0008</t>
+          <t>R-0006</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6116,12 +6150,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>route/tragitto_cecchina_anziate</t>
+          <t>route/tragitto_appia_falcognana</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6140,7 +6174,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6149,7 +6183,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QP 237).</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6159,7 +6193,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6176,7 +6210,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R-0009</t>
+          <t>R-0007</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6186,7 +6220,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>route/tragitto_colonna_treccani</t>
+          <t>route/tragitto_agostino_aquiro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6219,7 +6253,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6246,7 +6280,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R-0010</t>
+          <t>R-0008</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6256,12 +6290,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>route/tragitto_frattocchie_ciampino</t>
+          <t>route/tragitto_cecchina_anziate</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6280,7 +6314,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6289,7 +6323,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6299,7 +6333,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Come QP 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6316,7 +6350,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R-0011</t>
+          <t>R-0009</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6326,7 +6360,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>route/tragitto_monti_piazza_esedra</t>
+          <t>route/tragitto_colonna_treccani</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6350,7 +6384,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6359,7 +6393,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6369,7 +6403,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6386,7 +6420,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R-0012</t>
+          <t>R-0010</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6396,12 +6430,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+          <t>route/tragitto_frattocchie_ciampino</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6420,7 +6454,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6429,7 +6463,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6439,7 +6473,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Come QP 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6456,7 +6490,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R-0013</t>
+          <t>R-0011</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6466,7 +6500,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>route/tragitto_chiara_pantheon</t>
+          <t>route/tragitto_monti_piazza_esedra</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6490,7 +6524,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6499,7 +6533,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6509,7 +6543,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6526,7 +6560,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R-0014</t>
+          <t>R-0012</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6536,7 +6570,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>route/tragitto_duesanti_frattocchie</t>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6560,7 +6594,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6569,12 +6603,17 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6591,7 +6630,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R-0015</t>
+          <t>R-0013</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6601,7 +6640,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+          <t>route/tragitto_chiara_pantheon</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6624,10 +6663,8 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>139–140</t>
-        </is>
+      <c r="H92" t="n">
+        <v>41</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6636,12 +6673,17 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6658,7 +6700,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R-0016</t>
+          <t>R-0014</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6668,12 +6710,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_albano_laziale</t>
+          <t>route/tragitto_duesanti_frattocchie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>chora:DirectionalRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6692,7 +6734,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6701,17 +6743,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6728,7 +6765,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R-0017</t>
+          <t>R-0015</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6738,7 +6775,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_due_santi</t>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6761,8 +6798,10 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>206</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6771,7 +6810,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6793,7 +6832,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R-0018</t>
+          <t>R-0016</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6803,12 +6842,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_santo_stefano</t>
+          <t>route/tragitto_marino_albano_laziale</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:DirectionalRoute</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6827,7 +6866,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>153</v>
+        <v>278</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6836,7 +6875,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6846,7 +6885,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6863,7 +6902,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R-0019</t>
+          <t>R-0017</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6873,7 +6912,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>route/tragitto_merulana_policlinico</t>
+          <t>route/tragitto_marino_due_santi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6897,7 +6936,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6906,17 +6945,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -6933,7 +6967,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R-0020</t>
+          <t>R-0018</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6943,12 +6977,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>route/tragitto_marino_santo_stefano</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>chora:DreamedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6967,7 +7001,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6976,7 +7010,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6986,7 +7020,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» (2010, p. 269) è una nota attribuita di fase 3.</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7003,7 +7037,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R-0021</t>
+          <t>R-0019</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7013,12 +7047,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+          <t>route/tragitto_merulana_policlinico</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7037,7 +7071,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7046,7 +7080,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7056,7 +7090,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7073,27 +7107,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>R-0020</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>geometry/L-0001</t>
+          <t>chora:DreamedRoute</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7103,13 +7137,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qp</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>212</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7118,7 +7150,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7128,87 +7160,229 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Posizione adottata (D-037).</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» (2010, p. 269) è una nota attribuita di fase 3.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>R-0021</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>chora:IndicatedRoute</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>qp</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>237</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>bozza</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>geometry/L-0001</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Posizione adottata (D-037).</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>L-0002</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>geometry/L-0002</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>manzotti</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t>Posizione alternativa (D-037).</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>prova referenziale</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>validata</t>
         </is>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:S102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,11 @@
           <t>Grounded_In</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Original_Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1286,7 +1291,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Statuto deciso e motivato da LS: D-029, D-037. Validata (D-071).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1296,7 +1301,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4754,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>104, n. 97 (Lugnani 2001, cit.)</t>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4769,7 +4774,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4780,6 +4785,11 @@
       <c r="O64" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4973,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>104, n. 97 (Lugnani 2001, cit.)</t>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4983,7 +4993,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4994,6 +5004,11 @@
       <c r="O67" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7403,6 +7403,78 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>U-0009</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_bologna</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>chora:Discrepancy</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Luogo: via_delle_oche (QP 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>ref_00028</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lettura del censimento: la «stazione di Castello» (QP 279) come Castel Gandolfo, lettura immediata del toponimo. Identificazione contesa (DC-04): Manzotti 2010, p. 293 legge Castel Savello; la sua lettura entra in fase 3. Non adottata finché DC-04 non è deciso.</t>
+          <t>Lettura del censimento: la «stazione di Castello» (QPa 279) come Castel Gandolfo, lettura immediata del toponimo. Identificazione contesa (DC-04): Manzotti 2010, p. 293 legge Castel Savello; la sua lettura entra in fase 3. Non adottata finché DC-04 non è deciso.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>La «stazione di Castello» (QP 279) è la stazione dei carabinieri di Castel Savello: Manzotti scioglie così la dizione, contro la lettura immediata Castel Gandolfo (Cap. 4, § 4.4). Lettura adottata dal progetto (LS, 9/10/2026, DC-04).</t>
+          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: Manzotti scioglie così la dizione, contro la lettura immediata Castel Gandolfo (Cap. 4, § 4.4). Lettura adottata dal progetto (LS, 9/10/2026, DC-04).</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>La «stazione di Castello» (QP 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
+          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QP 16, 25) in fase 2 (T-41).</t>
+          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QP 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
+          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QP 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
+          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Due identificazioni concorrenti della «stazione di Castello» (QP 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
+          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QP 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>«Robine Vecchie» (QP 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
+          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QP 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
+          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>«Càrsoli» (QP 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
+          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QP 61, Dosso Faiti).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QP 61, Dosso Faiti).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QP 61, Dosso Faiti).</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QP 61, Monte Cengio).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QP 61, Monte Cengio).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QP 61, Monte Cengio).</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QP 177.</t>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fattocchie (RR II 219, stampa Garzanti) / Frattocchie (QP 241): emendamento dell'editore. Le occorrenze si annotano sulla lezione del testo di riferimento.</t>
+          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>via Lata (dtsFG) / via Lanza (QP 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
+          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285) / 219 (QP 16).</t>
+          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 285 ↔ QP 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 293) / 219 (QP 25).</t>
+          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QP 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QP 16).</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 285 ↔ QP 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QP 25).</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QP 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QP 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QP 237).</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Come QP 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Luogo: via_delle_oche (QP 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
+          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Bottega senza riscontro nei repertori: nome e collocazione d'autore.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -842,12 +842,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -874,7 +879,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Denominazione popolare di un luogo reale presso Sant'Ignazio a Roma: il Buco a Sant'Ignazio (ancora gaz_buco_a_santignazio, 41,898 N 12,480 E).</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -899,12 +904,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -939,6 +949,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>512</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>si</t>
@@ -946,7 +964,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Località reale nei pressi della stazione delle Frattocchie.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -956,12 +974,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1041,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1028,7 +1051,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1108,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1095,7 +1118,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1175,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1162,7 +1185,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1242,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1229,7 +1252,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1381,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1368,7 +1391,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1418,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1403,6 +1426,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>169</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>si</t>
@@ -1410,7 +1441,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Toponimo senza riscontro, collocato dal testo "a Sant'Ignazio", fra le provenienze di QPa 169.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1420,12 +1451,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1513,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): la denominazione è una «deformazione paraetimologica d'un toponimo reale» (Castelporziano, «il che penderebbe verso il luogo trasformato»), mentre la festa notturna «appartiene a uno spazio onirico e destrutturato, privo di collocazione metrica e dunque ascrivibile alla categoria dell'immaginato». Perimetro d'identità da dichiarare (H3, DC-09, DC-11).</t>
+          <t>Luogo senza corrispondenza con un luogo attestato: il nome deforma Castelporziano, ma la festa notturna appartiene a uno spazio d'immaginazione d'autore.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1487,7 +1523,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1497,7 +1533,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1635,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1614,7 +1650,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1624,12 +1660,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1727,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1696,7 +1737,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1764,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1738,7 +1779,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1748,12 +1789,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1788,6 +1834,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>si</t>
@@ -1795,7 +1846,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1805,12 +1856,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080). Pagina di Terzoli 2015 da compilare.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1998,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1952,7 +2008,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2065,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2019,7 +2075,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2132,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2086,7 +2142,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2199,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2153,7 +2209,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2266,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2220,7 +2276,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2303,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2257,8 +2313,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>173</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2267,7 +2326,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «il Monte Nuncupale, posto a chiusura d'un orizzonte che spazia «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su» (QP 173)», fra i luoghi inventati. NB: nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2277,7 +2336,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2287,7 +2346,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2403,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2354,7 +2413,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2470,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2421,7 +2480,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2507,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2463,7 +2522,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,12 +2532,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2607,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2553,7 +2617,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2674,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2620,7 +2684,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2741,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2687,7 +2751,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2808,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2754,7 +2818,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2875,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2821,7 +2885,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2856,6 +2920,16 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>si</t>
@@ -2863,7 +2937,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2873,12 +2947,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3014,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2945,7 +3024,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3081,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3012,7 +3091,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3148,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3079,7 +3158,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3218,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3149,7 +3228,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3255,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3186,8 +3265,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>107</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3196,7 +3278,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati con «una precisa collocazione topografica», «Roccafringoli, situata «su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio» (QP 107)». NB: il capitolo lo dice inventato; nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3206,7 +3288,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3216,7 +3298,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3355,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3283,7 +3365,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3422,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3350,7 +3432,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3489,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3417,7 +3499,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3526,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3454,8 +3536,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>141</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3464,7 +3549,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «Scerpure, la favolosa città del maharajah posizionata «sulle rive, più o meno, del nativo Brahmaputra» (QP 141)», fra i luoghi inventati; «Scerpure esibisce un nome inventato a fronte d'una collocazione geografica nota». NB: nei dati è Imagined dopo la permutazione (D-030, D-035).</t>
+          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3474,7 +3559,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3484,7 +3569,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3626,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3551,7 +3636,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3693,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3618,7 +3703,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3760,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3685,7 +3770,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3832,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3757,7 +3842,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3899,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3824,7 +3909,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3969,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3894,7 +3979,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3921,7 +4006,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3931,8 +4016,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>22</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3941,7 +4029,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «via topograficamente non precisata».</t>
+          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3951,7 +4039,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3961,7 +4049,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4076,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4003,7 +4091,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nessuna motivazione nei documenti del progetto (descrizione vuota, nessun passo del Cap. 4): da compilare.</t>
+          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4013,12 +4101,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Bozza T-33 (D-046): da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S103"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,26 @@
           <t>Original_Source</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Plays_On</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Variant_Kind</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Disagrees_With</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5569,6 +5589,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5634,6 +5659,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5701,6 +5731,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5768,6 +5803,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5835,6 +5875,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5900,6 +5945,11 @@
       <c r="O79" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W103"/>
+  <dimension ref="A1:W159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,6 +1859,11 @@
           <t>terzoli_2015</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>si</t>
@@ -1876,7 +1881,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080). Pagina di Terzoli 2015 da compilare.</t>
+          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2535,6 +2540,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>537</v>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>si</t>
@@ -3817,14 +3830,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>manzotti_2010</t>
@@ -3832,7 +3845,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>239, 293</t>
+          <t>293–294</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3852,7 +3865,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7318,7 +7331,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» (2010, p. 269) è una nota attribuita di fase 3.</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7615,6 +7628,3968 @@
       <c r="R103" t="inlineStr">
         <is>
           <t>ref_00028</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>N-0001</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>refuso per «Robinie vecchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>N-0002</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>N-0003</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>chora:IronicLowering</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>«ironico abbassamento»</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>italia</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>102–103</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>K-0002</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>169</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Risponde a K-0001 (D-087).</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>U-0010</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>reference/ref_00404</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>chora:Incompleteness</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>492</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>ref_00404</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>K-0003</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>reference/ref_00588</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>italia</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>101</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>ref_00588</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>V-0005</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>reference/ref_00132</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>reference/ref_00734</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>142</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>I-0001</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>narrativeplace/ca_francesi</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ca_francesi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>512</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>I-0002</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>narrativeplace/tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>512</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>I-0003</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>narrativeplace/fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>658</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>ref_00529</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T-0021</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>658 (Bertarelli 1924, p. 561)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>I-0004</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>narrativeplace/osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>776</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T-0022</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ciampino</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_frattocchie</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_torraccio</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T-0005</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_due_santi</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T-0006</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_pavona</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T-0010</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_solforata</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_pratica_di_mare</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T-0012</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ca_francesi</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T-0013</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_falcognana</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T-0014</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_cecchina</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T-0015</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_albano_laziale</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T-0016</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_zagarolo</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T-0017</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_marino</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T-0018</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ariccia</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T-0019</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_santa_palomba</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>T-0020</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_rocca_di_papa</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>K-0004</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>work/quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>418–419</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>T-0023</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato»</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>T-0024</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>K-0005</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>ref_00698</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>K-0006</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>narrativeplace/casello_km_20_25</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>911</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>K-0007</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>narrativeplace/tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>911</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>«immaginaria»</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>K-0008</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>ref_00534</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T-0025</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_monti_ernici</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>I-0005</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>239–240</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>K-0009</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>narrativeplace/marino</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>293–294</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>N-0004</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>chora:Paraetymology</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>273</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>K-0010</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>reference/ref_00539</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>276</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>ref_00539</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>I-0006</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>535–536</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>I-0007</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>grassadonia|lagossi|marchetti</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>536</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>I-0008</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>78</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>ref_00435|ref_00725</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>N-0005</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>reference/ref_00437</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>chora:Synecdoche</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>537</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>I-0009</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>537</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>I-0010</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_chigi</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>grassadonia|lagossi|marchetti</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>537</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>I-0011</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>narrativeplace/vite</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_via_della_vite</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>616</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>V-0006</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>reference/ref_00493</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>reference/ref_00735</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>78</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>N-0006</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>chora:OnomasticPun</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>S-osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>narrativeplace/osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>776</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Motivazione di LS (10/10/2026, D-087).</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>validata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S103"/>
+  <dimension ref="A1:W159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,26 @@
           <t>Original_Source</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Plays_On</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Variant_Kind</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Disagrees_With</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1839,6 +1859,11 @@
           <t>terzoli_2015</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>si</t>
@@ -1856,7 +1881,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080). Pagina di Terzoli 2015 da compilare.</t>
+          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2515,6 +2540,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>537</v>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>si</t>
@@ -3797,14 +3830,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>manzotti_2010</t>
@@ -3812,7 +3845,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>239, 293</t>
+          <t>293–294</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3832,7 +3865,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5569,6 +5602,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5634,6 +5672,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5701,6 +5744,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5768,6 +5816,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5835,6 +5888,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5902,6 +5960,11 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7268,7 +7331,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» (2010, p. 269) è una nota attribuita di fase 3.</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7565,6 +7628,3968 @@
       <c r="R103" t="inlineStr">
         <is>
           <t>ref_00028</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>N-0001</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>refuso per «Robinie vecchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>N-0002</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>N-0003</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>chora:IronicLowering</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>«ironico abbassamento»</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>italia</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>102–103</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>K-0002</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>169</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Risponde a K-0001 (D-087).</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>U-0010</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>uncertainty</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>reference/ref_00404</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>chora:Incompleteness</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>492</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>ref_00404</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>K-0003</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>reference/ref_00588</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>italia</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>101</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>ref_00588</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>V-0005</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>reference/ref_00132</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>reference/ref_00734</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>142</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>I-0001</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>narrativeplace/ca_francesi</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ca_francesi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>512</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>I-0002</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>narrativeplace/tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>512</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>I-0003</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>narrativeplace/fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>658</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>ref_00529</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T-0021</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>658 (Bertarelli 1924, p. 561)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>I-0004</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>narrativeplace/osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>776</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T-0022</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ciampino</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_frattocchie</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_torraccio</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T-0005</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_due_santi</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T-0006</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_pavona</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T-0010</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_solforata</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_pratica_di_mare</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T-0012</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ca_francesi</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T-0013</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_falcognana</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T-0014</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_cecchina</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T-0015</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_albano_laziale</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T-0016</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_zagarolo</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T-0017</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_marino</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T-0018</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ariccia</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T-0019</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_santa_palomba</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>T-0020</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_rocca_di_papa</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>K-0004</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>work/quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>418–419</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>T-0023</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato»</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>T-0024</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>K-0005</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>ref_00698</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>K-0006</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>narrativeplace/casello_km_20_25</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>911</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>K-0007</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>narrativeplace/tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>911</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>«immaginaria»</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>K-0008</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>ref_00534</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T-0025</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>repertory</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_monti_ernici</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>I-0005</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>239–240</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>K-0009</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>narrativeplace/marino</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>293–294</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>N-0004</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>chora:Paraetymology</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>273</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>K-0010</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>commentary</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>reference/ref_00539</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>276</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>ref_00539</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>I-0006</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>535–536</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>I-0007</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>grassadonia|lagossi|marchetti</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>536</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>I-0008</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>78</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>ref_00435|ref_00725</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>N-0005</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>reference/ref_00437</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>chora:Synecdoche</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>537</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>I-0009</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>537</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>I-0010</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_chigi</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>grassadonia|lagossi|marchetti</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>537</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>I-0011</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>narrativeplace/vite</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_via_della_vite</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>616</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>V-0006</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>reference/ref_00493</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>reference/ref_00735</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>78</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>N-0006</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>chora:OnomasticPun</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>S-osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>narrativeplace/osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>chora:Transformed</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>776</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Motivazione di LS (10/10/2026, D-087).</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>validata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W159"/>
+  <dimension ref="A1:W164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Validata da LS (10/10/2026, D-078). Superata dalla lettura S-casa_del_butiro-2 (D-090).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S-casal_bruciato</t>
+          <t>S-casa_del_butiro-2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1289,33 +1289,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>narrativeplace/casa_del_butiro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>268–269</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>193</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1324,22 +1322,27 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Casale reale dell'Agro romano, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569); posizione adottata TCI, alternativa IGM (D-037). Cap. 4, § 4.4 (r. 107): il disaccordo «non contrappone due differenti interpreti, bensì due distinti repertori cartografici». L'incertezza della posizione è SpatialDetermination, non statuto.</t>
+          <t>Casa senza riscontro reale, che il testo situa lungo “la stradiccia della fonte de salute” (QPa 193), nella zona dei Due Santi a cui è ancorata. Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>S-casa_del_butiro</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Statuto deciso e motivato da LS: D-029, D-037. Validata (D-071).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1351,7 +1354,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S-casello_km_20_25</t>
+          <t>S-casal_bruciato</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1361,12 +1364,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1381,7 +1384,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>268–269</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1391,7 +1399,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «casello ferroviario in prossimità di Casal Bruciato».</t>
+          <t>Casale reale dell'Agro romano, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569); posizione adottata TCI, alternativa IGM (D-037). Cap. 4, § 4.4 (r. 107): il disaccordo «non contrappone due differenti interpreti, bensì due distinti repertori cartografici». L'incertezza della posizione è SpatialDetermination, non statuto.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1401,12 +1409,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Statuto deciso e motivato da LS: D-029, D-037. Validata (D-071).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1418,7 +1426,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S-cassero</t>
+          <t>S-casello_km_20_25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1428,17 +1436,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>narrativeplace/cassero</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1448,11 +1456,8 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>169</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Toponimo senza riscontro, collocato dal testo "a Sant'Ignazio", fra le provenienze di QPa 169.</t>
+          <t>Descrizione del censimento: «casello ferroviario in prossimità di Casal Bruciato».</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1471,7 +1476,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1488,7 +1493,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S-castel_porcano</t>
+          <t>S-cassero</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1498,33 +1503,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
+          <t>narrativeplace/cassero</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>273, 276</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>169</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1533,7 +1536,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Luogo senza corrispondenza con un luogo attestato: il nome deforma Castelporziano, ma la festa notturna appartiene a uno spazio d'immaginazione d'autore.</t>
+          <t>Toponimo senza riscontro, collocato dal testo "a Sant'Ignazio", fra le provenienze di QPa 169.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1543,12 +1546,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1560,7 +1563,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S-castello</t>
+          <t>S-castel_porcano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1570,12 +1573,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1593,17 +1596,19 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>293</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>273, 276</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
+          <t>Luogo senza corrispondenza con un luogo attestato: il nome deforma Castelporziano, ma la festa notturna appartiene a uno spazio d'immaginazione d'autore.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1613,29 +1618,24 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-castel_porcano-2 (D-090).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S-casuccia_zamira</t>
+          <t>S-castel_porcano-2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>narrativeplace/casuccia_zamira</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1660,8 +1660,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>213</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1670,17 +1678,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
+          <t>Luogo del sogno di Pestalozzi, senza riscontro reale; il nome gioca su Castelporziano (Manzotti 2010, p. 273; N-0004), e attraverso il nome il luogo resta legato a una geografia nota (QPa 213). Luogo inventato secondo Reuschel e Hurni (2011).</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>S-castel_porcano</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1697,7 +1710,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S-cobianchi</t>
+          <t>S-castello</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1707,12 +1720,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>narrativeplace/cobianchi</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1727,8 +1740,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>293</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1737,7 +1753,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
+          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1747,24 +1763,29 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S-colli_saluberrimi</t>
+          <t>S-casuccia_zamira</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1774,12 +1795,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>narrativeplace/colli_saluberrimi</t>
+          <t>narrativeplace/casuccia_zamira</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1799,7 +1820,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
+          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1814,7 +1835,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1826,7 +1847,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S-ditta_ciurlani</t>
+          <t>S-cobianchi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1836,7 +1857,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/cobianchi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1856,12 +1877,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1871,7 +1887,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
+          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1881,12 +1897,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1898,7 +1914,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S-edicola_due_santi</t>
+          <t>S-colli_saluberrimi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1908,32 +1924,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>narrativeplace/colli_saluberrimi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>246</v>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>si</t>
@@ -1941,12 +1949,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>C-edicola_due_santi</t>
+          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1956,12 +1959,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1973,7 +1976,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S-gioielliere_catellani</t>
+          <t>S-ditta_ciurlani</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1983,7 +1986,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>narrativeplace/gioielliere_catellani</t>
+          <t>narrativeplace/ditta_ciurlani</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2003,7 +2006,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2013,7 +2021,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «negozio non identificabile».</t>
+          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2023,12 +2031,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2040,7 +2048,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S-grotta_de_sor_pippo</t>
+          <t>S-edicola_due_santi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2050,12 +2058,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>narrativeplace/grotta_de_sor_pippo</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2070,8 +2078,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>246</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2080,7 +2091,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
+          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2090,12 +2106,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2107,7 +2123,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S-laboratorio_zamira</t>
+          <t>S-gioielliere_catellani</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2117,12 +2133,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>narrativeplace/laboratorio_zamira</t>
+          <t>narrativeplace/gioielliere_catellani</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2137,7 +2153,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2147,7 +2163,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
+          <t>Descrizione del censimento: «negozio non identificabile».</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2174,7 +2190,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S-montagne_degli_equi</t>
+          <t>S-grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2184,12 +2200,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>narrativeplace/montagne_degli_equi</t>
+          <t>narrativeplace/grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2214,7 +2230,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
+          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2241,7 +2257,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S-monte_circeo</t>
+          <t>S-laboratorio_zamira</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2251,12 +2267,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_circeo</t>
+          <t>narrativeplace/laboratorio_zamira</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2271,7 +2287,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>sabatino_cap4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2281,7 +2297,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
+          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2308,7 +2324,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S-monte_nuncupale</t>
+          <t>S-montagne_degli_equi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2318,17 +2334,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_nuncupale</t>
+          <t>narrativeplace/montagne_degli_equi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2338,11 +2354,8 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>173</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2351,7 +2364,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
+          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2361,7 +2374,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2378,7 +2391,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S-orto_vigna_due_santi</t>
+          <t>S-monte_circeo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2388,12 +2401,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>narrativeplace/orto_vigna_due_santi</t>
+          <t>narrativeplace/monte_circeo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2418,7 +2431,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
+          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2445,7 +2458,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S-palazzo_219</t>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2455,37 +2468,40 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_219</t>
+          <t>narrativeplace/monte_nuncupale</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>173</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
+          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2495,7 +2511,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-monte_nuncupale-2 (D-090).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2512,7 +2528,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S-palazzo_del_mappamondo</t>
+          <t>S-monte_nuncupale-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2522,12 +2538,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/monte_nuncupale</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2537,16 +2553,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>537</v>
+        <v>173</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2555,22 +2571,27 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
+          <t>Rilievo senza riscontro reale, posto dal testo nell’orizzonte dei Colli Albani: “da Rocca Orsina al Monte Nuncupale, su” (QPa 173). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2582,7 +2603,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S-palazzo_simonetti</t>
+          <t>S-orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2592,12 +2613,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2612,11 +2633,8 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>78</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2625,12 +2643,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>C-palazzo_simonetti</t>
+          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2645,7 +2658,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2657,7 +2670,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S-passaggio_livello_casal_bruciato</t>
+          <t>S-palazzo_219</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2667,7 +2680,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
+          <t>narrativeplace/palazzo_219</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2697,7 +2710,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2724,7 +2737,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S-pensione_burgess</t>
+          <t>S-palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2734,28 +2747,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>narrativeplace/pensione_burgess</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>537</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2764,7 +2780,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
+          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2774,12 +2790,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2791,7 +2807,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S-piani_alti_219</t>
+          <t>S-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2801,7 +2817,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>narrativeplace/piani_alti_219</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2821,8 +2837,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>78</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2831,7 +2850,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2846,7 +2870,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2858,7 +2882,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S-piccarozzi</t>
+          <t>S-passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2868,7 +2892,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>narrativeplace/piccarozzi</t>
+          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2898,7 +2922,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
+          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2925,7 +2949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S-ponte_di_santa_fumia</t>
+          <t>S-pensione_burgess</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2935,12 +2959,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_di_santa_fumia</t>
+          <t>narrativeplace/pensione_burgess</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2955,12 +2979,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2970,7 +2989,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
+          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2980,12 +2999,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2997,7 +3016,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S-ponte_divino_amore</t>
+          <t>S-piani_alti_219</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3007,7 +3026,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_divino_amore</t>
+          <t>narrativeplace/piani_alti_219</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3037,7 +3056,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3064,7 +3083,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S-porta_borgo_marino</t>
+          <t>S-piccarozzi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3074,7 +3093,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>narrativeplace/porta_borgo_marino</t>
+          <t>narrativeplace/piccarozzi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3104,7 +3123,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
+          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3131,7 +3150,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S-pozzofondo</t>
+          <t>S-ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3141,12 +3160,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>narrativeplace/pozzofondo</t>
+          <t>narrativeplace/ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3161,7 +3180,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3171,7 +3195,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
+          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3181,12 +3205,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3198,7 +3222,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S-robine_vecchie</t>
+          <t>S-ponte_divino_amore</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3208,7 +3232,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>narrativeplace/robine_vecchie</t>
+          <t>narrativeplace/ponte_divino_amore</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3228,11 +3252,8 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>491</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3241,7 +3262,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
+          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3256,7 +3277,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3268,7 +3289,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S-roccafringoli</t>
+          <t>S-porta_borgo_marino</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3278,17 +3299,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>narrativeplace/roccafringoli</t>
+          <t>narrativeplace/porta_borgo_marino</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3298,11 +3319,8 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>107</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3311,7 +3329,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
+          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3321,7 +3339,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3338,7 +3356,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S-scale</t>
+          <t>S-pozzofondo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3348,12 +3366,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>narrativeplace/scale</t>
+          <t>narrativeplace/pozzofondo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3378,7 +3396,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3405,7 +3423,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S-scala_a</t>
+          <t>S-robine_vecchie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3415,7 +3433,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_a</t>
+          <t>narrativeplace/robine_vecchie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3435,8 +3453,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>491</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3445,7 +3466,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
+          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3460,7 +3481,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3472,7 +3493,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S-scala_b</t>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3482,37 +3503,40 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_b</t>
+          <t>narrativeplace/roccafringoli</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>107</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
+          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3522,7 +3546,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-roccafringoli-2 (D-090).</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3539,7 +3563,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S-scerpure</t>
+          <t>S-roccafringoli-2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3549,12 +3573,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>narrativeplace/scerpure</t>
+          <t>narrativeplace/roccafringoli</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3564,7 +3588,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3573,7 +3597,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3582,17 +3606,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
+          <t>Paese senza riscontro reale, collocato dal testo entro una geografia nota: “su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio” (QPa 107). Luogo inventato secondo Reuschel e Hurni (2011): “an invented setting within familiar geographical reality”.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3609,7 +3638,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S-stazione_carabinieri_castello</t>
+          <t>S-scale</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3619,7 +3648,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_carabinieri_castello</t>
+          <t>narrativeplace/scale</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3649,7 +3678,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3676,7 +3705,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S-stazione_pavona</t>
+          <t>S-scala_a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3686,7 +3715,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_pavona</t>
+          <t>narrativeplace/scala_a</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3716,7 +3745,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3743,7 +3772,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S-strada_di_campagna_celio</t>
+          <t>S-scala_b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3753,7 +3782,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>narrativeplace/strada_di_campagna_celio</t>
+          <t>narrativeplace/scala_b</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3783,7 +3812,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3810,7 +3839,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S-tenenza_carabinieri_marino</t>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3820,17 +3849,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3840,22 +3869,20 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>293–294</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>141</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
+          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3865,12 +3892,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-scerpure-2 (D-090).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3882,7 +3909,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S-terzo_piano_219</t>
+          <t>S-scerpure-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3892,28 +3919,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>narrativeplace/terzo_piano_219</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>141</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3922,17 +3952,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
+          <t>Città senza riscontro reale, collocata dal testo “sulle rive, più o meno, del nativo Brahmaputra” (QPa 141). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3949,7 +3984,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S-tor_di_gheppio</t>
+          <t>S-stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3959,12 +3994,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>narrativeplace/stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3979,11 +4014,8 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>679</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3992,7 +4024,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
+          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4019,7 +4051,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S-via_delle_oche</t>
+          <t>S-stazione_pavona</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4029,17 +4061,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>narrativeplace/via_delle_oche</t>
+          <t>narrativeplace/stazione_pavona</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4049,11 +4081,8 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>22</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4062,7 +4091,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
+          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4072,7 +4101,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4089,7 +4118,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S-villino_lungotevere</t>
+          <t>S-strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4099,17 +4128,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>narrativeplace/villino_lungotevere</t>
+          <t>narrativeplace/strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4117,6 +4146,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>si</t>
@@ -4124,7 +4158,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
+          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4134,7 +4168,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4151,27 +4185,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>U-0001</t>
+          <t>S-tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>chora:Confusion</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4186,12 +4220,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>268–269</t>
+          <t>293–294</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
+          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4201,7 +4240,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4211,39 +4250,29 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>documentaria</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>U-0002</t>
+          <t>S-terzo_piano_219</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/terzo_piano_219</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4258,15 +4287,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>293</v>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4276,54 +4307,39 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>identificazione</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>costruttiva</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>U-0003</t>
+          <t>S-tor_di_gheppio</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4338,15 +4354,20 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>cortellessa_2023</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>78</v>
+        <v>679</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4356,77 +4377,67 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>identificazione</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>U-0004</t>
+          <t>S-via_delle_oche</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>narrativeplace/via_delle_oche</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>491</v>
+        <v>22</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
+          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4436,72 +4447,59 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>documentaria</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>U-0005</t>
+          <t>S-villino_lungotevere</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_edicola_due_santi</t>
+          <t>narrativeplace/villino_lungotevere</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>246</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
+          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4511,34 +4509,24 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>costruttiva</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>U-0006</t>
+          <t>U-0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4548,12 +4536,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>narrativeplace/monti_ernici</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>chora:NonSpecificity</t>
+          <t>chora:Confusion</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4571,12 +4559,14 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>290</v>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
+          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4601,24 +4591,19 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>identificazione</t>
+          <t>geometria</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>ref_00541</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>U-0007</t>
+          <t>U-0002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4628,17 +4613,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>reference/ref_00523</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>chora:Oversight</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4652,11 +4637,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
+          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4681,19 +4666,24 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>identificazione</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>documentaria</t>
+          <t>costruttiva</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>U-0008</t>
+          <t>U-0003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4703,17 +4693,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>narrativeplace/direttissima_roma_napoli</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>chora:Anachronism</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4723,15 +4713,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
+          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4766,59 +4756,52 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ref_00535|ref_00635|ref_00703</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>U-0004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>103–104</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>491</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
+          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4828,7 +4811,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4839,58 +4822,61 @@
       <c r="O63" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>documentaria</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>U-0005</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>gazetteer/gaz_edicola_due_santi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>246</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
+          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4900,12 +4886,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4913,59 +4899,59 @@
           <t>bozza</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>costruttiva</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>U-0006</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/monti_ernici</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:NonSpecificity</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>669</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>290</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
+          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4975,7 +4961,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4986,58 +4972,66 @@
       <c r="O65" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>ref_00541</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>U-0007</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00523</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>chora:Oversight</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>103–104</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>254</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
+          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5047,7 +5041,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5058,58 +5052,61 @@
       <c r="O66" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>documentaria</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>U-0008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>narrativeplace/direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:Anachronism</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>270</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5119,7 +5116,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5132,16 +5129,26 @@
           <t>bozza</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ref_00535|ref_00635|ref_00703</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5151,17 +5158,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:AuthorMemory</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>perosa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5171,11 +5178,13 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>669</v>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>103–104</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5184,7 +5193,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5211,27 +5220,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P-0001</t>
+          <t>M-0002</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>partition</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>partition/citta_campagna</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>zone/roma_citta|zone/campagna_romana</t>
+          <t>chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>lugnani</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5241,22 +5250,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>§ 4.1, § 4.6 (R20)</t>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5266,7 +5275,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5277,33 +5286,38 @@
       <c r="O69" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C-edicola_due_santi</t>
+          <t>M-0003</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>cortellessa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5313,8 +5327,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>669</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5323,12 +5340,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5338,34 +5360,34 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C-palazzo_simonetti</t>
+          <t>M-0004</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:AuthorMemory</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>perosa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5375,7 +5397,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>103–104</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5385,49 +5412,54 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C-casal_bruciato</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casal_bruciato</t>
+          <t>chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>lugnani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5437,7 +5469,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5447,49 +5484,59 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>I-casal_bruciato</t>
+          <t>M-0006</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>cortellessa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5499,27 +5546,20 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>669</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>C-casal_bruciato</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5527,41 +5567,46 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V-0001</t>
+          <t>P-0001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>partition</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>partition/citta_campagna</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>reference/ref_00724</t>
+          <t>zone/roma_citta|zone/campagna_romana</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5571,15 +5616,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>241</v>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>§ 4.1, § 4.6 (R20)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
+          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5589,49 +5641,44 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
+          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V-0002</t>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>reference/ref_00436</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>reference/ref_00725</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5641,67 +5688,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>78</v>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
+          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V-0003a</t>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>reference/ref_00007</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5711,69 +5750,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V-0003b</t>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>reference/ref_00036</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>gazetteer/gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5783,69 +5812,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>V-0004a</t>
+          <t>I-casal_bruciato</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>reference/ref_00008</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5855,17 +5874,27 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
+          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5873,31 +5902,21 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V-0004b</t>
+          <t>V-0001</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5907,17 +5926,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>reference/ref_00038</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>reference/ref_00724</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5927,17 +5946,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>241</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
+          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5947,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5969,27 +5986,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R-0001</t>
+          <t>V-0002</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>reference/ref_00436</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00725</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5999,20 +6016,15 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>297</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>78</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6022,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
+          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6032,34 +6044,39 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R-0002</t>
+          <t>V-0003a</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+          <t>reference/ref_00007</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6069,20 +6086,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>169</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6092,7 +6106,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6102,34 +6116,39 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R-0003</t>
+          <t>V-0003b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>route/tragitto_tenenza_due_santi</t>
+          <t>reference/ref_00036</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6139,22 +6158,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>matt_pinotti_2022</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>208–215</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6162,6 +6176,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t>prova testuale</t>
@@ -6169,34 +6188,39 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R-0004</t>
+          <t>V-0004a</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+          <t>reference/ref_00008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6206,20 +6230,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>292</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6229,7 +6250,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6239,34 +6260,39 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R-0005</t>
+          <t>V-0004b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>route/tragitto_viminale_merulana</t>
+          <t>reference/ref_00038</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6276,20 +6302,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>25</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6297,6 +6320,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>prova testuale</t>
@@ -6304,14 +6332,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R-0006</t>
+          <t>R-0001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6321,12 +6354,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>route/tragitto_appia_falcognana</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6345,7 +6378,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6354,7 +6387,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6364,7 +6397,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6381,7 +6414,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R-0007</t>
+          <t>R-0002</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6391,12 +6424,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>route/tragitto_agostino_aquiro</t>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6415,7 +6448,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6424,7 +6457,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6434,7 +6467,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6451,7 +6484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R-0008</t>
+          <t>R-0003</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6461,7 +6494,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>route/tragitto_cecchina_anziate</t>
+          <t>route/tragitto_tenenza_due_santi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6484,8 +6517,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H87" t="n">
-        <v>173</v>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>208–215</t>
+        </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6494,17 +6529,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6521,7 +6551,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R-0009</t>
+          <t>R-0004</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6531,7 +6561,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>route/tragitto_colonna_treccani</t>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6555,7 +6585,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6564,7 +6594,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6574,7 +6604,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6591,7 +6621,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R-0010</t>
+          <t>R-0005</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6601,12 +6631,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>route/tragitto_frattocchie_ciampino</t>
+          <t>route/tragitto_viminale_merulana</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6625,7 +6655,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6634,17 +6664,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6661,7 +6686,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R-0011</t>
+          <t>R-0006</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6671,12 +6696,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>route/tragitto_monti_piazza_esedra</t>
+          <t>route/tragitto_appia_falcognana</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6695,7 +6720,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6704,7 +6729,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6714,7 +6739,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6731,7 +6756,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R-0012</t>
+          <t>R-0007</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6741,7 +6766,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+          <t>route/tragitto_agostino_aquiro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6765,7 +6790,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6774,7 +6799,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6801,7 +6826,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R-0013</t>
+          <t>R-0008</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6811,7 +6836,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>route/tragitto_chiara_pantheon</t>
+          <t>route/tragitto_cecchina_anziate</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6835,7 +6860,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6844,7 +6869,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6854,7 +6879,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6871,7 +6896,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R-0014</t>
+          <t>R-0009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6881,7 +6906,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>route/tragitto_duesanti_frattocchie</t>
+          <t>route/tragitto_colonna_treccani</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6905,7 +6930,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6914,12 +6939,17 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6936,7 +6966,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R-0015</t>
+          <t>R-0010</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6946,12 +6976,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+          <t>route/tragitto_frattocchie_ciampino</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6969,10 +6999,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>139–140</t>
-        </is>
+      <c r="H94" t="n">
+        <v>174</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6981,12 +7009,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7003,7 +7036,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R-0016</t>
+          <t>R-0011</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7013,12 +7046,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_albano_laziale</t>
+          <t>route/tragitto_monti_piazza_esedra</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>chora:DirectionalRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7037,7 +7070,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>278</v>
+        <v>182</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7046,7 +7079,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7056,7 +7089,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7073,7 +7106,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R-0017</t>
+          <t>R-0012</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7083,7 +7116,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_due_santi</t>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7107,7 +7140,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7116,12 +7149,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7138,7 +7176,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R-0018</t>
+          <t>R-0013</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7148,7 +7186,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_santo_stefano</t>
+          <t>route/tragitto_chiara_pantheon</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7172,7 +7210,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7181,7 +7219,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7191,7 +7229,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7208,7 +7246,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R-0019</t>
+          <t>R-0014</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7218,7 +7256,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>route/tragitto_merulana_policlinico</t>
+          <t>route/tragitto_duesanti_frattocchie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7242,7 +7280,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7251,17 +7289,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7278,7 +7311,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R-0020</t>
+          <t>R-0015</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7288,12 +7321,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>chora:DreamedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7311,8 +7344,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>212</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7321,17 +7356,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7348,7 +7378,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R-0021</t>
+          <t>R-0016</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7358,12 +7388,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+          <t>route/tragitto_marino_albano_laziale</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:DirectionalRoute</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7382,7 +7412,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7391,7 +7421,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7401,7 +7431,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7418,27 +7448,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>R-0017</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_marino_due_santi</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>geometry/L-0001</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7448,13 +7478,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>206</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7463,7 +7491,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7471,46 +7499,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>Posizione adottata (D-037).</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>R-0018</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_marino_santo_stefano</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>geometry/L-0002</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7520,22 +7543,20 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>153</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7545,39 +7566,39 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Posizione alternativa (D-037).</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>U-0009</t>
+          <t>R-0019</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_bologna</t>
+          <t>route/tragitto_merulana_policlinico</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7590,71 +7611,69 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>93</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>ref_00028</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N-0001</t>
+          <t>R-0020</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>chora:DreamedRoute</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7664,79 +7683,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>212</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>refuso per «Robinie vecchie»</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N-0002</t>
+          <t>R-0021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7746,79 +7753,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>237</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>refuso per «Rovine vecchie»</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N-0003</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chora:IronicLowering</t>
+          <t>geometry/L-0001</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7828,74 +7823,69 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>491–492</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Posizione adottata (D-037).</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>«ironico abbassamento»</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>K-0001</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>geometry/L-0002</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7905,59 +7895,64 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>italia_2020</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>102–103</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Posizione alternativa (D-037).</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>K-0002</t>
+          <t>U-0009</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_bologna</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7970,17 +7965,9 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>169</v>
-      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7990,12 +7977,12 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Risponde a K-0001 (D-087).</t>
+          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8003,36 +7990,41 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>K-0001</t>
+          <t>ref_00028</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>U-0010</t>
+          <t>N-0001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>reference/ref_00404</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>chora:TypoHypothesis</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8050,12 +8042,19 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H109" t="n">
-        <v>492</v>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8078,46 +8077,41 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ref_00404</t>
+          <t>ref_00403</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>«toponimi non segnalati nelle carte topografiche»</t>
+          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>K-0003</t>
+          <t>N-0002</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>reference/ref_00403</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8127,15 +8121,22 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>italia_2020</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>101</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8160,29 +8161,34 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ref_00588</t>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V-0005</t>
+          <t>N-0003</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>reference/ref_00132</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>reference/ref_00734</t>
+          <t>chora:IronicLowering</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8200,12 +8206,19 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H111" t="n">
-        <v>142</v>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8220,7 +8233,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8230,39 +8243,34 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>ref_00132</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>«ironico abbassamento»</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>I-0001</t>
+          <t>K-0001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>narrativeplace/ca_francesi</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8272,20 +8280,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
-        <v>512</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>102–103</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8308,36 +8313,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>«località nei pressi della stazione delle Frattocchie»</t>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>I-0002</t>
+          <t>K-0002</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_ser_paolo</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8347,20 +8347,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>512</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>169</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8370,12 +8365,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Risponde a K-0001 (D-087).</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8383,31 +8378,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>K-0001</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>I-0003</t>
+          <t>U-0010</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>narrativeplace/fontana_di_papa</t>
+          <t>reference/ref_00404</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8426,16 +8426,11 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>658</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>492</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8458,36 +8453,46 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>ref_00529</t>
+          <t>ref_00404</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>T-0021</t>
+          <t>K-0003</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1924</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8497,17 +8502,15 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>658 (Bertarelli 1924, p. 561)</t>
-        </is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>101</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8522,34 +8525,39 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>ref_00588</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>I-0004</t>
+          <t>V-0005</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>narrativeplace/osteriuccia_bivio</t>
+          <t>reference/ref_00132</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>reference/ref_00734</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8568,16 +8576,11 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>776</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>142</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8592,7 +8595,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8602,34 +8605,34 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ref_00736</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>T-0022</t>
+          <t>I-0001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>narrativeplace/ca_francesi</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8647,14 +8650,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+      <c r="H117" t="n">
+        <v>512</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8669,34 +8675,39 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>I-0002</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ciampino</t>
+          <t>narrativeplace/tor_ser_paolo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8714,14 +8725,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+      <c r="H118" t="n">
+        <v>512</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8736,34 +8750,39 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>I-0003</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>narrativeplace/fontana_di_papa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8781,14 +8800,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+      <c r="H119" t="n">
+        <v>658</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8803,19 +8825,24 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>ref_00529</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8825,12 +8852,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_frattocchie</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8850,12 +8877,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>658 (Bertarelli 1924, p. 561)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8882,22 +8909,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>T-0004</t>
+          <t>I-0004</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_torraccio</t>
+          <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8915,14 +8942,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+      <c r="H121" t="n">
+        <v>776</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8937,19 +8967,29 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>T-0005</t>
+          <t>T-0022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8959,7 +8999,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_due_santi</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8984,12 +9024,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9016,7 +9056,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>T-0006</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9026,7 +9066,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_ciampino</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9056,7 +9096,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9083,7 +9123,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9093,7 +9133,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9123,7 +9163,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9150,7 +9190,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9160,7 +9200,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_divino_amore</t>
+          <t>gazetteer/gaz_frattocchie</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9190,7 +9230,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9217,7 +9257,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0004</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9227,7 +9267,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pavona</t>
+          <t>gazetteer/gaz_torraccio</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9257,7 +9297,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9284,7 +9324,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>T-0010</t>
+          <t>T-0005</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9294,7 +9334,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_solforata</t>
+          <t>gazetteer/gaz_due_santi</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9324,7 +9364,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9351,7 +9391,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>T-0006</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9361,7 +9401,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pratica_di_mare</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9391,7 +9431,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9418,7 +9458,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>T-0012</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9428,7 +9468,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9458,7 +9498,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9485,7 +9525,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>T-0013</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9495,7 +9535,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_falcognana</t>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9525,7 +9565,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9552,7 +9592,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>T-0014</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9562,7 +9602,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_cecchina</t>
+          <t>gazetteer/gaz_pavona</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9592,7 +9632,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9619,7 +9659,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>T-0015</t>
+          <t>T-0010</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9629,7 +9669,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_albano_laziale</t>
+          <t>gazetteer/gaz_solforata</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9659,7 +9699,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9686,7 +9726,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>T-0016</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9696,7 +9736,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_zagarolo</t>
+          <t>gazetteer/gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9726,7 +9766,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9753,7 +9793,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>T-0017</t>
+          <t>T-0012</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9763,7 +9803,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_marino</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9793,7 +9833,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9820,7 +9860,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>T-0018</t>
+          <t>T-0013</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9830,7 +9870,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ariccia</t>
+          <t>gazetteer/gaz_falcognana</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9860,7 +9900,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9887,7 +9927,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T-0019</t>
+          <t>T-0014</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9897,7 +9937,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_santa_palomba</t>
+          <t>gazetteer/gaz_cecchina</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9927,7 +9967,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9954,7 +9994,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T-0020</t>
+          <t>T-0015</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9964,7 +10004,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_rocca_di_papa</t>
+          <t>gazetteer/gaz_albano_laziale</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9994,7 +10034,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10021,17 +10061,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>K-0004</t>
+          <t>T-0016</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>work/quer_pasticciaccio</t>
+          <t>gazetteer/gaz_zagarolo</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10051,12 +10096,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>418–419</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10071,24 +10116,19 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>T-0023</t>
+          <t>T-0017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10098,12 +10138,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_marino</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10123,12 +10163,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10149,18 +10189,13 @@
       <c r="O139" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>T-0024</t>
+          <t>T-0018</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10170,7 +10205,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_ariccia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10195,12 +10230,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10227,17 +10262,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>K-0005</t>
+          <t>T-0019</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>gazetteer/gaz_santa_palomba</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10257,12 +10297,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10283,28 +10323,28 @@
       <c r="O141" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>K-0006</t>
+          <t>T-0020</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>gazetteer/gaz_rocca_di_papa</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10322,12 +10362,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H142" t="n">
-        <v>911</v>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10342,24 +10384,19 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>K-0007</t>
+          <t>K-0004</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10369,7 +10406,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>work/quer_pasticciaccio</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10387,12 +10424,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H143" t="n">
-        <v>911</v>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>418–419</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10417,29 +10456,34 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>«immaginaria»</t>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>K-0008</t>
+          <t>T-0023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -10449,17 +10493,17 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>268–269</t>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10474,7 +10518,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -10482,16 +10526,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>ref_00534</t>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>T-0025</t>
+          <t>T-0024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10501,12 +10545,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_monti_ernici</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10526,12 +10570,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10558,27 +10602,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>I-0005</t>
+          <t>K-0005</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -10588,22 +10627,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>239–240</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10618,7 +10652,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -10626,16 +10660,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>«re-invenzione romantica»</t>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>K-0009</t>
+          <t>K-0006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10645,12 +10679,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>narrativeplace/marino</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -10660,17 +10694,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>293–294</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>911</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10691,33 +10723,33 @@
       <c r="O147" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>N-0004</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>chora:Paraetymology</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10727,15 +10759,15 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>273</v>
+        <v>911</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10758,21 +10790,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>ref_00538|ref_00539</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_castel_porziano</t>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>«immaginaria»</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>K-0010</t>
+          <t>K-0008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10782,7 +10809,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>reference/ref_00539</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10800,12 +10827,14 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H149" t="n">
-        <v>276</v>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10830,29 +10859,29 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>ref_00539</t>
+          <t>ref_00534</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>I-0006</t>
+          <t>T-0025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>gazetteer/gaz_monti_ernici</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10872,17 +10901,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>535–536</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10897,24 +10921,19 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>I-0007</t>
+          <t>I-0005</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10924,17 +10943,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10944,11 +10963,13 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>536</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>239–240</t>
+        </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -10957,7 +10978,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10967,7 +10988,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -10980,41 +11001,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>I-0008</t>
+          <t>K-0009</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>narrativeplace/marino</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11024,20 +11035,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>78</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>293–294</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11052,24 +11060,19 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>N-0005</t>
+          <t>N-0004</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11079,17 +11082,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>reference/ref_00437</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>chora:Synecdoche</t>
+          <t>chora:Paraetymology</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11099,15 +11102,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>537</v>
+        <v>273</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11132,39 +11135,34 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>ref_00437</t>
+          <t>ref_00538|ref_00539</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>I-0009</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>reference/ref_00539</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11174,20 +11172,15 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>537</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>276</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11212,14 +11205,14 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ref_00437</t>
+          <t>ref_00539</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>I-0010</t>
+          <t>I-0006</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11229,17 +11222,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_chigi</t>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11252,8 +11245,10 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H155" t="n">
-        <v>537</v>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>535–536</t>
+        </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -11262,7 +11257,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11272,7 +11267,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11287,19 +11282,14 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>I-0011</t>
+          <t>I-0007</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11309,17 +11299,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>narrativeplace/vite</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_via_della_vite</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11333,16 +11323,16 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>616</v>
+        <v>536</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11352,7 +11342,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11367,34 +11357,34 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V-0006</t>
+          <t>I-0008</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>reference/ref_00493</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>reference/ref_00735</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -11415,9 +11405,14 @@
       <c r="H157" t="n">
         <v>78</v>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11442,24 +11437,14 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>«da Faraja»</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>N-0006</t>
+          <t>N-0005</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11469,12 +11454,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>reference/ref_00437</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>chora:OnomasticPun</t>
+          <t>chora:Synecdoche</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11492,14 +11477,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
-        </is>
+      <c r="H158" t="n">
+        <v>537</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11520,74 +11503,466 @@
       <c r="O158" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>I-0009</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>537</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>I-0010</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_chigi</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>grassadonia|lagossi|marchetti</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>537</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>I-0011</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>narrativeplace/vite</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_via_della_vite</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>616</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>V-0006</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>reference/ref_00493</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>reference/ref_00735</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>78</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>N-0006</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>chora:OnomasticPun</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>S-osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>chora:Transformed</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H159" t="n">
+      <c r="H164" t="n">
         <v>776</v>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t>Motivazione di LS (10/10/2026, D-087).</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr">
+      <c r="N164" t="inlineStr">
         <is>
           <t>prova referenziale</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
+      <c r="O164" t="inlineStr">
         <is>
           <t>validata</t>
         </is>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W164"/>
+  <dimension ref="A1:W166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,7 +1078,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S-cantinone_albano</t>
+          <t>S-cantina_zamira</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>narrativeplace/cantinone_albano</t>
+          <t>narrativeplace/cantina_zamira</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1098,18 +1098,21 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>165</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1118,17 +1121,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Ristorante non identificato nel territorio di Albano Laziale».</t>
+          <t>Parte di casuccia_zamira (Is_Part_Of), sotto il laboratorio della Zamira (QPa 165): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Luogo entrato con la soglia di censimento (D-091).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1145,7 +1148,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S-casa_crocchiapani</t>
+          <t>S-cantinone_albano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1155,7 +1158,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>narrativeplace/casa_crocchiapani</t>
+          <t>narrativeplace/cantinone_albano</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1185,7 +1188,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Parte di tor_di_gheppio nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Abitazione immaginaria di Assunta (Tina) Crocchiapani».</t>
+          <t>Descrizione del censimento: «Ristorante non identificato nel territorio di Albano Laziale».</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1212,7 +1215,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S-casa_del_butiro</t>
+          <t>S-casa_crocchiapani</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1222,12 +1225,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>narrativeplace/casa_del_butiro</t>
+          <t>narrativeplace/casa_crocchiapani</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1247,12 +1250,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Casa immaginata nella zona dei Due Santi».</t>
+          <t>Parte di tor_di_gheppio nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Abitazione immaginaria di Assunta (Tina) Crocchiapani».</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1262,7 +1265,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078). Superata dalla lettura S-casa_del_butiro-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1279,7 +1282,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S-casa_del_butiro-2</t>
+          <t>S-casa_del_butiro</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1294,50 +1297,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>193</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Casa senza riscontro reale, che il testo situa lungo “la stradiccia della fonte de salute” (QPa 193), nella zona dei Due Santi a cui è ancorata. Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>S-casa_del_butiro</t>
+          <t>Descrizione del censimento: «Casa immaginata nella zona dei Due Santi».</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078). Superata dalla lettura S-casa_del_butiro-2 (D-090).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1354,7 +1349,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S-casal_bruciato</t>
+          <t>S-casa_del_butiro-2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1364,33 +1359,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>narrativeplace/casa_del_butiro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>268–269</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>193</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1399,22 +1392,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Casale reale dell'Agro romano, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569); posizione adottata TCI, alternativa IGM (D-037). Cap. 4, § 4.4 (r. 107): il disaccordo «non contrappone due differenti interpreti, bensì due distinti repertori cartografici». L'incertezza della posizione è SpatialDetermination, non statuto.</t>
+          <t>Casa senza riscontro reale, che il testo situa lungo “la stradiccia della fonte de salute” (QPa 193), nella zona dei Due Santi a cui è ancorata. Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>S-casa_del_butiro</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Statuto deciso e motivato da LS: D-029, D-037. Validata (D-071).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1426,7 +1424,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S-casello_km_20_25</t>
+          <t>S-casal_bruciato</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1436,12 +1434,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1456,7 +1454,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>268–269</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1466,7 +1469,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «casello ferroviario in prossimità di Casal Bruciato».</t>
+          <t>Casale reale dell'Agro romano, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569); posizione adottata TCI, alternativa IGM (D-037). Cap. 4, § 4.4 (r. 107): il disaccordo «non contrappone due differenti interpreti, bensì due distinti repertori cartografici». L'incertezza della posizione è SpatialDetermination, non statuto.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1476,12 +1479,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Statuto deciso e motivato da LS: D-029, D-037. Validata (D-071).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1493,7 +1496,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S-cassero</t>
+          <t>S-casello_km_20_25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1503,17 +1506,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>narrativeplace/cassero</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1523,11 +1526,8 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>169</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Toponimo senza riscontro, collocato dal testo "a Sant'Ignazio", fra le provenienze di QPa 169.</t>
+          <t>Descrizione del censimento: «casello ferroviario in prossimità di Casal Bruciato».</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S-castel_porcano</t>
+          <t>S-cassero</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1573,42 +1573,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
+          <t>narrativeplace/cassero</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>273, 276</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>169</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Luogo senza corrispondenza con un luogo attestato: il nome deforma Castelporziano, ma la festa notturna appartiene a uno spazio d'immaginazione d'autore.</t>
+          <t>Toponimo senza riscontro, collocato dal testo "a Sant'Ignazio", fra le provenienze di QPa 169.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1618,12 +1616,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-castel_porcano-2 (D-090).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1635,7 +1633,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S-castel_porcano-2</t>
+          <t>S-castel_porcano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1650,55 +1648,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>213</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>273, 276</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Luogo del sogno di Pestalozzi, senza riscontro reale; il nome gioca su Castelporziano (Manzotti 2010, p. 273; N-0004), e attraverso il nome il luogo resta legato a una geografia nota (QPa 213). Luogo inventato secondo Reuschel e Hurni (2011).</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>S-castel_porcano</t>
+          <t>Luogo senza corrispondenza con un luogo attestato: il nome deforma Castelporziano, ma la festa notturna appartiene a uno spazio d'immaginazione d'autore.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-castel_porcano-2 (D-090).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1710,7 +1705,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S-castello</t>
+          <t>S-castel_porcano-2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1720,31 +1715,31 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>293</v>
+        <v>213</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1753,39 +1748,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
+          <t>Luogo del sogno di Pestalozzi, senza riscontro reale; il nome gioca su Castelporziano (Manzotti 2010, p. 273; N-0004), e attraverso il nome il luogo resta legato a una geografia nota (QPa 213). Luogo inventato secondo Reuschel e Hurni (2011).</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>S-castel_porcano</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S-casuccia_zamira</t>
+          <t>S-castello</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1795,17 +1790,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>narrativeplace/casuccia_zamira</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1813,6 +1808,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>293</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>si</t>
@@ -1820,7 +1823,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
+          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1830,24 +1833,29 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S-cobianchi</t>
+          <t>S-casuccia_zamira</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1857,29 +1865,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>narrativeplace/cobianchi</t>
+          <t>narrativeplace/casuccia_zamira</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>censimento_gaddatlas</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>si</t>
@@ -1887,7 +1890,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
+          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1897,7 +1900,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1914,7 +1917,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S-colli_saluberrimi</t>
+          <t>S-cobianchi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1924,7 +1927,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>narrativeplace/colli_saluberrimi</t>
+          <t>narrativeplace/cobianchi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1934,7 +1937,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1942,6 +1945,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>si</t>
@@ -1949,7 +1957,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
+          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1959,12 +1967,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1976,7 +1984,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S-ditta_ciurlani</t>
+          <t>S-colli_saluberrimi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/colli_saluberrimi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1996,24 +2004,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>si</t>
@@ -2021,7 +2019,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
+          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2031,7 +2029,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2048,7 +2046,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S-edicola_due_santi</t>
+          <t>S-ditta_ciurlani</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2058,12 +2056,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>narrativeplace/ditta_ciurlani</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2078,11 +2076,13 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>246</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2091,12 +2091,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>C-edicola_due_santi</t>
+          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2106,12 +2101,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
+          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2123,7 +2118,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S-gioielliere_catellani</t>
+          <t>S-edicola_due_santi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2133,12 +2128,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>narrativeplace/gioielliere_catellani</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2153,8 +2148,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>246</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2163,7 +2161,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «negozio non identificabile».</t>
+          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2173,12 +2176,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2190,7 +2193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S-grotta_de_sor_pippo</t>
+          <t>S-gioielliere_catellani</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2200,12 +2203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>narrativeplace/grotta_de_sor_pippo</t>
+          <t>narrativeplace/gioielliere_catellani</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2230,7 +2233,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
+          <t>Descrizione del censimento: «negozio non identificabile».</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2257,7 +2260,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S-laboratorio_zamira</t>
+          <t>S-grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2267,7 +2270,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>narrativeplace/laboratorio_zamira</t>
+          <t>narrativeplace/grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2287,7 +2290,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2297,7 +2300,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
+          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2324,7 +2327,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S-montagne_degli_equi</t>
+          <t>S-laboratorio_zamira</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2334,12 +2337,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>narrativeplace/montagne_degli_equi</t>
+          <t>narrativeplace/laboratorio_zamira</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2354,7 +2357,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>sabatino_cap4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2364,7 +2367,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
+          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2391,7 +2394,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S-monte_circeo</t>
+          <t>S-montagne_degli_equi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2401,7 +2404,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_circeo</t>
+          <t>narrativeplace/montagne_degli_equi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2431,7 +2434,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
+          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2458,7 +2461,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S-monte_nuncupale</t>
+          <t>S-monte_circeo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2468,17 +2471,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_nuncupale</t>
+          <t>narrativeplace/monte_circeo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2488,20 +2491,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>173</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
+          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-monte_nuncupale-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S-monte_nuncupale-2</t>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2566,27 +2566,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Rilievo senza riscontro reale, posto dal testo nell’orizzonte dei Colli Albani: “da Rocca Orsina al Monte Nuncupale, su” (QPa 173). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>S-monte_nuncupale</t>
+          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-monte_nuncupale-2 (D-090).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2603,7 +2598,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S-orto_vigna_due_santi</t>
+          <t>S-monte_nuncupale-2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2613,7 +2608,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>narrativeplace/orto_vigna_due_santi</t>
+          <t>narrativeplace/monte_nuncupale</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2623,18 +2618,21 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>173</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2643,17 +2641,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
+          <t>Rilievo senza riscontro reale, posto dal testo nell’orizzonte dei Colli Albani: “da Rocca Orsina al Monte Nuncupale, su” (QPa 173). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2670,7 +2673,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S-palazzo_219</t>
+          <t>S-orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2680,12 +2683,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_219</t>
+          <t>narrativeplace/orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2710,7 +2713,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
+          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2737,7 +2740,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S-palazzo_del_mappamondo</t>
+          <t>S-palazzo_219</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2747,7 +2750,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_219</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2757,7 +2760,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2767,11 +2770,8 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>537</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
+          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S-palazzo_simonetti</t>
+          <t>S-palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2827,21 +2827,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2850,12 +2850,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>C-palazzo_simonetti</t>
+          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2865,7 +2860,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2882,7 +2877,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S-passaggio_livello_casal_bruciato</t>
+          <t>S-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2892,7 +2887,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2912,8 +2907,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>78</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2922,7 +2920,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2937,7 +2940,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2949,7 +2952,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S-pensione_burgess</t>
+          <t>S-passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2959,12 +2962,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>narrativeplace/pensione_burgess</t>
+          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2989,7 +2992,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
+          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3016,7 +3019,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S-piani_alti_219</t>
+          <t>S-pensione_burgess</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3026,12 +3029,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>narrativeplace/piani_alti_219</t>
+          <t>narrativeplace/pensione_burgess</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3056,7 +3059,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3083,7 +3086,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S-piccarozzi</t>
+          <t>S-piani_alti_219</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3093,7 +3096,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>narrativeplace/piccarozzi</t>
+          <t>narrativeplace/piani_alti_219</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3123,7 +3126,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3150,7 +3153,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S-ponte_di_santa_fumia</t>
+          <t>S-piccarozzi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3160,7 +3163,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_di_santa_fumia</t>
+          <t>narrativeplace/piccarozzi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3180,12 +3183,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3195,7 +3193,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
+          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3205,12 +3203,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3222,7 +3220,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S-ponte_divino_amore</t>
+          <t>S-ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3232,7 +3230,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_divino_amore</t>
+          <t>narrativeplace/ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3252,7 +3250,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3262,7 +3265,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
+          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3272,12 +3275,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3289,7 +3292,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S-porta_borgo_marino</t>
+          <t>S-ponte_divino_amore</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3299,7 +3302,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>narrativeplace/porta_borgo_marino</t>
+          <t>narrativeplace/ponte_divino_amore</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3329,7 +3332,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
+          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3356,7 +3359,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S-pozzofondo</t>
+          <t>S-porta_borgo_marino</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3366,12 +3369,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>narrativeplace/pozzofondo</t>
+          <t>narrativeplace/porta_borgo_marino</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3396,7 +3399,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
+          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3423,7 +3426,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S-robine_vecchie</t>
+          <t>S-pozzofondo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3433,12 +3436,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>narrativeplace/robine_vecchie</t>
+          <t>narrativeplace/pozzofondo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3453,11 +3456,8 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>491</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
+          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S-roccafringoli</t>
+          <t>S-robine_vecchie</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3503,17 +3503,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>narrativeplace/roccafringoli</t>
+          <t>narrativeplace/robine_vecchie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3523,20 +3523,20 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>107</v>
+        <v>491</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
+          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-roccafringoli-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S-roccafringoli-2</t>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3601,27 +3601,22 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paese senza riscontro reale, collocato dal testo entro una geografia nota: “su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio” (QPa 107). Luogo inventato secondo Reuschel e Hurni (2011): “an invented setting within familiar geographical reality”.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>S-roccafringoli</t>
+          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-roccafringoli-2 (D-090).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3638,7 +3633,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S-scale</t>
+          <t>S-roccafringoli-2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3648,28 +3643,31 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>narrativeplace/scale</t>
+          <t>narrativeplace/roccafringoli</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>107</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3678,17 +3676,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Paese senza riscontro reale, collocato dal testo entro una geografia nota: “su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio” (QPa 107). Luogo inventato secondo Reuschel e Hurni (2011): “an invented setting within familiar geographical reality”.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3705,7 +3708,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S-scala_a</t>
+          <t>S-sacello_responsale</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3715,28 +3718,31 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_a</t>
+          <t>narrativeplace/sacello_responsale</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>165</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3745,17 +3751,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
+          <t>Parte di casuccia_zamira (Is_Part_Of), oltre l'uscio con catenaccio della sala di consultazione, cioè della cantina (QPa 165): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Luogo entrato con la soglia di censimento (D-091).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3772,7 +3778,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S-scala_b</t>
+          <t>S-scale</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3782,7 +3788,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_b</t>
+          <t>narrativeplace/scale</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3812,7 +3818,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3839,7 +3845,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S-scerpure</t>
+          <t>S-scala_a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3849,17 +3855,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>narrativeplace/scerpure</t>
+          <t>narrativeplace/scala_a</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3869,20 +3875,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>141</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3892,7 +3895,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-scerpure-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3909,7 +3912,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S-scerpure-2</t>
+          <t>S-scala_b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3919,31 +3922,28 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>narrativeplace/scerpure</t>
+          <t>narrativeplace/scala_b</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>141</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3952,22 +3952,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Città senza riscontro reale, collocata dal testo “sulle rive, più o meno, del nativo Brahmaputra” (QPa 141). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>S-scerpure</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3984,7 +3979,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S-stazione_carabinieri_castello</t>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3994,37 +3989,40 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_carabinieri_castello</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>141</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4034,7 +4032,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-scerpure-2 (D-090).</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4051,7 +4049,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S-stazione_pavona</t>
+          <t>S-scerpure-2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4061,28 +4059,31 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_pavona</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>141</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4091,17 +4092,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
+          <t>Città senza riscontro reale, collocata dal testo “sulle rive, più o meno, del nativo Brahmaputra” (QPa 141). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4118,7 +4124,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S-strada_di_campagna_celio</t>
+          <t>S-stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4128,7 +4134,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>narrativeplace/strada_di_campagna_celio</t>
+          <t>narrativeplace/stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4158,7 +4164,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
+          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4185,7 +4191,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S-tenenza_carabinieri_marino</t>
+          <t>S-stazione_pavona</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4195,7 +4201,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
+          <t>narrativeplace/stazione_pavona</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4205,7 +4211,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4215,12 +4221,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>293–294</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4230,7 +4231,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
+          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4240,12 +4241,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4257,7 +4258,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S-terzo_piano_219</t>
+          <t>S-strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4267,7 +4268,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>narrativeplace/terzo_piano_219</t>
+          <t>narrativeplace/strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4297,7 +4298,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
+          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4324,7 +4325,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S-tor_di_gheppio</t>
+          <t>S-tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4334,31 +4335,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>679</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>293–294</t>
+        </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4367,7 +4370,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
+          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4377,12 +4380,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4394,7 +4397,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S-via_delle_oche</t>
+          <t>S-terzo_piano_219</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4404,17 +4407,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>narrativeplace/via_delle_oche</t>
+          <t>narrativeplace/terzo_piano_219</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4424,11 +4427,8 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>22</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4464,7 +4464,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S-villino_lungotevere</t>
+          <t>S-tor_di_gheppio</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>narrativeplace/villino_lungotevere</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4492,6 +4492,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>679</v>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>si</t>
@@ -4499,7 +4507,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
+          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4509,7 +4517,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4526,27 +4534,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>U-0001</t>
+          <t>S-via_delle_oche</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>narrativeplace/via_delle_oche</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>chora:Confusion</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4556,17 +4564,20 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>268–269</t>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>22</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
+          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4576,72 +4587,59 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>documentaria</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>U-0002</t>
+          <t>S-villino_lungotevere</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/villino_lungotevere</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>293</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
+          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4651,39 +4649,24 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>identificazione</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>costruttiva</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>U-0003</t>
+          <t>U-0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4693,35 +4676,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Confusion</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>78</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
+          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4746,24 +4731,19 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>identificazione</t>
+          <t>geometria</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>U-0004</t>
+          <t>U-0002</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4773,12 +4753,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4793,15 +4773,15 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>491</v>
+        <v>293</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
+          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4826,19 +4806,24 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>identificazione</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>documentaria</t>
+          <t>costruttiva</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>U-0005</t>
+          <t>U-0003</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4848,12 +4833,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_edicola_due_santi</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4868,15 +4853,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
+          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4891,7 +4876,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4901,19 +4886,24 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>geometria</t>
+          <t>identificazione</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>costruttiva</t>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>U-0006</t>
+          <t>U-0004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4923,17 +4913,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>narrativeplace/monti_ernici</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>chora:NonSpecificity</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4943,15 +4933,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>290</v>
+        <v>491</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
+          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4976,24 +4966,19 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>identificazione</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>ref_00541</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>U-0007</t>
+          <t>U-0005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5003,17 +4988,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>reference/ref_00523</t>
+          <t>gazetteer/gaz_edicola_due_santi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>chora:Oversight</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5027,11 +5012,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
+          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5046,7 +5031,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5056,19 +5041,19 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>geometria</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>documentaria</t>
+          <t>costruttiva</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>U-0008</t>
+          <t>U-0006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5078,12 +5063,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>narrativeplace/direttissima_roma_napoli</t>
+          <t>narrativeplace/monti_ernici</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>chora:Anachronism</t>
+          <t>chora:NonSpecificity</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5102,11 +5087,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
+          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5141,59 +5126,52 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ref_00535|ref_00635|ref_00703</t>
+          <t>ref_00541</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>U-0007</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>reference/ref_00523</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>chora:Oversight</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>103–104</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>254</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
+          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5203,7 +5181,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5214,58 +5192,61 @@
       <c r="O68" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>documentaria</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>U-0008</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:Anachronism</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>270</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
+          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5275,7 +5256,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5288,16 +5269,26 @@
           <t>bozza</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>ref_00535|ref_00635|ref_00703</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5312,12 +5303,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:AuthorMemory</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>perosa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5327,11 +5318,13 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>669</v>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>103–104</t>
+        </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5340,7 +5333,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5367,7 +5360,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0002</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5377,17 +5370,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>lugnani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5402,7 +5395,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>103–104</t>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5412,7 +5405,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5422,7 +5415,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5433,13 +5426,18 @@
       <c r="O71" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>M-0003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5449,17 +5447,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>cortellessa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5469,13 +5467,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
-        </is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>669</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5484,7 +5480,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5494,7 +5490,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5505,18 +5501,13 @@
       <c r="O72" t="inlineStr">
         <is>
           <t>bozza</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>M-0004</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5531,12 +5522,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:AuthorMemory</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>perosa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5546,11 +5537,13 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>669</v>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>103–104</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5559,7 +5552,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5586,27 +5579,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>P-0001</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>partition</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>partition/citta_campagna</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>zone/roma_citta|zone/campagna_romana</t>
+          <t>chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>lugnani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5616,22 +5609,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>§ 4.1, § 4.6 (R20)</t>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5641,7 +5634,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5652,33 +5645,38 @@
       <c r="O74" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C-edicola_due_santi</t>
+          <t>M-0006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>cortellessa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5688,8 +5686,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>669</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5698,12 +5699,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5713,29 +5719,29 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C-palazzo_simonetti</t>
+          <t>P-0001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>partition</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>partition/citta_campagna</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>zone/roma_citta|zone/campagna_romana</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5750,54 +5756,64 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>§ 4.1, § 4.6 (R20)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
+          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
+          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C-casal_bruciato</t>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casal_bruciato</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5822,17 +5838,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
+          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
+          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5844,22 +5860,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>I-casal_bruciato</t>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5874,32 +5890,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>C-casal_bruciato</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5916,27 +5922,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V-0001</t>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>reference/ref_00724</t>
+          <t>gazetteer/gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5946,67 +5952,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>241</v>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
+          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V-0002</t>
+          <t>I-casal_bruciato</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>reference/ref_00436</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>reference/ref_00725</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6016,15 +6014,27 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>78</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
+          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6032,31 +6042,21 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V-0003a</t>
+          <t>V-0001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6066,17 +6066,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>reference/ref_00007</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>reference/ref_00724</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6086,17 +6086,15 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>241</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
+          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6106,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6128,7 +6126,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V-0003b</t>
+          <t>V-0002</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6138,17 +6136,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>reference/ref_00036</t>
+          <t>reference/ref_00436</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>reference/ref_00725</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6158,17 +6156,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>78</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
+          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6200,7 +6196,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V-0004a</t>
+          <t>V-0003a</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6210,7 +6206,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>reference/ref_00008</t>
+          <t>reference/ref_00007</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6240,7 +6236,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
+          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6272,7 +6268,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V-0004b</t>
+          <t>V-0003b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6282,7 +6278,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>reference/ref_00038</t>
+          <t>reference/ref_00036</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6312,7 +6308,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
+          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6344,27 +6340,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R-0001</t>
+          <t>V-0004a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>reference/ref_00008</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6374,20 +6370,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>297</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6397,7 +6390,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6407,34 +6400,39 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R-0002</t>
+          <t>V-0004b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+          <t>reference/ref_00038</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6444,20 +6442,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>169</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6467,7 +6462,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6477,14 +6472,19 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R-0003</t>
+          <t>R-0001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>route/tragitto_tenenza_due_santi</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6517,10 +6517,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>208–215</t>
-        </is>
+      <c r="H87" t="n">
+        <v>297</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6529,12 +6527,17 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6551,7 +6554,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R-0004</t>
+          <t>R-0002</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6561,12 +6564,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6585,7 +6588,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>292</v>
+        <v>169</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6594,7 +6597,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6604,7 +6607,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6621,7 +6624,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R-0005</t>
+          <t>R-0003</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6631,7 +6634,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>route/tragitto_viminale_merulana</t>
+          <t>route/tragitto_tenenza_due_santi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6654,8 +6657,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H89" t="n">
-        <v>25</v>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>208–215</t>
+        </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6664,7 +6669,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6686,7 +6691,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R-0006</t>
+          <t>R-0004</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6696,12 +6701,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>route/tragitto_appia_falcognana</t>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6729,7 +6734,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6739,7 +6744,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6756,7 +6761,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R-0007</t>
+          <t>R-0005</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6766,7 +6771,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>route/tragitto_agostino_aquiro</t>
+          <t>route/tragitto_viminale_merulana</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6790,7 +6795,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6799,17 +6804,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R-0008</t>
+          <t>R-0006</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>route/tragitto_cecchina_anziate</t>
+          <t>route/tragitto_appia_falcognana</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R-0009</t>
+          <t>R-0007</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>route/tragitto_colonna_treccani</t>
+          <t>route/tragitto_agostino_aquiro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R-0010</t>
+          <t>R-0008</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>route/tragitto_frattocchie_ciampino</t>
+          <t>route/tragitto_cecchina_anziate</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7036,7 +7036,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R-0011</t>
+          <t>R-0009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>route/tragitto_monti_piazza_esedra</t>
+          <t>route/tragitto_colonna_treccani</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7106,7 +7106,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R-0012</t>
+          <t>R-0010</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+          <t>route/tragitto_frattocchie_ciampino</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7176,7 +7176,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R-0013</t>
+          <t>R-0011</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>route/tragitto_chiara_pantheon</t>
+          <t>route/tragitto_monti_piazza_esedra</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R-0014</t>
+          <t>R-0012</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>route/tragitto_duesanti_frattocchie</t>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7289,12 +7289,17 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7311,7 +7316,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R-0015</t>
+          <t>R-0013</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7321,7 +7326,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+          <t>route/tragitto_chiara_pantheon</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7344,10 +7349,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>139–140</t>
-        </is>
+      <c r="H99" t="n">
+        <v>41</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7356,12 +7359,17 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7378,7 +7386,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R-0016</t>
+          <t>R-0014</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7388,12 +7396,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_albano_laziale</t>
+          <t>route/tragitto_duesanti_frattocchie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>chora:DirectionalRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7412,7 +7420,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7421,17 +7429,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7448,7 +7451,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R-0017</t>
+          <t>R-0015</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7458,7 +7461,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_due_santi</t>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7481,8 +7484,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>206</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7491,7 +7496,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7513,7 +7518,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R-0018</t>
+          <t>R-0016</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7523,12 +7528,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_santo_stefano</t>
+          <t>route/tragitto_marino_albano_laziale</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:DirectionalRoute</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7547,7 +7552,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>153</v>
+        <v>278</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -7556,7 +7561,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7566,7 +7571,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7583,7 +7588,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R-0019</t>
+          <t>R-0017</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7593,7 +7598,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>route/tragitto_merulana_policlinico</t>
+          <t>route/tragitto_marino_due_santi</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7617,7 +7622,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -7626,17 +7631,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7653,7 +7653,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R-0020</t>
+          <t>R-0018</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>route/tragitto_marino_santo_stefano</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>chora:DreamedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7723,7 +7723,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R-0021</t>
+          <t>R-0019</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+          <t>route/tragitto_merulana_policlinico</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7793,27 +7793,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>R-0020</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>geometry/L-0001</t>
+          <t>chora:DreamedRoute</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7823,13 +7823,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>212</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -7838,7 +7836,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7848,44 +7846,44 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Posizione adottata (D-037).</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>R-0021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>geometry/L-0002</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7895,22 +7893,20 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>237</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7920,44 +7916,44 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Posizione alternativa (D-037).</t>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>U-0009</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_bologna</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>geometry/L-0001</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7965,19 +7961,34 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
+          <t>Posizione adottata (D-037).</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -7988,48 +7999,33 @@
       <c r="O108" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>ref_00028</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>N-0001</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>geometry/L-0002</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8039,12 +8035,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>491–492</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8054,64 +8050,54 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Posizione alternativa (D-037).</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N-0002</t>
+          <t>U-0009</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_bologna</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8119,24 +8105,9 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8146,12 +8117,12 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8159,21 +8130,26 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>refuso per «Rovine vecchie»</t>
+          <t>ref_00028</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N-0003</t>
+          <t>N-0001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8188,7 +8164,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>chora:IronicLowering</t>
+          <t>chora:TypoHypothesis</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8218,7 +8194,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8248,19 +8224,19 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>«ironico abbassamento»</t>
+          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>K-0001</t>
+          <t>N-0002</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8268,9 +8244,14 @@
           <t>reference/ref_00403</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8280,17 +8261,22 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>italia_2020</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>102–103</t>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8316,18 +8302,23 @@
       <c r="R112" t="inlineStr">
         <is>
           <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>K-0002</t>
+          <t>N-0003</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8335,9 +8326,14 @@
           <t>reference/ref_00403</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>chora:IronicLowering</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8347,15 +8343,22 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
-        <v>169</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8365,12 +8368,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Risponde a K-0001 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8383,36 +8386,31 @@
           <t>ref_00403</t>
         </is>
       </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>K-0001</t>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>«ironico abbassamento»</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>U-0010</t>
+          <t>K-0001</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>reference/ref_00404</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>chora:Incompleteness</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8422,15 +8420,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>492</v>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>102–103</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8453,31 +8453,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>ref_00404</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>«toponimi non segnalati nelle carte topografiche»</t>
+          <t>ref_00403</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>K-0003</t>
+          <t>K-0002</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8487,12 +8472,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8502,15 +8487,15 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>italia_2020</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8520,12 +8505,12 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Risponde a K-0001 (D-087).</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8535,29 +8520,34 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>ref_00588</t>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>K-0001</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>V-0005</t>
+          <t>U-0010</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>reference/ref_00132</t>
+          <t>reference/ref_00404</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>reference/ref_00734</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8576,11 +8566,11 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>142</v>
+        <v>492</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8595,7 +8585,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8603,41 +8593,46 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ref_00132</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00404</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>I-0001</t>
+          <t>K-0003</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>narrativeplace/ca_francesi</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8647,20 +8642,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>italia_2020</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>512</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>101</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8683,31 +8673,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>«località nei pressi della stazione delle Frattocchie»</t>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>ref_00588</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>I-0002</t>
+          <t>V-0005</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_ser_paolo</t>
+          <t>reference/ref_00132</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>reference/ref_00734</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8726,16 +8716,11 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>512</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>142</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8750,7 +8735,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8758,16 +8743,21 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>I-0003</t>
+          <t>I-0001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8777,12 +8767,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>narrativeplace/fontana_di_papa</t>
+          <t>narrativeplace/ca_francesi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8801,7 +8791,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>658</v>
+        <v>512</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -8810,7 +8800,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8833,31 +8823,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>ref_00529</t>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>T-0021</t>
+          <t>I-0002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>narrativeplace/tor_ser_paolo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8875,14 +8865,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>658 (Bertarelli 1924, p. 561)</t>
+      <c r="H120" t="n">
+        <v>512</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8897,19 +8890,24 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>I-0004</t>
+          <t>I-0003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8919,12 +8917,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>narrativeplace/osteriuccia_bivio</t>
+          <t>narrativeplace/fontana_di_papa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8943,16 +8941,16 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>776</v>
+        <v>658</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8977,19 +8975,14 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ref_00736</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
+          <t>ref_00529</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>T-0022</t>
+          <t>T-0021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8999,12 +8992,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9024,12 +9017,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+          <t>658 (Bertarelli 1924, p. 561)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9056,22 +9049,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>I-0004</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ciampino</t>
+          <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9089,14 +9082,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+      <c r="H123" t="n">
+        <v>776</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9111,19 +9107,29 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>T-0022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9133,7 +9139,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9158,12 +9164,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9190,7 +9196,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9200,7 +9206,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_frattocchie</t>
+          <t>gazetteer/gaz_ciampino</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9230,7 +9236,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9257,7 +9263,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>T-0004</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9267,7 +9273,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_torraccio</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9297,7 +9303,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9324,7 +9330,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>T-0005</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9334,7 +9340,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_due_santi</t>
+          <t>gazetteer/gaz_frattocchie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9364,7 +9370,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9391,7 +9397,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>T-0006</t>
+          <t>T-0004</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9401,7 +9407,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_torraccio</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9431,7 +9437,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9458,7 +9464,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>T-0005</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9468,7 +9474,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_due_santi</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9498,7 +9504,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9525,7 +9531,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0006</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9535,7 +9541,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_divino_amore</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9565,7 +9571,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9592,7 +9598,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9602,7 +9608,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pavona</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9632,7 +9638,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9659,7 +9665,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>T-0010</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9669,7 +9675,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_solforata</t>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9699,7 +9705,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9726,7 +9732,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9736,7 +9742,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pratica_di_mare</t>
+          <t>gazetteer/gaz_pavona</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9766,7 +9772,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9793,7 +9799,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>T-0012</t>
+          <t>T-0010</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9803,7 +9809,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>gazetteer/gaz_solforata</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9833,7 +9839,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9860,7 +9866,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>T-0013</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9870,7 +9876,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_falcognana</t>
+          <t>gazetteer/gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9900,7 +9906,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9927,7 +9933,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T-0014</t>
+          <t>T-0012</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9937,7 +9943,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_cecchina</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9967,7 +9973,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9994,7 +10000,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T-0015</t>
+          <t>T-0013</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10004,7 +10010,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_albano_laziale</t>
+          <t>gazetteer/gaz_falcognana</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10034,7 +10040,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10061,7 +10067,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T-0016</t>
+          <t>T-0014</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10071,7 +10077,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_zagarolo</t>
+          <t>gazetteer/gaz_cecchina</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10101,7 +10107,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10128,7 +10134,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>T-0017</t>
+          <t>T-0015</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10138,7 +10144,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_marino</t>
+          <t>gazetteer/gaz_albano_laziale</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10168,7 +10174,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10195,7 +10201,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>T-0018</t>
+          <t>T-0016</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10205,7 +10211,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ariccia</t>
+          <t>gazetteer/gaz_zagarolo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10235,7 +10241,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10262,7 +10268,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>T-0019</t>
+          <t>T-0017</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10272,7 +10278,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_santa_palomba</t>
+          <t>gazetteer/gaz_marino</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10302,7 +10308,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10329,7 +10335,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>T-0020</t>
+          <t>T-0018</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10339,7 +10345,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_rocca_di_papa</t>
+          <t>gazetteer/gaz_ariccia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10369,7 +10375,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10396,17 +10402,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>K-0004</t>
+          <t>T-0019</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>work/quer_pasticciaccio</t>
+          <t>gazetteer/gaz_santa_palomba</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10426,12 +10437,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>418–419</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10446,24 +10457,19 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>T-0023</t>
+          <t>T-0020</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10473,12 +10479,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_rocca_di_papa</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10498,12 +10504,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10524,33 +10530,23 @@
       <c r="O144" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>T-0024</t>
+          <t>K-0004</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1925</t>
+          <t>work/quer_pasticciaccio</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10570,12 +10566,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>418–419</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10590,29 +10586,39 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>K-0005</t>
+          <t>T-0023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10632,12 +10638,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10660,26 +10666,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>ref_00698</t>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>K-0006</t>
+          <t>T-0024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10697,12 +10708,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H147" t="n">
-        <v>911</v>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10717,24 +10730,19 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>K-0007</t>
+          <t>K-0005</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10744,7 +10752,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10762,12 +10770,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H148" t="n">
-        <v>911</v>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10782,7 +10792,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -10790,16 +10800,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>«immaginaria»</t>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>K-0008</t>
+          <t>K-0006</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10809,12 +10819,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -10824,17 +10834,15 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>268–269</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>911</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10857,31 +10865,26 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>ref_00534</t>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>T-0025</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_monti_ernici</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1924</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10899,14 +10902,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
-        </is>
+      <c r="H150" t="n">
+        <v>911</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10921,34 +10922,34 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>«immaginaria»</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>I-0005</t>
+          <t>K-0008</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10968,17 +10969,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>239–240</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>268–269</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11001,31 +10997,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>«re-invenzione romantica»</t>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>ref_00534</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>K-0009</t>
+          <t>T-0025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>narrativeplace/marino</t>
+          <t>gazetteer/gaz_monti_ernici</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11035,17 +11036,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>293–294</t>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11060,7 +11061,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -11072,22 +11073,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>N-0004</t>
+          <t>I-0005</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>chora:Paraetymology</t>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -11105,12 +11106,19 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H153" t="n">
-        <v>273</v>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>239–240</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11133,21 +11141,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>ref_00538|ref_00539</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_castel_porziano</t>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>K-0010</t>
+          <t>K-0009</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11157,7 +11160,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>reference/ref_00539</t>
+          <t>narrativeplace/marino</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11175,12 +11178,14 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H154" t="n">
-        <v>276</v>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>293–294</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11201,38 +11206,33 @@
       <c r="O154" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>ref_00539</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>I-0006</t>
+          <t>N-0004</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+          <t>chora:Paraetymology</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11242,22 +11242,15 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>535–536</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>273</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11282,34 +11275,34 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ref_00435</t>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>I-0007</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>reference/ref_00539</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11319,20 +11312,15 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>536</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>276</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11342,7 +11330,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11357,19 +11345,14 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ref_00435</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+          <t>ref_00539</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>I-0008</t>
+          <t>I-0006</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11384,12 +11367,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11399,11 +11382,13 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>78</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>535–536</t>
+        </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -11412,7 +11397,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11427,7 +11412,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -11437,34 +11422,34 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ref_00435|ref_00725</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>N-0005</t>
+          <t>I-0007</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>reference/ref_00437</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>chora:Synecdoche</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11478,11 +11463,16 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>537</v>
+        <v>536</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11492,7 +11482,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11507,19 +11497,19 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>I-0009</t>
+          <t>I-0008</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11529,17 +11519,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11549,20 +11539,20 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11577,7 +11567,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -11587,34 +11577,34 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>ref_00437</t>
+          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>I-0010</t>
+          <t>N-0005</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>reference/ref_00437</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_chigi</t>
+          <t>chora:Synecdoche</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11630,14 +11620,9 @@
       <c r="H160" t="n">
         <v>537</v>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11647,7 +11632,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11665,16 +11650,16 @@
           <t>ref_00437</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>I-0011</t>
+          <t>I-0009</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11684,12 +11669,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>narrativeplace/vite</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_via_della_vite</t>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -11708,7 +11693,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>616</v>
+        <v>537</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -11717,7 +11702,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11742,39 +11727,34 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+          <t>ref_00437</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>V-0006</t>
+          <t>I-0010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>reference/ref_00493</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>reference/ref_00735</t>
+          <t>gazetteer/gaz_palazzo_chigi</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11784,15 +11764,20 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>78</v>
+        <v>537</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -11802,12 +11787,12 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11817,39 +11802,34 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>«da Faraja»</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>N-0006</t>
+          <t>I-0011</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/vite</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>chora:OnomasticPun</t>
+          <t>gazetteer/gaz_via_della_vite</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11867,14 +11847,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
+      <c r="H163" t="n">
+        <v>616</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11895,74 +11878,231 @@
       <c r="O163" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>V-0006</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>reference/ref_00493</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>reference/ref_00735</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>78</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>N-0006</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>chora:OnomasticPun</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>S-osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>chora:Transformed</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H164" t="n">
+      <c r="H166" t="n">
         <v>776</v>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>Motivazione di LS (10/10/2026, D-087).</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
+      <c r="N166" t="inlineStr">
         <is>
           <t>prova referenziale</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
+      <c r="O166" t="inlineStr">
         <is>
           <t>validata</t>
         </is>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W166"/>
+  <dimension ref="A1:W174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Revisione critica (D-090). Superata dalla lettura S-castel_porcano-3 (D-092).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1780,7 +1780,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S-castello</t>
+          <t>S-castel_porcano-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1790,31 +1790,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>293</v>
+        <v>679</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
+          <t>Deformazione onomastica di Castel Porziano, tenuta reale di caccia a sud di Roma, luogo della festa notturna nel sogno di Pestalozzi (Terzoli 2015, pp. 633–634, 679): un luogo reale rinominato e rimodellato.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>S-castel_porcano-2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
+          <t>Revisione critica (D-092).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S-casuccia_zamira</t>
+          <t>S-castello</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>narrativeplace/casuccia_zamira</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1883,6 +1883,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>293</v>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>si</t>
@@ -1890,7 +1898,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
+          <t>La «stazione di Castello» (QPa 279) è la stazione dei carabinieri di Castel Savello: identificazione adottata A-0002 (Manzotti 2010, p. 293). Il luogo testuale nomina in forma ellittica un luogo reale: statuto Imported. La lettura alternativa (Castel Gandolfo, A-0001) è anch'essa un luogo reale.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1900,24 +1908,29 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Decisione di LS (9/10/2026, REVIEW_2 § 2); prima Invented (bozza T-33).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S-cobianchi</t>
+          <t>S-casuccia_zamira</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1927,29 +1940,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>narrativeplace/cobianchi</t>
+          <t>narrativeplace/casuccia_zamira</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>censimento_gaddatlas</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>si</t>
@@ -1957,7 +1965,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
+          <t>Luogo del mondo diegetico della Zamira: segue lo statuto del laboratorio (laboratorio_zamira).</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1967,7 +1975,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1984,7 +1992,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S-colli_saluberrimi</t>
+          <t>S-cobianchi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>narrativeplace/colli_saluberrimi</t>
+          <t>narrativeplace/cobianchi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2004,7 +2012,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2012,6 +2020,11 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>si</t>
@@ -2019,7 +2032,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
+          <t>Descrizione del censimento: «Luogo specificato ma non identificabile».</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2029,12 +2042,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2046,7 +2059,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S-ditta_ciurlani</t>
+          <t>S-colli_saluberrimi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2056,7 +2069,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/colli_saluberrimi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2066,24 +2079,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>si</t>
@@ -2091,7 +2094,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
+          <t>Perifrasi d'autore per colli reali: i Colli Albani (ancora gaz_colli_albani).</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2101,7 +2104,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2118,7 +2121,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S-edicola_due_santi</t>
+          <t>S-ditta_ciurlani</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2128,12 +2131,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>narrativeplace/ditta_ciurlani</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2148,11 +2151,13 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>246</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2161,12 +2166,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>C-edicola_due_santi</t>
+          <t>Terzoli ricostruisce l'origine onomastica di Ciurlani e il gioco di parole con "truffaldino"; nessun elemento di collocazione topografica.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
+          <t>Validata da LS; pagine di Terzoli 2015 compilate (D-087).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2193,7 +2193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S-gioielliere_catellani</t>
+          <t>S-edicola_due_santi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>narrativeplace/gioielliere_catellani</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2223,8 +2223,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>246</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2233,7 +2236,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «negozio non identificabile».</t>
+          <t>Cap. 4, n. 24 (r. 601): «L'edicola dei Due Santi (QP 216, 219), che una prima lettura direbbe inventata, conserva secondo Manzotti una traccia nella piantina dei Castelli della guida del Touring». Imported (D-031); revisione della lettura di censimento (Imagined) in T-38.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2243,12 +2251,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Statuto deciso e motivato da LS: D-031. Validata (D-071).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2260,7 +2268,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S-grotta_de_sor_pippo</t>
+          <t>S-gioielliere_catellani</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2270,12 +2278,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>narrativeplace/grotta_de_sor_pippo</t>
+          <t>narrativeplace/gioielliere_catellani</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2300,7 +2308,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
+          <t>Descrizione del censimento: «negozio non identificabile».</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2327,7 +2335,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S-laboratorio_zamira</t>
+          <t>S-grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2337,7 +2345,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>narrativeplace/laboratorio_zamira</t>
+          <t>narrativeplace/grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2357,7 +2365,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2367,7 +2375,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
+          <t>Descrizione del censimento: «Trattoria non meglio identificata nel territorio di Marino».</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2394,7 +2402,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S-montagne_degli_equi</t>
+          <t>S-laboratorio_zamira</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2404,12 +2412,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>narrativeplace/montagne_degli_equi</t>
+          <t>narrativeplace/laboratorio_zamira</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>sabatino_cap4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2434,7 +2442,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
+          <t>Cap. 4, § 4.3 (r. 85): «il secondo “vortice” diegetico della bettola della Zamira, collocato in un non meglio precisato luogo della campagna dei Castelli», fra i luoghi inventati; r. 93: «la bettola della Zamira risiede ai Due Santi».</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2461,7 +2469,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S-monte_circeo</t>
+          <t>S-montagne_degli_equi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2471,7 +2479,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_circeo</t>
+          <t>narrativeplace/montagne_degli_equi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2501,7 +2509,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
+          <t>Descrizione del censimento: «Montagne appartenenti allo storico popolo degli Equi».</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2528,7 +2536,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S-monte_nuncupale</t>
+          <t>S-monte_circeo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2538,17 +2546,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>narrativeplace/monte_nuncupale</t>
+          <t>narrativeplace/monte_circeo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2558,20 +2566,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>173</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
+          <t>Descrizione del censimento: «Monte tirrenico, nel Lazio».</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2581,7 +2586,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-monte_nuncupale-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2598,7 +2603,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S-monte_nuncupale-2</t>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2613,7 +2618,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2623,7 +2628,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2636,27 +2641,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Rilievo senza riscontro reale, posto dal testo nell’orizzonte dei Colli Albani: “da Rocca Orsina al Monte Nuncupale, su” (QPa 173). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>S-monte_nuncupale</t>
+          <t>Monte senza corrispondenza con un rilievo attestato; l'autore lo immagina a chiusura dell'orizzonte dei Colli Albani ("da Rocca Orsina al Monte Nuncupale, su", QPa 173).</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-monte_nuncupale-2 (D-090).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S-orto_vigna_due_santi</t>
+          <t>S-monte_nuncupale-2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>narrativeplace/orto_vigna_due_santi</t>
+          <t>narrativeplace/monte_nuncupale</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2693,18 +2693,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>173</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2713,17 +2716,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
+          <t>Rilievo senza riscontro reale, posto dal testo nell’orizzonte dei Colli Albani: “da Rocca Orsina al Monte Nuncupale, su” (QPa 173). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>S-monte_nuncupale</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2740,7 +2748,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S-palazzo_219</t>
+          <t>S-orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2750,12 +2758,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_219</t>
+          <t>narrativeplace/orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2780,7 +2788,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
+          <t>Parte di laboratorio_zamira nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Luogo non precisato simile a un orto o una vigna, di fronte al laboratorio della Zamira, al lato opposto della via Appia».</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2807,7 +2815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S-palazzo_del_mappamondo</t>
+          <t>S-palazzo_219</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2817,7 +2825,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_219</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2827,7 +2835,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2837,11 +2845,8 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>537</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2850,7 +2855,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
+          <t>Statuto Transformed confermato da LS (D-035, 9/10/2026). Cap. 4, tab. 4.2 (r. 273): «Palazzo al 219» come caso generatore di R07; DATA_CHECKS DC-08: edificio in una via reale, Transformed salvo diversa evidenza. Varianti 119 → 219 (QPL 285, 293 / QPa 16, 25) in fase 2 (T-41).</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2860,12 +2865,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2877,7 +2882,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S-palazzo_simonetti</t>
+          <t>S-palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2887,7 +2892,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2897,21 +2902,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2920,12 +2925,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>C-palazzo_simonetti</t>
+          <t>Palazzo Venezia, sede di Mussolini, indicato per antonomasia dalla Sala del Mappamondo e deformato in "Mappamonno": referente reale, nome trasformato.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S-passaggio_livello_casal_bruciato</t>
+          <t>S-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2982,8 +2982,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>78</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2992,7 +2995,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Palazzo reale (Simonetti o De Carolis) in via Lata, che QPa 177 colloca in via Lanza, dove non esiste: trasformazione per rilocazione (D-036). Cap. 4, § 4.2 (r. 45): «la stampa del 1957 colloca in via Lanza – abbinamento privo di riscontro reale per l'edificio […] –, laddove il dattiloscritto registrava correttamente via Lata».</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3007,7 +3015,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3019,7 +3027,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S-pensione_burgess</t>
+          <t>S-passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3029,12 +3037,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>narrativeplace/pensione_burgess</t>
+          <t>narrativeplace/passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3059,7 +3067,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
+          <t>Parte di casello_km_20_25 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3086,7 +3094,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S-piani_alti_219</t>
+          <t>S-pensione_burgess</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3096,12 +3104,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>narrativeplace/piani_alti_219</t>
+          <t>narrativeplace/pensione_burgess</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3121,12 +3129,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Descrizione del censimento: «Albergo immaginario, possibile deformazione di Pensione Villa Borghese, via Sgambati 4, vicino Porta Pinciana».</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Validata da LS (10/10/2026, D-078). Superata dalla lettura S-pensione_burgess-2 (D-092).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3153,7 +3161,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S-piccarozzi</t>
+          <t>S-pensione_burgess-2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3163,27 +3171,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>narrativeplace/piccarozzi</t>
+          <t>narrativeplace/pensione_burgess</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>22, 574–575</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3193,22 +3206,27 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
+          <t>Pensione senza referente identificato: il nome varia attraverso più lingue (Bergèss, Bergesse, Burgess) e nella forma esatta evoca l'archeologo Richard Burgess, in coerenza con il cognome di Diomede Lanciani (Terzoli 2015, pp. 22, 574–575). Invenzione collocata a Roma.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>S-pensione_burgess</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-092).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3220,7 +3238,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S-ponte_di_santa_fumia</t>
+          <t>S-piani_alti_219</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3230,7 +3248,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_di_santa_fumia</t>
+          <t>narrativeplace/piani_alti_219</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3250,12 +3268,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3265,7 +3278,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3275,12 +3288,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3292,7 +3305,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S-ponte_divino_amore</t>
+          <t>S-piccarozzi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3302,7 +3315,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>narrativeplace/ponte_divino_amore</t>
+          <t>narrativeplace/piccarozzi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3332,7 +3345,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
+          <t>Descrizione del censimento: «Bar in galleria colonna».</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3359,7 +3372,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S-porta_borgo_marino</t>
+          <t>S-ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3369,7 +3382,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>narrativeplace/porta_borgo_marino</t>
+          <t>narrativeplace/ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3389,7 +3402,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3399,7 +3417,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
+          <t>Strada che dall'Anziate va verso Casal Bruciato, parallela alla strada di Falconara percorsa da Pestalozzi, e scavalca la ferrovia Roma–Velletri in località Ponte di Santa Fumia: planimetria e toponimi corrispondono a quelli delle cartine della Guida Touring 1925 (tra le pp. 736–737, cart. 4, e 758–759, cart. 1).</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3409,12 +3427,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3426,7 +3444,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S-pozzofondo</t>
+          <t>S-ponte_divino_amore</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3436,12 +3454,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>narrativeplace/pozzofondo</t>
+          <t>narrativeplace/ponte_divino_amore</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3466,7 +3484,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
+          <t>Descrizione del censimento: «Il «ponte» è il cavalcavia stradale della SP 91/b sulla ferrovia Roma–Velletri, oggi linea FL4. Non attraversa un corso d’acqua e non coincide con un ponte situato accanto al santuario.».</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3493,7 +3511,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S-robine_vecchie</t>
+          <t>S-porta_borgo_marino</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3503,7 +3521,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>narrativeplace/robine_vecchie</t>
+          <t>narrativeplace/porta_borgo_marino</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3523,11 +3541,8 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>491</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3536,7 +3551,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
+          <t>Descrizione del censimento: «Porta al confine del comune di Marino».</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3551,7 +3566,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3563,7 +3578,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S-roccafringoli</t>
+          <t>S-pozzofondo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3573,17 +3588,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>narrativeplace/roccafringoli</t>
+          <t>narrativeplace/pozzofondo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3593,20 +3608,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>107</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
+          <t>Descrizione del censimento: «località immaginaria, luogo d'origine di Clelia Farcioni».</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3616,7 +3628,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-roccafringoli-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3633,7 +3645,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S-roccafringoli-2</t>
+          <t>S-robine_vecchie</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3643,31 +3655,31 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>narrativeplace/roccafringoli</t>
+          <t>narrativeplace/robine_vecchie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>107</v>
+        <v>491</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3676,27 +3688,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Paese senza riscontro reale, collocato dal testo entro una geografia nota: “su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio” (QPa 107). Luogo inventato secondo Reuschel e Hurni (2011): “an invented setting within familiar geographical reality”.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>S-roccafringoli</t>
+          <t>Cap. 4, § 4.3 (r. 83): «Robine Vecchie», che entrambe le edizioni conservano a testo (RR II, p. 154; QPa 169), «non registrato nelle carte topografiche»: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; r. 93: situata «tra le Frattocchie e i Due Santi» (ancoraggio relazionale).</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3708,7 +3715,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S-sacello_responsale</t>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3718,12 +3725,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>narrativeplace/sacello_responsale</t>
+          <t>narrativeplace/roccafringoli</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3733,7 +3740,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3742,26 +3749,26 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Parte di casuccia_zamira (Is_Part_Of), oltre l'uscio con catenaccio della sala di consultazione, cioè della cantina (QPa 165): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Paese senza corrispondenza con un luogo attestato; l'autore lo immagina sui monti presso Palestrina ("a monte Manno, quasi", QPa 107).</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Luogo entrato con la soglia di censimento (D-091).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-roccafringoli-2 (D-090).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3778,7 +3785,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S-scale</t>
+          <t>S-roccafringoli-2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3788,28 +3795,31 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>narrativeplace/scale</t>
+          <t>narrativeplace/roccafringoli</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>107</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3818,17 +3828,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
+          <t>Paese senza riscontro reale, collocato dal testo entro una geografia nota: “su su in cima ai monti, a monte Manno, quasi, che da Palestrina ce se va cor ciuccio” (QPa 107). Luogo inventato secondo Reuschel e Hurni (2011): “an invented setting within familiar geographical reality”.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>S-roccafringoli</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3845,7 +3860,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S-scala_a</t>
+          <t>S-sacello_responsale</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3855,28 +3870,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_a</t>
+          <t>narrativeplace/sacello_responsale</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>165</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3885,17 +3903,17 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
+          <t>Parte di casuccia_zamira (Is_Part_Of), oltre l'uscio con catenaccio della sala di consultazione, cioè della cantina (QPa 165): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Luogo entrato con la soglia di censimento (D-091).</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3912,7 +3930,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S-scala_b</t>
+          <t>S-scale</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3922,7 +3940,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>narrativeplace/scala_b</t>
+          <t>narrativeplace/scale</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3952,7 +3970,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219».</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3979,7 +3997,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S-scerpure</t>
+          <t>S-scala_a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3989,17 +4007,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>narrativeplace/scerpure</t>
+          <t>narrativeplace/scala_a</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>chora:Imagined</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4009,20 +4027,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>141</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165): «lungo la scala A, al terzo piano, i coniugi Balducci risiedono esattamente «in faccia» alla contessa Menegazzi (QP 16)». Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4032,7 +4047,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-scerpure-2 (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4049,7 +4064,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S-scerpure-2</t>
+          <t>S-scala_b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4059,31 +4074,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>narrativeplace/scerpure</t>
+          <t>narrativeplace/scala_b</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>141</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4092,22 +4104,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Città senza riscontro reale, collocata dal testo “sulle rive, più o meno, del nativo Brahmaputra” (QPa 141). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>S-scerpure</t>
+          <t>Interno del palazzo di via Merulana 219 (Is_Part_Of palazzo_219): Cap. 4, § 4.6 (r. 165), il dilemma se sia «meglio salire la scala A o la scala B» (Amigoni 1995, pp. 36–40). Lo statuto segue quello del palazzo.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Revisione critica (D-090).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4124,7 +4131,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S-stazione_carabinieri_castello</t>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4134,37 +4141,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_carabinieri_castello</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Imagined</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>141</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
+          <t>Città senza corrispondenza con un luogo attestato; l'autore la immagina "sulle rive, più o meno, del nativo Brahmaputra" (QPa 141).</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4174,7 +4184,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-scerpure-2 (D-090).</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4191,7 +4201,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S-stazione_pavona</t>
+          <t>S-scerpure-2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4201,28 +4211,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>narrativeplace/stazione_pavona</t>
+          <t>narrativeplace/scerpure</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>chora:Transformed</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>141</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4231,17 +4244,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
+          <t>Città senza riscontro reale, collocata dal testo “sulle rive, più o meno, del nativo Brahmaputra” (QPa 141). Luogo inventato in una geografia nota (Reuschel e Hurni 2011).</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>S-scerpure</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Revisione critica (D-090).</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4258,7 +4276,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S-strada_di_campagna_celio</t>
+          <t>S-stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4268,7 +4286,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>narrativeplace/strada_di_campagna_celio</t>
+          <t>narrativeplace/stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4298,7 +4316,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
+          <t>Parte di castello nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4325,7 +4343,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S-tenenza_carabinieri_marino</t>
+          <t>S-stazione_pavona</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4335,7 +4353,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
+          <t>narrativeplace/stazione_pavona</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4345,7 +4363,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4355,12 +4373,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>293–294</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4370,7 +4383,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
+          <t>Descrizione del censimento: «Stazione del paese di Pavona, non meglio identificata».</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4380,12 +4393,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4397,7 +4410,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S-terzo_piano_219</t>
+          <t>S-strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4407,7 +4420,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>narrativeplace/terzo_piano_219</t>
+          <t>narrativeplace/strada_di_campagna_celio</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4437,7 +4450,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
+          <t>Descrizione del censimento: «Strada non meglio qualificata nel quartiere del Celio».</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4464,7 +4477,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S-tor_di_gheppio</t>
+          <t>S-tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4474,31 +4487,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>manzotti</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>679</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>293–294</t>
+        </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4507,7 +4522,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
+          <t>Cap. 4, § 4.3 (r. 85): «Di segno spiccatamente trasformato appare […] la «Tenenza dei Carabinieri di Marino»: come ricorda Emilio Manzotti, negli anni Venti Marino ospitava unicamente una “stazione” dei carabinieri dipendente dalla tenenza di Frascati», sede definita «una re-invenzione romantica».</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4517,12 +4532,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Validata da LS (10/10/2026, D-078).</t>
+          <t>Autore della lettura Manzotti, codificatore LS (D-087).</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4534,7 +4549,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S-via_delle_oche</t>
+          <t>S-terzo_piano_219</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4544,17 +4559,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>narrativeplace/via_delle_oche</t>
+          <t>narrativeplace/terzo_piano_219</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4564,11 +4579,8 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>22</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4577,7 +4589,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
+          <t>Parte di palazzo_219 nel censimento (Is_Part_Of): lo statuto segue quello del luogo di cui è parte. Descrizione del censimento: «Interno del palazzo in via Merulana 219, terzo piano».</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4587,7 +4599,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Motivazione riscritta da LS (10/10/2026, D-079).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4604,7 +4616,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S-villino_lungotevere</t>
+          <t>S-tor_di_gheppio</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4614,7 +4626,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>narrativeplace/villino_lungotevere</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4624,7 +4636,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4632,6 +4644,14 @@
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>679</v>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>si</t>
@@ -4639,7 +4659,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
+          <t>Cap. 4, § 4.3 (r. 85): tra i luoghi inventati dotati di «una precisa collocazione topografica», «Tor di Gheppio (paese d'origine dell'Assunta Crocchiapani)»; § 4.4 (r. 115): «toponimo di finzione incastonato nella campagna dei Castelli, e dunque ascrivibile alla categoria dei luoghi inventati» (cfr. Cortellessa 2023, p. 679).</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4649,7 +4669,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
+          <t>Validata da LS (10/10/2026, D-078).</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4666,27 +4686,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>U-0001</t>
+          <t>S-via_delle_oche</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>narrativeplace/via_delle_oche</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>chora:Confusion</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4696,17 +4716,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>268–269</t>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>22</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
+          <t>Via reale di Bologna, nota via di prostituzione, che il testo traslata a Milano (QPa 22; U-0009).</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4716,152 +4739,134 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione riscritta da LS (10/10/2026, D-079). Superata dalla lettura S-via_delle_oche-2 (D-092).</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>documentaria</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>U-0002</t>
+          <t>S-via_delle_oche-2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>narrativeplace/castello</t>
+          <t>narrativeplace/via_delle_oche</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>annotator/lorenzo_sabatino</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>293</v>
+        <v>77</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
+          <t>Via storica di Milano, oggi via Bernardino Zenale (Terzoli 2015, p. 77; L'Adalgisa, p. 564, n. 53).</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>S-via_delle_oche</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Revisione critica (D-092).</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>identificazione</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>costruttiva</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>ref_00651</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>U-0003</t>
+          <t>S-villino_lungotevere</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/villino_lungotevere</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>chora:ContestedIdentification</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>78</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Villino senza riscontro, collocato dal testo sul Lungotevere.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4871,39 +4876,24 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
+          <t>Motivazione nuova di LS (10/10/2026, D-080).</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>identificazione</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>U-0004</t>
+          <t>U-0001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4913,35 +4903,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:Confusion</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>agent/manzotti</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>annotator/lorenzo_sabatino</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>491</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>268–269</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
+          <t>La topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»; TCI e testo tra le due ferrovie, IGM a ovest della Roma–Napoli. Discrepanza fra testo e repertorio, non corretta (D-037).</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4966,7 +4958,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>geometria</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4978,7 +4970,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>U-0005</t>
+          <t>U-0002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4988,12 +4980,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_edicola_due_santi</t>
+          <t>narrativeplace/castello</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5012,11 +5004,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
+          <t>Due identificazioni concorrenti della «stazione di Castello» (QPa 279): Castel Gandolfo (lettura immediata, A-0001) e Castel Savello (Manzotti, A-0002, adottata). Cap. 4, § 4.4 (r. 107).</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5031,7 +5023,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5041,19 +5033,24 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>geometria</t>
+          <t>identificazione</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>costruttiva</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>ref_00651</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>U-0006</t>
+          <t>U-0003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5063,17 +5060,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>narrativeplace/monti_ernici</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>chora:NonSpecificity</t>
+          <t>chora:ContestedIdentification</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5083,15 +5080,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
+          <t>Quale palazzo reale sta dietro il «palazzo Simonetti» in via Lanza (QPa 177): il palazzo Simonetti / De Carolis in via Lata del dattiloscritto (Pinotti) o il palazzo Odescalchi Simonetti di via Vittoria Colonna (Terzoli, cit. ivi). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5126,14 +5123,14 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ref_00541</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>U-0007</t>
+          <t>U-0004</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5143,17 +5140,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reference/ref_00523</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>chora:Oversight</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5163,15 +5160,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>254</v>
+        <v>491</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
+          <t>«Robine Vecchie» (QPa 169) non è registrato nelle carte topografiche: refuso per «Robinie vecchie» o «Rovine vecchie», oppure «ironico abbassamento» delle Rovine della zona; Pinotti conserva la lezione. Cap. 4, § 4.3 (r. 83).</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5208,7 +5205,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>U-0008</t>
+          <t>U-0005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5218,17 +5215,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>narrativeplace/direttissima_roma_napoli</t>
+          <t>gazetteer/gaz_edicola_due_santi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>chora:Anachronism</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>agent/manzotti</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5242,11 +5239,11 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
+          <t>Il tabernacolo ha traccia nella piantina dei Castelli del Touring (Manzotti), ma il progetto non dispone di una coordinata: la posizione deriva da Due Santi con uno scarto dichiarato di circa 40 m (D-031); il volume TCI citato è da verificare (DC-03).</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5261,7 +5258,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5271,69 +5268,57 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>identificazione</t>
+          <t>geometria</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>ref_00535|ref_00635|ref_00703</t>
+          <t>costruttiva</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>U-0006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/monti_ernici</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>chora:NonSpecificity</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>103–104</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>290</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
+          <t>«d'in vetta al crinale degli Ernici o dei Simbruini» (QPa 215): identificazione per disgiunzione, non risolta dal testo (WO T-16; Cap. 4, § 4.4).</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5343,7 +5328,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5354,58 +5339,66 @@
       <c r="O70" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>ref_00541</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>U-0007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>reference/ref_00523</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:Oversight</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>254</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
+          <t>«Càrsoli» (QPa 210) in luogo della grafia corretta Carsòli, «frutto verosimilmente di un'attrazione analogica con la vicina Àrsoli» (Cap. 4, § 4.4, r. 111). Discrepanza di forma registrata, non corretta.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5415,7 +5408,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5428,59 +5421,59 @@
           <t>bozza</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>documentaria</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>U-0008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:Anachronism</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>agent/manzotti</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>annotator/lorenzo_sabatino</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>669</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>270</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
+          <t>La direttissima Roma–Napoli fu ultimata e inaugurata dopo gli eventi narrati (marzo 1927) (Cap. 4, § 4.4, r. 111). Anacronismo registrato, non corretto.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5490,7 +5483,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Bozza T-34 (D-047): classificazione da validare in REVIEW_2</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5501,13 +5494,28 @@
       <c r="O72" t="inlineStr">
         <is>
           <t>bozza</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>identificazione</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>ref_00535|ref_00635|ref_00703</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5517,7 +5525,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5552,7 +5560,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5579,7 +5587,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>M-0002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5589,7 +5597,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5624,7 +5632,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5656,7 +5664,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>M-0003</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5666,7 +5674,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00144</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5699,7 +5707,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5726,27 +5734,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P-0001</t>
+          <t>M-0004</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>partition</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>partition/citta_campagna</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>zone/roma_citta|zone/campagna_romana</t>
+          <t>chora:AuthorMemory</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>perosa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5756,22 +5764,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
+          <t>perosa_2023a</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>§ 4.1, § 4.6 (R20)</t>
+          <t>103–104</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5781,7 +5789,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5798,27 +5806,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C-edicola_due_santi</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>lugnani</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5828,7 +5836,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>perosa_2023a</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>104, n. 97</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5838,12 +5851,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5853,34 +5871,39 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C-palazzo_simonetti</t>
+          <t>M-0006</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>reference/ref_00145</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>chora:AuthorMemory|chora:CharacterMemory</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>cortellessa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5890,8 +5913,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
+          <t>cortellessa_2023</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>669</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5900,44 +5926,49 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
+          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
+          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C-casal_bruciato</t>
+          <t>P-0001</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>partition</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>partition/citta_campagna</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casal_bruciato</t>
+          <t>zone/roma_citta|zone/campagna_romana</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5952,54 +5983,64 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
+          <t>sabatino_cap4</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>§ 4.1, § 4.6 (R20)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
+          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
+          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>I-casal_bruciato</t>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6014,37 +6055,27 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>C-casal_bruciato</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6056,27 +6087,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V-0001</t>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>reference/ref_00724</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6086,67 +6117,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>241</v>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
+          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V-0002</t>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>reference/ref_00436</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>reference/ref_00725</t>
+          <t>gazetteer/gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6156,67 +6179,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>78</v>
+          <t>censimento_gaddatlas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
+          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V-0003a</t>
+          <t>I-casal_bruciato</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>reference/ref_00007</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6226,17 +6241,27 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
+          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6244,31 +6269,21 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V-0003b</t>
+          <t>V-0001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6278,17 +6293,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>reference/ref_00036</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>reference/ref_00724</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6298,17 +6313,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>241</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
+          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6318,7 +6331,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6340,7 +6353,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V-0004a</t>
+          <t>V-0002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6350,17 +6363,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>reference/ref_00008</t>
+          <t>reference/ref_00436</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>reference/ref_00725</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6370,17 +6383,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>78</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
+          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6390,7 +6401,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6412,7 +6423,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V-0004b</t>
+          <t>V-0003a</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6422,12 +6433,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>reference/ref_00038</t>
+          <t>reference/ref_00007</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6452,7 +6463,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
+          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6462,7 +6473,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6484,27 +6495,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R-0001</t>
+          <t>V-0003b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>reference/ref_00036</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6514,20 +6525,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>297</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6537,7 +6545,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6547,34 +6555,39 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R-0002</t>
+          <t>V-0004a</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+          <t>reference/ref_00008</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6584,20 +6597,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>169</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6607,7 +6617,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6617,34 +6627,39 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R-0003</t>
+          <t>V-0004b</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>route/tragitto_tenenza_due_santi</t>
+          <t>reference/ref_00038</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6654,22 +6669,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>matt_pinotti_2022</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>208–215</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6677,6 +6687,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>prova testuale</t>
@@ -6684,14 +6699,19 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R-0004</t>
+          <t>R-0001</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6701,7 +6721,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6725,7 +6745,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6734,7 +6754,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6744,7 +6764,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6761,7 +6781,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R-0005</t>
+          <t>R-0002</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6771,12 +6791,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>route/tragitto_viminale_merulana</t>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6795,7 +6815,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6804,12 +6824,17 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6826,7 +6851,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R-0006</t>
+          <t>R-0003</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6836,12 +6861,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>route/tragitto_appia_falcognana</t>
+          <t>route/tragitto_tenenza_due_santi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6859,8 +6884,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H92" t="n">
-        <v>238</v>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>208–215</t>
+        </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6869,17 +6896,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6896,7 +6918,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R-0007</t>
+          <t>R-0004</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6906,7 +6928,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>route/tragitto_agostino_aquiro</t>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6930,7 +6952,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6939,7 +6961,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6949,7 +6971,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6966,7 +6988,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R-0008</t>
+          <t>R-0005</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6976,7 +6998,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>route/tragitto_cecchina_anziate</t>
+          <t>route/tragitto_viminale_merulana</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7000,7 +7022,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7009,17 +7031,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7036,7 +7053,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R-0009</t>
+          <t>R-0006</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7046,12 +7063,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>route/tragitto_colonna_treccani</t>
+          <t>route/tragitto_appia_falcognana</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7070,7 +7087,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>40</v>
+        <v>238</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7079,7 +7096,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7089,7 +7106,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7106,7 +7123,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R-0010</t>
+          <t>R-0007</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7116,12 +7133,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>route/tragitto_frattocchie_ciampino</t>
+          <t>route/tragitto_agostino_aquiro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7140,7 +7157,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7149,7 +7166,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7159,7 +7176,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7176,7 +7193,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R-0011</t>
+          <t>R-0008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7186,7 +7203,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>route/tragitto_monti_piazza_esedra</t>
+          <t>route/tragitto_cecchina_anziate</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7210,7 +7227,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7219,7 +7236,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7229,7 +7246,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7246,7 +7263,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R-0012</t>
+          <t>R-0009</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7256,7 +7273,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+          <t>route/tragitto_colonna_treccani</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7280,7 +7297,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7289,7 +7306,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7316,7 +7333,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R-0013</t>
+          <t>R-0010</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7326,12 +7343,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>route/tragitto_chiara_pantheon</t>
+          <t>route/tragitto_frattocchie_ciampino</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7350,7 +7367,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7359,7 +7376,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7369,7 +7386,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7386,7 +7403,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R-0014</t>
+          <t>R-0011</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7396,7 +7413,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>route/tragitto_duesanti_frattocchie</t>
+          <t>route/tragitto_monti_piazza_esedra</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7420,7 +7437,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7429,12 +7446,17 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7451,7 +7473,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R-0015</t>
+          <t>R-0012</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7461,7 +7483,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7484,10 +7506,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>139–140</t>
-        </is>
+      <c r="H101" t="n">
+        <v>173</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7496,12 +7516,17 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7518,7 +7543,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R-0016</t>
+          <t>R-0013</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7528,12 +7553,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_albano_laziale</t>
+          <t>route/tragitto_chiara_pantheon</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>chora:DirectionalRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7552,7 +7577,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>278</v>
+        <v>41</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -7561,7 +7586,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7571,7 +7596,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7588,7 +7613,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R-0017</t>
+          <t>R-0014</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7598,7 +7623,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_due_santi</t>
+          <t>route/tragitto_duesanti_frattocchie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7622,7 +7647,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>206</v>
+        <v>56</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -7631,7 +7656,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7653,7 +7678,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R-0018</t>
+          <t>R-0015</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7663,7 +7688,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_santo_stefano</t>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7686,8 +7711,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H104" t="n">
-        <v>153</v>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -7696,17 +7723,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7723,7 +7745,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R-0019</t>
+          <t>R-0016</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7733,12 +7755,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>route/tragitto_merulana_policlinico</t>
+          <t>route/tragitto_marino_albano_laziale</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:DirectionalRoute</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7757,7 +7779,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>93</v>
+        <v>278</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7766,7 +7788,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7776,7 +7798,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7793,7 +7815,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R-0020</t>
+          <t>R-0017</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7803,12 +7825,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>route/tragitto_marino_due_santi</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chora:DreamedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7827,7 +7849,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -7836,17 +7858,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7863,7 +7880,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>R-0021</t>
+          <t>R-0018</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7873,12 +7890,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+          <t>route/tragitto_marino_santo_stefano</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7897,7 +7914,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>237</v>
+        <v>153</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -7906,7 +7923,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7916,7 +7933,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7933,27 +7950,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>R-0019</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_merulana_policlinico</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>geometry/L-0001</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7963,13 +7980,11 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>93</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -7978,7 +7993,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7988,44 +8003,44 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Posizione adottata (D-037).</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>R-0020</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>geometry/L-0002</t>
+          <t>chora:DreamedRoute</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8035,22 +8050,20 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>212</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8060,39 +8073,39 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Posizione alternativa (D-037).</t>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>validata</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>U-0009</t>
+          <t>R-0021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_bologna</t>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8105,71 +8118,69 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>237</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072).</t>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>geometria</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>ref_00028</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N-0001</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>geometry/L-0001</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8179,79 +8190,69 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>491–492</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Posizione adottata (D-037).</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N-0002</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>geometry/L-0002</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8261,12 +8262,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>491–492</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8276,64 +8277,54 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Posizione alternativa (D-037).</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>refuso per «Rovine vecchie»</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N-0003</t>
+          <t>U-0009</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>gazetteer/gaz_bologna</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>chora:IronicLowering</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8341,16 +8332,6 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
-      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>no</t>
@@ -8358,7 +8339,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8368,12 +8349,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072). Superata: la via è milanese, oggi via Bernardino Zenale (Terzoli 2015, p. 77); la discrepanza non sussiste (D-092).</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8381,26 +8362,31 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>«ironico abbassamento»</t>
+          <t>ref_00028</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>K-0001</t>
+          <t>N-0001</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8408,9 +8394,14 @@
           <t>reference/ref_00403</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8420,17 +8411,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>italia_2020</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>102–103</t>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8456,18 +8452,23 @@
       <c r="R114" t="inlineStr">
         <is>
           <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>K-0002</t>
+          <t>N-0002</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8475,9 +8476,14 @@
           <t>reference/ref_00403</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>chora:TypoHypothesis</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8487,15 +8493,22 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>169</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8505,12 +8518,12 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Risponde a K-0001 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8523,31 +8536,31 @@
           <t>ref_00403</t>
         </is>
       </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>K-0001</t>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>U-0010</t>
+          <t>N-0003</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>reference/ref_00404</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>chora:IronicLowering</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8565,12 +8578,19 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H116" t="n">
-        <v>492</v>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8593,31 +8613,21 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ref_00404</t>
+          <t>ref_00403</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>«toponimi non segnalati nelle carte topografiche»</t>
+          <t>«ironico abbassamento»</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>K-0003</t>
+          <t>K-0001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8627,7 +8637,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8645,12 +8655,14 @@
           <t>italia_2020</t>
         </is>
       </c>
-      <c r="H117" t="n">
-        <v>101</v>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>102–103</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8675,34 +8687,29 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>ref_00588</t>
+          <t>ref_00403</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V-0005</t>
+          <t>K-0002</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>reference/ref_00132</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>reference/ref_00734</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8712,15 +8719,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8730,7 +8737,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Risponde a K-0001 (D-087).</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8745,34 +8752,34 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ref_00132</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>K-0001</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>I-0001</t>
+          <t>U-0010</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>narrativeplace/ca_francesi</t>
+          <t>reference/ref_00404</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8791,16 +8798,11 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>512</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>492</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8823,36 +8825,46 @@
           <t>validata</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>ref_00404</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>«località nei pressi della stazione delle Frattocchie»</t>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>I-0002</t>
+          <t>K-0003</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_ser_paolo</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8862,20 +8874,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>italia_2020</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>512</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>101</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8898,31 +8905,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>ref_00588</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>I-0003</t>
+          <t>V-0005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>narrativeplace/fontana_di_papa</t>
+          <t>reference/ref_00132</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>reference/ref_00734</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8941,16 +8948,11 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>658</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>142</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8965,7 +8967,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8975,29 +8977,34 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ref_00529</t>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>T-0021</t>
+          <t>I-0001</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>narrativeplace/ca_francesi</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9015,14 +9022,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>658 (Bertarelli 1924, p. 561)</t>
+      <c r="H122" t="n">
+        <v>512</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9037,19 +9047,24 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>I-0004</t>
+          <t>I-0002</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9059,12 +9074,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>narrativeplace/osteriuccia_bivio</t>
+          <t>narrativeplace/tor_ser_paolo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9083,16 +9098,16 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>776</v>
+        <v>512</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9115,36 +9130,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>ref_00736</t>
-        </is>
-      </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>T-0022</t>
+          <t>I-0003</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>narrativeplace/fontana_di_papa</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9162,14 +9172,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+      <c r="H124" t="n">
+        <v>658</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9184,19 +9197,24 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>ref_00529</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>T-0021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9206,12 +9224,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ciampino</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9231,12 +9249,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>658 (Bertarelli 1924, p. 561)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9263,22 +9281,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>I-0004</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9296,14 +9314,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+      <c r="H126" t="n">
+        <v>776</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9318,19 +9339,29 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9340,7 +9371,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_frattocchie</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9365,12 +9396,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9397,7 +9428,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>T-0004</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9407,7 +9438,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_torraccio</t>
+          <t>gazetteer/gaz_ciampino</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9437,7 +9468,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9464,7 +9495,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>T-0005</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9474,7 +9505,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_due_santi</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9504,7 +9535,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9531,7 +9562,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>T-0006</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9541,7 +9572,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_frattocchie</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9571,7 +9602,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9598,7 +9629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>T-0004</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9608,7 +9639,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_torraccio</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9638,7 +9669,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9665,7 +9696,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0005</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9675,7 +9706,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_divino_amore</t>
+          <t>gazetteer/gaz_due_santi</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9705,7 +9736,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9732,7 +9763,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0006</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9742,7 +9773,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pavona</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9772,7 +9803,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9799,7 +9830,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>T-0010</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9809,7 +9840,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_solforata</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9839,7 +9870,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9866,7 +9897,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9876,7 +9907,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pratica_di_mare</t>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9906,7 +9937,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9933,7 +9964,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T-0012</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9943,7 +9974,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>gazetteer/gaz_pavona</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9973,7 +10004,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10000,7 +10031,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T-0013</t>
+          <t>T-0010</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10010,7 +10041,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_falcognana</t>
+          <t>gazetteer/gaz_solforata</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10040,7 +10071,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10067,7 +10098,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T-0014</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10077,7 +10108,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_cecchina</t>
+          <t>gazetteer/gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10107,7 +10138,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10134,7 +10165,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>T-0015</t>
+          <t>T-0012</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10144,7 +10175,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_albano_laziale</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10174,7 +10205,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10201,7 +10232,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>T-0016</t>
+          <t>T-0013</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10211,7 +10242,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_zagarolo</t>
+          <t>gazetteer/gaz_falcognana</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10241,7 +10272,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10268,7 +10299,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>T-0017</t>
+          <t>T-0014</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10278,7 +10309,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_marino</t>
+          <t>gazetteer/gaz_cecchina</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10308,7 +10339,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10335,7 +10366,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>T-0018</t>
+          <t>T-0015</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10345,7 +10376,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ariccia</t>
+          <t>gazetteer/gaz_albano_laziale</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10375,7 +10406,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10402,7 +10433,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>T-0019</t>
+          <t>T-0016</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10412,7 +10443,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_santa_palomba</t>
+          <t>gazetteer/gaz_zagarolo</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10442,7 +10473,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10469,7 +10500,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>T-0020</t>
+          <t>T-0017</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10479,7 +10510,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_rocca_di_papa</t>
+          <t>gazetteer/gaz_marino</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10509,7 +10540,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10536,17 +10567,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>K-0004</t>
+          <t>T-0018</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>work/quer_pasticciaccio</t>
+          <t>gazetteer/gaz_ariccia</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10566,12 +10602,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>418–419</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10586,24 +10622,19 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>T-0023</t>
+          <t>T-0019</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10613,12 +10644,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_santa_palomba</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10638,12 +10669,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10664,18 +10695,13 @@
       <c r="O146" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>T-0024</t>
+          <t>T-0020</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10685,7 +10711,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_rocca_di_papa</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -10710,12 +10736,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10742,7 +10768,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>K-0005</t>
+          <t>K-0004</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10752,7 +10778,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>work/quer_pasticciaccio</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10772,12 +10798,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>418–419</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10792,7 +10818,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -10800,26 +10826,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>ref_00698</t>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>K-0006</t>
+          <t>T-0023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10837,12 +10868,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H149" t="n">
-        <v>911</v>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10857,7 +10890,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10867,24 +10900,29 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>«immaginario»</t>
+          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>K-0007</t>
+          <t>T-0024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10902,12 +10940,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H150" t="n">
-        <v>911</v>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10922,24 +10962,19 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>«immaginaria»</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>K-0008</t>
+          <t>K-0005</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10949,12 +10984,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10964,17 +10999,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>268–269</t>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10989,7 +11024,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10999,29 +11034,24 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ref_00534</t>
+          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>T-0025</t>
+          <t>K-0006</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_monti_ernici</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1924</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11039,14 +11069,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
-        </is>
+      <c r="H152" t="n">
+        <v>911</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11061,39 +11089,39 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>I-0005</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11103,22 +11131,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>239–240</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>911</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11143,14 +11164,14 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>«re-invenzione romantica»</t>
+          <t>«immaginaria»</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>K-0009</t>
+          <t>K-0008</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11160,7 +11181,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>narrativeplace/marino</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11180,12 +11201,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>293–294</t>
+          <t>268–269</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11206,33 +11227,38 @@
       <c r="O154" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>ref_00534</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>N-0004</t>
+          <t>T-0025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
+          <t>gazetteer/gaz_monti_ernici</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>chora:Paraetymology</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11242,15 +11268,17 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>273</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11265,39 +11293,34 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>ref_00538|ref_00539</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>K-0010</t>
+          <t>I-0005</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>reference/ref_00539</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11315,12 +11338,19 @@
           <t>manzotti_2010</t>
         </is>
       </c>
-      <c r="H156" t="n">
-        <v>276</v>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>239–240</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11343,36 +11373,31 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>ref_00539</t>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>I-0006</t>
+          <t>K-0009</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+          <t>narrativeplace/marino</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11382,22 +11407,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>535–536</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>293–294</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11418,38 +11438,33 @@
       <c r="O157" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>I-0007</t>
+          <t>N-0004</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>chora:Paraetymology</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11459,20 +11474,15 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>536</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>273</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11482,7 +11492,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11497,39 +11507,34 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>ref_00435</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>I-0008</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>reference/ref_00539</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11539,20 +11544,15 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>78</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>276</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -11577,29 +11577,29 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>ref_00435|ref_00725</t>
+          <t>ref_00539</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>N-0005</t>
+          <t>I-0006</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>reference/ref_00437</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>chora:Synecdoche</t>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -11617,12 +11617,19 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H160" t="n">
-        <v>537</v>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>535–536</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11647,19 +11654,14 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>I-0009</t>
+          <t>I-0007</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11669,17 +11671,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11693,16 +11695,16 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11712,7 +11714,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11727,14 +11729,19 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>ref_00437</t>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>I-0010</t>
+          <t>I-0008</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11744,17 +11751,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_chigi</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11764,11 +11771,11 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -11777,7 +11784,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -11787,12 +11794,12 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11802,34 +11809,29 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>I-0011</t>
+          <t>N-0005</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>narrativeplace/vite</t>
+          <t>reference/ref_00437</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_via_della_vite</t>
+          <t>chora:Synecdoche</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11848,16 +11850,11 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>616</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+        <v>537</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11882,39 +11879,39 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>V-0006</t>
+          <t>I-0009</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>reference/ref_00493</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>reference/ref_00735</t>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -11924,15 +11921,20 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>78</v>
+        <v>537</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11947,7 +11949,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -11957,44 +11959,34 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>«da Faraja»</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>ref_00437</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>N-0006</t>
+          <t>I-0010</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>chora:OnomasticPun</t>
+          <t>gazetteer/gaz_palazzo_chigi</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -12007,14 +11999,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
+      <c r="H165" t="n">
+        <v>537</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12024,7 +12019,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12035,76 +12030,677 @@
       <c r="O165" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>I-0011</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>narrativeplace/vite</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_via_della_vite</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>616</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>V-0006</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>reference/ref_00493</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>reference/ref_00735</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>pinotti</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>78</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>prova testuale</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>N-0006</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>narrativeplace/ditta_ciurlani</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>chora:OnomasticPun</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Loci critici (D-087).</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>S-osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>chora:Transformed</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
         <is>
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H166" t="n">
+      <c r="H169" t="n">
         <v>776</v>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="J169" t="inlineStr">
         <is>
           <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>Motivazione di LS (10/10/2026, D-087).</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
+      <c r="N169" t="inlineStr">
         <is>
           <t>prova referenziale</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>validata</t>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>I-0012</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>679</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Castel Porcano è la deformazione di Castel Porziano, allora tenuta reale di caccia a sud di Roma (cfr. pp. 633–634).</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Fase 3d (D-092).</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>I-0013</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>narrativeplace/via_delle_oche</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_via_delle_oche_milano</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>77</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Via delle Oche è oggi via Bernardino Zenale, fra via San Vittore e corso Magenta, presso Santa Maria delle Grazie; il commento rinvia all'Adalgisa, p. 564, n. 53 («Via di Okk»).</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Fase 3d (D-092).</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>prova referenziale</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>I-0014</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>narrativeplace/rocca_orsina</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_rocca_orsina</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>507–508</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Rocca Orsina è la Rocca Orsini di Marino, di cui il palazzo Colonna occupa il sedime; Gadda la nomina anche in Fuga a Tor di Nona (RD 981).</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Fase 3d (D-092). Terzoli data la rocca alla fine del XV secolo (Paolo Orsini); altre fonti la danno al XIII–XIV: la datazione non incide sull'identificazione.</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>I-0015</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>narrativeplace/monte_nuncupale</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_campidoglio</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>507–508</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Ipotesi dubitativa del commento ("forse da identificare con il Campidoglio"); non adottata: il "su" del passo si accorda con l'orizzonte dei Colli Albani.</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Fase 3d (D-092).</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>forse da identificare con il Campidoglio</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>N-0007</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>naming</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>chora:Paraetymology</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>terzoli</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>679</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Gioco paraetimologico su Castel Porziano, con il rinvio a Circe e alla Guida Touring 1924, p. 569 («già Porciliano»); vale anche per «Castel Porcino».</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Fase 3d (D-092).</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>lettura critica</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/Assertions.xlsx
+++ b/data/source/xlsx/Assertions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W174"/>
+  <dimension ref="A1:W168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5515,27 +5515,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>P-0001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>partition</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>partition/citta_campagna</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>zone/roma_citta|zone/campagna_romana</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5545,22 +5545,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
+          <t>sabatino_cap4</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>103–104</t>
+          <t>§ 4.1, § 4.6 (R20)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Dosso Faiti).</t>
+          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5587,27 +5587,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>C-edicola_due_santi</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/edicola_due_santi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>chora:Invented</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5617,12 +5617,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>104, n. 97</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5632,17 +5627,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Dosso Faiti).</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
+          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5652,39 +5642,34 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>C-palazzo_simonetti</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>reference/ref_00144</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>chora:Imported</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5694,11 +5679,8 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>669</v>
+          <t>censimento_gaddatlas</t>
+        </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5707,54 +5689,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Dosso Faiti).</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory</t>
+          <t>gazetteer/gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>perosa</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5764,12 +5741,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>103–104</t>
+          <t>censimento_gaddatlas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5779,54 +5751,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>«Gadda sembra infatti proiettare sul personaggio di Ingravallo una propria tessera autobiografica»: la memoria della morte del fratello Enrico e del lutto materno (QPa 61, Monte Cengio).</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
+          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>I-casal_bruciato</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>narrativeplace/casal_bruciato</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>chora:CharacterMemory</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>lugnani</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5836,22 +5803,27 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>perosa_2023a</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>104, n. 97</t>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>La «mamma» rinvia al «figlio e fante don Ciccio», e forse ai suoi fratelli caduti in guerra (QPa 61, Monte Cengio).</t>
+          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>C-casal_bruciato</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5859,51 +5831,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto. Lugnani 2001, cit. in Perosa 2023a, p. 104, n. 97.</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>bozza</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>lugnani_2001</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>V-0001</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>reference/ref_00145</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>chora:AuthorMemory|chora:CharacterMemory</t>
+          <t>reference/ref_00724</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>cortellessa</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5913,20 +5875,15 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>cortellessa_2023</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>669</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>241</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>La sequenza «sovrappone la memoria del personaggio, anzi la sovrimprime, a quella dell'autore» (QPa 61, Monte Cengio).</t>
+          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5936,44 +5893,49 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3: le tre letture convivono, nessuna è adottata dal progetto.</t>
+          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>P-0001</t>
+          <t>V-0002</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>partition</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>partition/citta_campagna</t>
+          <t>reference/ref_00436</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>zone/roma_citta|zone/campagna_romana</t>
+          <t>reference/ref_00725</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5983,22 +5945,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>sabatino_cap4</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>§ 4.1, § 4.6 (R20)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>78</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Partizione Roma città / campagna romana, lettura adottata dal progetto. Criterio: distanza dell'ancora primaria del luogo dal Campidoglio; città fino a 10 km (nei dati il primo luogo di campagna, Castel di Leva, è a 12,9 km; l'ultimo urbano, l'Acqua Marcia, a 8,4), campagna fra 10 e 30 km. Non si assegnano d'ufficio entità lineari o areali che attraversano la soglia, luoghi Imagined, luoghi senza ancora, il litorale e la fascia fra 30 e 60 km: sono i casi di confine (REVIEW_2).</t>
+          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6008,44 +5963,49 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Il poligono comunale di roma.geojson è scartato come criterio: include l'Agro romano (Divino Amore, Castel di Leva, Tor di Gheppio) ed esclude il Vaticano. Altre letture della partizione (Roggia, Perosa, Savettieri, Alfano, Calvino): fase 3.</t>
+          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C-edicola_due_santi</t>
+          <t>V-0003a</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>narrativeplace/edicola_due_santi</t>
+          <t>reference/ref_00007</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>chora:Invented</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6055,59 +6015,69 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lettura del censimento: «Edicola immaginata», parte dell'orto/vigna dei Due Santi, senza ancoraggio. Nel censimento l'etichetta era «Imagined», che prima della correzione dello schema (D-030) designava il luogo fittizio in una geografia nota, oggi Invented.</t>
+          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Superata da S-edicola_due_santi (Manzotti 2010, p. 246; D-031).</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C-palazzo_simonetti</t>
+          <t>V-0003b</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>reference/ref_00036</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>chora:Imported</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6117,59 +6087,69 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Lettura del censimento: palazzo reale, ancorato a via Lanza dove lo pone QPa 177.</t>
+          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Superata da S-palazzo_simonetti (Pinotti 2025, p. 78; D-036): in via Lanza non esiste un palazzo Simonetti.</t>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C-casal_bruciato</t>
+          <t>V-0004a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>reference/ref_00008</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casal_bruciato</t>
+          <t>reference/ref_00726</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6179,59 +6159,69 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>censimento_gaddatlas</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>matt_pinotti_2022</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lettura del censimento: Casal Bruciato identificato con il quartiere omonimo del Tiburtino (41,9070 N 12,5506 E).</t>
+          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L'entità gaz_casal_bruciato è stata eliminata (D-029): l'IRI resta come valore di questa lettura superata. Passaggio intermedio D-029 (luogo trasformato senza referente, ancorato a Marino, Albano, Pavona e Santa Palomba), superato da D-037.</t>
+          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>I-casal_bruciato</t>
+          <t>V-0004b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>narrativeplace/casal_bruciato</t>
+          <t>reference/ref_00038</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>reference/ref_00727</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>matt|pinotti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6241,27 +6231,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>matt_pinotti_2022</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>schede 8, 11, 30, 31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Casal Bruciato è il casale dell'Agro romano a sud di Roma, «Casal(e) Bruciato / Abbruciato / Abbrusciato» (Nibby, Dintorni di Roma, p. 569), fra le ferrovie Roma–Napoli e Roma–Velletri; posizione adottata TCI (D-037).</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>C-casal_bruciato</t>
+          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6269,41 +6249,51 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>forma</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V-0001</t>
+          <t>R-0001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>reference/ref_00724</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6317,11 +6307,16 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>241</v>
+        <v>297</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fattocchie (QP, RR II 219) / Frattocchie (QPa 241): emendamento dell'editore.</t>
+          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6331,7 +6326,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.3 (r. 83) e n. 26. La lettura di Terzoli 2015, p. 771 («se non è refuso, rafforza l'onomatopea») e quella di Italia 2020, pp. 101–102 entrano in fase 3.</t>
+          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,39 +6336,34 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V-0002</t>
+          <t>R-0002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>reference/ref_00436</t>
+          <t>route/tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>reference/ref_00725</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6383,15 +6373,20 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>78</v>
+        <v>169</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>via Lata (dtsFG) / via Lanza (QPa 177): il dattiloscritto dei capitoli nuovi colloca il palazzo Simonetti nella via reale in cui si trova; la stampa lo sposta in via Lanza, dove non esiste (D-036).</t>
+          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6401,7 +6396,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Cap. 4, § 4.2 (r. 45). La lettura di Terzoli (palazzo Odescalchi Simonetti) entra in fase 3.</t>
+          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6411,39 +6406,34 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V-0003a</t>
+          <t>R-0003</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>reference/ref_00007</t>
+          <t>route/tragitto_tenenza_due_santi</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6453,17 +6443,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>208–215</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 285) / 219 (QPa 16).</t>
+          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6471,11 +6466,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>prova testuale</t>
@@ -6483,39 +6473,34 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V-0003b</t>
+          <t>R-0004</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>reference/ref_00036</t>
+          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6525,17 +6510,20 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>292</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Civico 119 (QPL 293) / 219 (QPa 25).</t>
+          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6545,7 +6533,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6555,39 +6543,34 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V-0004a</t>
+          <t>R-0005</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>reference/ref_00008</t>
+          <t>route/tragitto_viminale_merulana</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>reference/ref_00726</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6597,17 +6580,20 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>25</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 285) / «palazzo dell'Oro» (QPa 16).</t>
+          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6615,11 +6601,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Corrispondenza QPL 285 ↔ QPa 16 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr">
         <is>
           <t>prova testuale</t>
@@ -6627,39 +6608,34 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V-0004b</t>
+          <t>R-0006</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>route</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>reference/ref_00038</t>
+          <t>route/tragitto_appia_falcognana</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>reference/ref_00727</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>matt|pinotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6669,17 +6645,20 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>matt_pinotti_2022</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>schede 8, 11, 30, 31</t>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>238</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>«palazzo degli ori» (QPL 293) / «palazzo dell'Oro» (QPa 25).</t>
+          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6689,7 +6668,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Corrispondenza QPL 293 ↔ QPa 25 confermata da LS (9/10/2026). Cap. 4, § 4.2 (r. 45).</t>
+          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6699,19 +6678,14 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>forma</t>
+          <t>bozza</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R-0001</t>
+          <t>R-0007</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6721,7 +6695,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>route/tragitto_agostino_aquiro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6745,7 +6719,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>297</v>
+        <v>40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6754,7 +6728,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>«Discesero ai Torraccio […] Svoltarono sull'Appia a li Due Santi […] Valicò invece il binario»: Ingravallo, Di Pietrantonio, l'autista e Runzato percorrono il tragitto in auto.</t>
+          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6764,7 +6738,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L'ultimo nodo (ponte del Divino Amore) è un termine di paragone («simile a quello ch'era due chilometri più a nord, presso il ponte»): lasciato invariato per decisione di LS (9/10/2026, D-064).</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6781,7 +6755,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R-0002</t>
+          <t>R-0008</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6791,12 +6765,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>route/tragitto_santarella_torraccio_divino_amore</t>
+          <t>route/tragitto_cecchina_anziate</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6815,7 +6789,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6824,7 +6798,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «si preannunciava di lontano, dal Torraccio, […] o dal Divino Amore»: le provenienze si ricavano dal rumore, «altre volte» da un luogo o dall'altro.</t>
+          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6834,7 +6808,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Separato dal tragitto di QPa 297 (D-060). È un elenco disgiuntivo e abituale di provenienze, non una sequenza: potrebbe non essere un percorso.</t>
+          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6851,7 +6825,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R-0003</t>
+          <t>R-0009</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6861,7 +6835,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>route/tragitto_tenenza_due_santi</t>
+          <t>route/tragitto_colonna_treccani</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6884,10 +6858,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>208–215</t>
-        </is>
+      <c r="H92" t="n">
+        <v>40</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6896,12 +6868,17 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Pestalozzi e Cocullo scendono dalla caserma di Marino alla porta del borgo, prendono l'Appia, passano la Fontana e si fermano ai Due Santi.</t>
+          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6918,7 +6895,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R-0004</t>
+          <t>R-0010</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6928,12 +6905,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>route/tragitto_brancaccio_piazza_san_giovanni</t>
+          <t>route/tragitto_frattocchie_ciampino</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:InferredRoute</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6952,7 +6929,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>292</v>
+        <v>174</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6961,7 +6938,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>«A largo Brancaccio, mentre che staveno svortando in via Merulana verso piazza San Giovanni»: il tragitto è in corso.</t>
+          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6971,7 +6948,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>L'ultimo nodo è una direzione («verso piazza San Giovanni»): l'arrivo non è narrato.</t>
+          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6988,7 +6965,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R-0005</t>
+          <t>R-0011</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6998,7 +6975,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>route/tragitto_viminale_merulana</t>
+          <t>route/tragitto_monti_piazza_esedra</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7022,7 +6999,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7031,12 +7008,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>«Saliti sul PV e discesi appunto al Viminale, presero il tram di San Giovanni […] raggiunsero il civico ducentodicinnove».</t>
+          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7053,7 +7035,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R-0006</t>
+          <t>R-0012</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7063,12 +7045,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>route/tragitto_appia_falcognana</t>
+          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:CompletedRoute</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7087,7 +7069,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7096,7 +7078,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>«La strada era una sola, pe fortuna, salvo il primo pezzo però: la statale, l'Appia, poi ad angolo retto la deviazione della provinciale, pe Falcognana»: la strada spiegata dopo le indicazioni di Camilla (QPa 237).</t>
+          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7106,7 +7088,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Incerto fra indicato e compiuto: il passo descrive la strada, il viaggio segue.</t>
+          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7123,7 +7105,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R-0007</t>
+          <t>R-0013</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7133,7 +7115,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>route/tragitto_agostino_aquiro</t>
+          <t>route/tragitto_chiara_pantheon</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7157,7 +7139,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7166,7 +7148,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Il commendator Angeloni e i suoi pari «sogliono deambulare» da Sant'Agostino a Santa Maria in Aquiro.</t>
+          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7193,7 +7175,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R-0008</t>
+          <t>R-0014</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7203,7 +7185,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>route/tragitto_cecchina_anziate</t>
+          <t>route/tragitto_duesanti_frattocchie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7227,7 +7209,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7236,17 +7218,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>La motocicletta di Santarella «infilava […] la mala curva d'aa stazione d'aa Cecchina», poi si fermava a Santa Palomba e a Campoleone, «il caso richiedendo».</t>
+          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo), con fermate eventuali.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7263,7 +7240,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R-0009</t>
+          <t>R-0015</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7273,7 +7250,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>route/tragitto_colonna_treccani</t>
+          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7296,8 +7273,10 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>40</v>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>139–140</t>
+        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7306,17 +7285,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Angeloni e i suoi pari «si avventurano» per via Colonna, piazza de Pietra, via de Pietra fino al Corso.</t>
+          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo).</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7333,7 +7307,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R-0010</t>
+          <t>R-0016</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7343,12 +7317,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>route/tragitto_frattocchie_ciampino</t>
+          <t>route/tragitto_marino_albano_laziale</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>chora:InferredRoute</t>
+          <t>chora:DirectionalRoute</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7367,7 +7341,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7376,7 +7350,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>«Oppure a metà le Frattocchie, doveva spengere: al passaggio dell'Appia, o a Ca' Francesi, a Tor Ser Paolo, alla stazione di Ciampino»: luoghi alternativi della fermata.</t>
+          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7386,7 +7360,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Come QPa 169: elenco disgiuntivo e abituale, non una sequenza.</t>
+          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7403,7 +7377,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R-0011</t>
+          <t>R-0017</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7413,7 +7387,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>route/tragitto_monti_piazza_esedra</t>
+          <t>route/tragitto_marino_due_santi</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7437,7 +7411,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7446,17 +7420,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Diomede «si differiva passo passo da un quartiere all'altro: monticiano a le dieci, trasteverino a le quattro, a Piazza Colonna o a l'Esedra».</t>
+          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Percorso abituale (iterativo); l'ultimo nodo è disgiuntivo («o»).</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7473,7 +7442,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R-0012</t>
+          <t>R-0018</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7483,7 +7452,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>route/tragitto_rocca_di_papa_monte_nuncupale</t>
+          <t>route/tragitto_marino_santo_stefano</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7507,7 +7476,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7516,7 +7485,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Santarella «da Rocca di Papa a Castel Savelli, giù: da Rocca Orsina al Monte Nuncupale, su».</t>
+          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7526,7 +7495,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7543,7 +7512,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R-0013</t>
+          <t>R-0019</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7553,7 +7522,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>route/tragitto_chiara_pantheon</t>
+          <t>route/tragitto_merulana_policlinico</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7577,7 +7546,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -7586,7 +7555,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Di quaresima Angeloni e i suoi pari «si contentano lungheggiar Santa Chiara […] imboccheno la Palommella e sfioreno er dedietro ar Panteone».</t>
+          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7596,7 +7565,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Percorso abituale (iterativo).</t>
+          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7613,7 +7582,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R-0014</t>
+          <t>R-0020</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7623,12 +7592,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>route/tragitto_duesanti_frattocchie</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:DreamedRoute</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7647,7 +7616,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -7656,12 +7625,17 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>La corsa del tram dei Castelli: «Ai Due Santi, al Torraccio, a le Frattocchie […] era salita una quantità di persone».</t>
+          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7678,7 +7652,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R-0015</t>
+          <t>R-0021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7688,12 +7662,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>route/tragitto_policlinico_san_lorenzo_al_verano</t>
+          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:IndicatedRoute</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7711,10 +7685,8 @@
           <t>qpa</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>139–140</t>
-        </is>
+      <c r="H104" t="n">
+        <v>237</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -7723,12 +7695,17 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Il corteo funebre «spostò dar Policlinico a le otto […] tajarono pe la direttissima der viale Regina Margherita […] arrivarono a San Lorenzo ar Verano».</t>
+          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7745,27 +7722,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R-0016</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_albano_laziale</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>chora:DirectionalRoute</t>
+          <t>geometry/L-0001</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7775,11 +7752,13 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
-        <v>278</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7788,7 +7767,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Santarella «era a percorrere sulla sua motocicletta la via provinciale da Marino ad Albano»: il passo dà la strada e la sua direzione, non il tratto percorso.</t>
+          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7798,44 +7777,44 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Alternativa: compiuto. Il Cap. 4 (r. 194) chiama questo tipo «presunto».</t>
+          <t>Posizione adottata (D-037).</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R-0017</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_due_santi</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>geometry/L-0002</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7845,20 +7824,22 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>206</v>
+          <t>manzotti_2010</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
+        </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Pestalozzi «usciva (in motocicletta) dalla caserma […] di Marino per catapultarsi alla bottega-laboratorio».</t>
+          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7866,36 +7847,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Posizione alternativa (D-037).</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>R-0018</t>
+          <t>U-0009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>uncertainty</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>route/tragitto_marino_santo_stefano</t>
+          <t>gazetteer/gaz_bologna</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:Discrepancy</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7908,69 +7894,76 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>153</v>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>«arrivò a Santo Stefano in motocicletta il brigadiere Pestalozzi […] latore di un rapporto […] della Tenenza».</t>
+          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Nodi nell'ordine di occorrenza nel testo (decisione di LS, 9/10/2026, D-064): Santo Stefano 1, Tenenza 2. La partenza dalla Tenenza è inferita dal rapporto.</t>
+          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072). Superata: la via è milanese, oggi via Bernardino Zenale (Terzoli 2015, p. 77); la discrepanza non sussiste (D-092).</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>geometria</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>documentaria</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>ref_00028</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>R-0019</t>
+          <t>N-0001</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>route/tragitto_merulana_policlinico</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>chora:CompletedRoute</t>
+          <t>chora:TypoHypothesis</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7980,67 +7973,79 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>93</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>L'autorità giudiziaria «era intervenuta […] a via Merulana, indi al Policlinico».</t>
+          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Focalizzatrice del tragitto: Liliana, come nel database (decisione di LS, 9/10/2026, D-064).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>refuso per «Robinie vecchie»</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>R-0020</t>
+          <t>N-0002</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>chora:DreamedRoute</t>
+          <t>chora:TypoHypothesis</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8050,67 +8055,79 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>212</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Il sogno di Pestalozzi: «al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest!», il Roma-Napoli che «filava filava», la fuga «verso le gore senza foce del Campo Morto».</t>
+          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). La lettura di Manzotti di «per fil a dest» è K-0008 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>refuso per «Rovine vecchie»</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>R-0021</t>
+          <t>N-0003</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>route/tragitto_castel_di_leva_casal_bruciato</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chora:IndicatedRoute</t>
+          <t>chora:IronicLowering</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8120,67 +8137,74 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>qpa</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>237</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>491–492</t>
+        </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Camilla indica la strada: «Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato».</t>
+          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Nuovo percorso (D-060). Il nodo finale è il passaggio a livello: nei dati l'occorrenza è di casal_bruciato.</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>bozza</t>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>«ironico abbassamento»</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>K-0001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>geometry/L-0001</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8190,69 +8214,64 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>italia_2020</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>si</t>
+          <t>102–103</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>La carta TCI colloca il casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato, come il testo. Coordinate stimate: punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia.</t>
+          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Posizione adottata (D-037).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>K-0002</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>geometry/L-0002</t>
+          <t>reference/ref_00403</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8262,49 +8281,52 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>268–269; Tavv. VI–VII, pp. 300–301</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>169</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>La tavoletta IGM colloca «Casale Abbruciato» a ovest della Roma–Napoli: reticolo UTM 33 della tavola, E 297,7 N 4621,3 km.</t>
+          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Posizione alternativa (D-037).</t>
+          <t>Risponde a K-0001 (D-087).</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>ref_00403</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>K-0001</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>U-0009</t>
+          <t>U-0010</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8314,17 +8336,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_bologna</t>
+          <t>reference/ref_00404</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>chora:Discrepancy</t>
+          <t>chora:Incompleteness</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8332,14 +8354,17 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>492</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Il testo colloca a Milano ("udito a Milano […] al dispensario celtico di via delle Oche") la via bolognese delle Oche, nota via di prostituzione: traslazione d'autore, registrata e non corretta.</t>
+          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8349,12 +8374,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Luogo: via_delle_oche (QPa 22). Soggetto l'entità dell'ancora, per la regola dell'asse geometria (D-070); lo statuto del luogo non cambia (D-072). Superata: la via è milanese, oggi via Bernardino Zenale (Terzoli 2015, p. 77); la discrepanza non sussiste (D-092).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8364,7 +8389,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>geometria</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -8374,34 +8399,34 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ref_00028</t>
+          <t>ref_00404</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>«toponimi non segnalati nelle carte topografiche»</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N-0001</t>
+          <t>K-0003</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>chora:TypoHypothesis</t>
+          <t>reference/ref_00588</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>italia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8411,22 +8436,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>101</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Prima ipotesi di Terzoli: refuso per «Robinie vecchie».</t>
+          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8451,34 +8469,29 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>refuso per «Robinie vecchie»</t>
+          <t>ref_00588</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N-0002</t>
+          <t>V-0005</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>reference/ref_00132</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>chora:TypoHypothesis</t>
+          <t>reference/ref_00734</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8496,19 +8509,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="H115" t="n">
+        <v>142</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Seconda ipotesi: refuso per «Rovine vecchie», dai ruderi della zona (Rovina del Pecoraro, della Strega, del Fenilone, presso la Cecchignola).</t>
+          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8523,7 +8529,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8533,34 +8539,34 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>refuso per «Rovine vecchie»</t>
+          <t>ref_00132</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N-0003</t>
+          <t>I-0001</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>narrativeplace/ca_francesi</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>chora:IronicLowering</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8578,19 +8584,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>491–492</t>
-        </is>
+      <c r="H116" t="n">
+        <v>512</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Terza ipotesi: «ironico abbassamento» delle «rovine» della zona, per parafrasi e paronomasia.</t>
+          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8613,36 +8617,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>«ironico abbassamento»</t>
+          <t>«località nei pressi della stazione delle Frattocchie»</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>K-0001</t>
+          <t>I-0002</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>narrativeplace/tor_ser_paolo</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8652,17 +8656,20 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>italia_2020</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>102–103</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>512</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Secondo Italia, Pinotti 2018 emenda «Robine» come refuso di Garzanti 1992.</t>
+          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8685,31 +8692,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>ref_00403</t>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>K-0002</t>
+          <t>I-0003</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>reference/ref_00403</t>
+          <t>narrativeplace/fontana_di_papa</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>lorenzo_sabatino</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8719,15 +8731,20 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>qpa</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>169</v>
+        <v>658</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>In Pinotti 2018 non c'è emendamento di «Robine»: QPa 169 legge «Robine Vecchie».</t>
+          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8737,12 +8754,12 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Risponde a K-0001 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8752,34 +8769,29 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ref_00403</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>K-0001</t>
+          <t>ref_00529</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>U-0010</t>
+          <t>T-0021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>uncertainty</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>reference/ref_00404</t>
+          <t>gazetteer/gaz_fontana_di_papa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>chora:Incompleteness</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8797,12 +8809,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H119" t="n">
-        <v>492</v>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>658 (Bertarelli 1924, p. 561)</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>«Cassero» e «Sant'Ignazio»: toponimi che Terzoli non trova nelle carte topografiche.</t>
+          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8817,54 +8831,39 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>documentaria</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>ref_00404</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>«toponimi non segnalati nelle carte topografiche»</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>K-0003</t>
+          <t>I-0004</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>reference/ref_00588</t>
+          <t>narrativeplace/osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>italia</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8874,15 +8873,20 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>italia_2020</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>101</v>
+        <v>776</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Nessun elemento fa pensare a un'invenzione gaddiana: l'emendamento «Frattocchie» di Pinotti 2018 è giustificato. Concorde con V-0001.</t>
+          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8907,29 +8911,34 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ref_00588</t>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V-0005</t>
+          <t>T-0022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>reference/ref_00132</t>
+          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>reference/ref_00734</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8947,12 +8956,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H121" t="n">
-        <v>142</v>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Nel cap. II le fermate del tram («Ai Due Santi, al Torraccio, a le Frattocchie») sostituiscono la sola «Marino» di QPL (RR II, p. 324).</t>
+          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8967,44 +8978,34 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>ref_00132</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>I-0001</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>narrativeplace/ca_francesi</t>
+          <t>gazetteer/gaz_ciampino</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9022,17 +9023,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H122" t="n">
-        <v>512</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>si</t>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Ca' Francesi: località nei pressi della stazione delle Frattocchie.</t>
+          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9047,39 +9045,34 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>«località nei pressi della stazione delle Frattocchie»</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>I-0002</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_ser_paolo</t>
+          <t>gazetteer/gaz_tor_ser_paolo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9097,17 +9090,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H123" t="n">
-        <v>512</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>si</t>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Tor ser Paolo, o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino.</t>
+          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9122,39 +9112,34 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>«o Torre Messer Paoli, tra via Cavona e via dei Laghi, presso Marino»</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>I-0003</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>narrativeplace/fontana_di_papa</t>
+          <t>gazetteer/gaz_frattocchie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9172,17 +9157,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H124" t="n">
-        <v>658</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>si</t>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>«La fontana» è Fontana di Papa, frazione di Ariccia, una decina di km a sud delle Frattocchie lungo l'Anziatina (Guida 1924, p. 561).</t>
+          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9197,24 +9179,19 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>ref_00529</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>T-0021</t>
+          <t>T-0004</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9224,12 +9201,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_fontana_di_papa</t>
+          <t>gazetteer/gaz_torraccio</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9249,12 +9226,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>658 (Bertarelli 1924, p. 561)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Fontana di Papa è registrata nella Guida 1924, p. 561.</t>
+          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9281,22 +9258,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>I-0004</t>
+          <t>T-0005</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>repertory</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>narrativeplace/osteriuccia_bivio</t>
+          <t>gazetteer/gaz_due_santi</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>source/bertarelli_1925</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9314,17 +9291,14 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H126" t="n">
-        <v>776</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>L'«osteriuccia del bivio» è l'«Osteria» registrata dalla guida sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie. Non adottata: il luogo si posiziona dalle ancore.</t>
+          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9339,29 +9313,19 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>ref_00736</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>«nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"»</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>T-0022</t>
+          <t>T-0006</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9371,7 +9335,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_osteria_bivio_frattocchie</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9396,12 +9360,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>776 (Bertarelli 1925, cart. 1, tra pp. 758–759, «Osteria»; cart. 4, tra pp. 736–737, «Ost.»)</t>
+          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>L'osteria del bivio è registrata sulle cart. 1 e 4 della Guida 1925.</t>
+          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9428,7 +9392,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9438,7 +9402,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ciampino</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9468,7 +9432,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>«Ciampino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9495,7 +9459,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9505,7 +9469,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_tor_ser_paolo</t>
+          <t>gazetteer/gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9535,7 +9499,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>«Tor ser Paolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9562,7 +9526,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9572,7 +9536,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_frattocchie</t>
+          <t>gazetteer/gaz_pavona</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9602,7 +9566,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>«Frattocchie» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9629,7 +9593,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>T-0004</t>
+          <t>T-0010</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9639,7 +9603,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_torraccio</t>
+          <t>gazetteer/gaz_solforata</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9669,7 +9633,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>«Torraccio» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9696,7 +9660,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>T-0005</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9706,7 +9670,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_due_santi</t>
+          <t>gazetteer/gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9736,7 +9700,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>«Due Santi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9763,7 +9727,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>T-0006</t>
+          <t>T-0012</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9773,7 +9737,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>gazetteer/gaz_ca_francesi</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9803,7 +9767,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>«Ponte di Santa Fumia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9830,7 +9794,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>T-0013</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9840,7 +9804,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_falcognana</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9870,7 +9834,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>«Casal Abbruciato» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9897,7 +9861,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0014</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9907,7 +9871,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_divino_amore</t>
+          <t>gazetteer/gaz_cecchina</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9937,7 +9901,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>«Ponte del Divino Amore» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9964,7 +9928,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0015</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9974,7 +9938,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pavona</t>
+          <t>gazetteer/gaz_albano_laziale</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10004,7 +9968,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>«Pavona» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10031,7 +9995,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T-0010</t>
+          <t>T-0016</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10041,7 +10005,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_solforata</t>
+          <t>gazetteer/gaz_zagarolo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10071,7 +10035,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>«Zolforata» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10098,7 +10062,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>T-0017</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10108,7 +10072,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_pratica_di_mare</t>
+          <t>gazetteer/gaz_marino</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10138,7 +10102,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>«Pratica di Mare» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10165,7 +10129,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>T-0012</t>
+          <t>T-0018</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10175,7 +10139,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ca_francesi</t>
+          <t>gazetteer/gaz_ariccia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10205,7 +10169,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>«Ca' dei Francesi» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10232,7 +10196,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>T-0013</t>
+          <t>T-0019</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10242,7 +10206,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_falcognana</t>
+          <t>gazetteer/gaz_santa_palomba</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10272,7 +10236,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>«Falcognana» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10299,7 +10263,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>T-0014</t>
+          <t>T-0020</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10309,7 +10273,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_cecchina</t>
+          <t>gazetteer/gaz_rocca_di_papa</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10339,7 +10303,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>«Cecchina» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10366,22 +10330,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>T-0015</t>
+          <t>K-0004</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_albano_laziale</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1925</t>
+          <t>work/quer_pasticciaccio</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10401,12 +10360,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>418–419</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>«Albano» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10421,19 +10380,24 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>T-0016</t>
+          <t>T-0023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10443,12 +10407,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_zagarolo</t>
+          <t>gazetteer/gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>source/bertarelli_1924</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10468,12 +10432,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>«Zagarolo» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10494,13 +10458,18 @@
       <c r="O143" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>T-0017</t>
+          <t>T-0024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10510,7 +10479,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_marino</t>
+          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10535,12 +10504,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>«Marino» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10567,22 +10536,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>T-0018</t>
+          <t>K-0005</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ariccia</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1925</t>
+          <t>route/tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10602,12 +10566,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>«Ariccia» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10628,28 +10592,28 @@
       <c r="O145" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>T-0019</t>
+          <t>K-0006</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_santa_palomba</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1925</t>
+          <t>narrativeplace/casello_km_20_25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10667,14 +10631,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
-        </is>
+      <c r="H146" t="n">
+        <v>911</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>«Santa Palomba» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10689,34 +10651,34 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>«immaginario»</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>T-0020</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_rocca_di_papa</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>source/bertarelli_1925</t>
+          <t>narrativeplace/tor_di_gheppio</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10734,14 +10696,12 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>418–419 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
-        </is>
+      <c r="H147" t="n">
+        <v>911</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>«Rocca di Papa» è registrato sulla cart. 4 della Guida 1925 (topografia della guida in QP).</t>
+          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10756,19 +10716,24 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>«immaginaria»</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>K-0004</t>
+          <t>K-0008</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10778,12 +10743,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>work/quer_pasticciaccio</t>
+          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10793,17 +10758,17 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>418–419</t>
+          <t>268–269</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>La topografia di QP è strettamente legata a quella della guida del Touring, anche nelle indicazioni stradali date ai personaggi.</t>
+          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10826,16 +10791,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>«la topografia di QP è strettamente legata a quella della guida del Touring»</t>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ref_00534</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>T-0023</t>
+          <t>T-0025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10845,7 +10810,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_casale_abbruciato</t>
+          <t>gazetteer/gaz_monti_ernici</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -10870,12 +10835,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>766 (Bertarelli 1924, cart. 2, tra pp. 480–481)</t>
+          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>«C. Abbruciato» sulla cartina del 1924; concorde con L-0001.</t>
+          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10896,38 +10861,33 @@
       <c r="O149" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>«C. Abbruciato»</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>T-0024</t>
+          <t>I-0005</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_ponte_di_santa_fumia</t>
+          <t>narrativeplace/tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>source/bertarelli_1925</t>
+          <t>gazetteer/gaz_palazzo_colonna_marino</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -10937,17 +10897,22 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>911 (Bertarelli 1925, cart. 4, tra pp. 736–737)</t>
+          <t>239–240</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Ponte di Santa Fumia sulla cart. 4 della Guida 1925.</t>
+          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10962,19 +10927,24 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>«re-invenzione romantica»</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>K-0005</t>
+          <t>K-0009</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10984,12 +10954,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>route/tragitto_torraccio_ponte_divino_amore</t>
+          <t>narrativeplace/marino</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10999,17 +10969,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>911 (cfr. Terzoli 2008, pp. 109–113)</t>
+          <t>293–294</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>La strada dall'Anziate a Casal Bruciato, parallela alla Falcognana, corrisponde alla planimetria delle cart. 4 e 1 della Guida 1925.</t>
+          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11024,39 +10994,39 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>ref_00698</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>K-0006</t>
+          <t>N-0004</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>narrativeplace/casello_km_20_25</t>
+          <t>narrativeplace/castel_porcano</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>chora:Paraetymology</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11066,15 +11036,15 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>911</v>
+        <v>273</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginario» il casello di Casal Bruciato. Commento attribuito: lo statuto non cambia.</t>
+          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11097,16 +11067,21 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>«immaginario»</t>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>ref_00538|ref_00539</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>K-0007</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11116,12 +11091,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>narrativeplace/tor_di_gheppio</t>
+          <t>reference/ref_00539</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>manzotti</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11131,15 +11106,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>manzotti_2010</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>911</v>
+        <v>276</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Terzoli chiama «immaginaria» Tor di Gheppio. Commento attribuito: lo statuto non cambia.</t>
+          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11162,31 +11137,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>«immaginaria»</t>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ref_00539</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>K-0008</t>
+          <t>I-0006</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>route/tragitto_sogno_casal_bruciato_campo_morto</t>
+          <t>narrativeplace/palazzo_simonetti</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11196,17 +11176,22 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>268–269</t>
+          <t>535–536</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>«Per fil a dest»: passaggio a livello sulla Roma–Velletri presso il casello km 20,25, fra Santa Maria delle Mole (km 17,55) e Pavona (km 23,38); premonizione dell'itinerario di fuga.</t>
+          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11231,34 +11216,34 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ref_00534</t>
+          <t>ref_00435</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>T-0025</t>
+          <t>I-0007</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>repertory</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_monti_ernici</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>source/bertarelli_1924</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11271,14 +11256,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>696 (Bertarelli 1924, p. 498; cart. 2)</t>
+      <c r="H155" t="n">
+        <v>536</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>I monti Ernici nella Guida 1924, p. 498, e sulla cart. 2.</t>
+          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11288,24 +11276,34 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>prova referenziale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>ref_00435</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>I-0005</t>
+          <t>I-0008</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11315,17 +11313,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>narrativeplace/tenenza_carabinieri_marino</t>
+          <t>narrativeplace/palazzo_simonetti</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_colonna_marino</t>
+          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11335,13 +11333,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>239–240</t>
-        </is>
+          <t>pinotti_2025</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>78</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -11350,7 +11346,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>La caserma è il palazzo Frangipani-Orsini-Colonna su piazza Umberto I (oggi della Repubblica) (TCI, Italia centrale IV, p. 761), non la palazzina in Pierangeli: «re-invenzione romantica». Non adottata: le ancore della tenenza non cambiano.</t>
+          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11365,7 +11361,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -11373,31 +11369,36 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>«re-invenzione romantica»</t>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>K-0009</t>
+          <t>N-0005</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>narrativeplace/marino</t>
+          <t>reference/ref_00437</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>chora:Synecdoche</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11407,17 +11408,15 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>293–294</t>
-        </is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>537</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Marino come topografia familiare (Longone-Lukones) e luogo di delizie enologiche.</t>
+          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11438,33 +11437,43 @@
       <c r="O157" t="inlineStr">
         <is>
           <t>validata</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>N-0004</t>
+          <t>I-0009</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>narrativeplace/castel_porcano</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>chora:Paraetymology</t>
+          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11474,15 +11483,20 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>273</v>
+        <v>537</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Gioco paraetimologico su Castelporziano (Real Tenuta; TCI, Italia centrale I, p. 569); vale anche per «Castel Porcino».</t>
+          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11507,34 +11521,34 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>ref_00538|ref_00539</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_castel_porziano</t>
+          <t>ref_00437</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>K-0010</t>
+          <t>I-0010</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>reference/ref_00539</t>
+          <t>narrativeplace/palazzo_del_mappamondo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>gazetteer/gaz_palazzo_chigi</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>manzotti</t>
+          <t>grassadonia|lagossi|marchetti</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11544,15 +11558,20 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>manzotti_2010</t>
+          <t>terzoli_2015</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>276</v>
+        <v>537</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lo slittamento Porcano → Porcino sottolinea lo spostamento del sogno verso la Zamira.</t>
+          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11562,7 +11581,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11577,14 +11596,19 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>ref_00539</t>
+          <t>ref_00437</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>I-0006</t>
+          <t>I-0011</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11594,12 +11618,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/vite</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_odescalchi_simonetti</t>
+          <t>gazetteer/gaz_via_della_vite</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -11617,19 +11641,17 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>535–536</t>
-        </is>
+      <c r="H160" t="n">
+        <v>616</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Palazzo Odescalchi Simonetti, via Vittoria Colonna 11: l'indirizzo romano di Gadda (pensione White).</t>
+          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11654,34 +11676,39 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ref_00435</t>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>I-0007</t>
+          <t>V-0006</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>reference/ref_00493</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>reference/ref_00735</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>pinotti</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11691,20 +11718,15 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>terzoli_2015</t>
+          <t>pinotti_2025</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>536</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+        <v>78</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Palazzo De Carolis Simonetti, via del Corso 307 / via Lata 3.</t>
+          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11714,12 +11736,12 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536 (D-087).</t>
+          <t>Loci critici (D-087).</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova testuale</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11729,39 +11751,44 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>ref_00435</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
+          <t>ref_00493</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>«da Faraja»</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>sostituzione</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>I-0008</t>
+          <t>N-0006</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>identification</t>
+          <t>naming</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_simonetti</t>
+          <t>narrativeplace/ditta_ciurlani</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_de_carolis_simonetti</t>
+          <t>chora:OnomasticPun</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11771,20 +11798,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>78</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>433–435, 644</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Lo stesso edificio, dalla lezione «via Lata» del dattiloscritto dei capitoli nuovi.</t>
+          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -11799,44 +11823,39 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>ref_00435|ref_00725</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>N-0005</t>
+          <t>S-osteriuccia_bivio</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>naming</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>reference/ref_00437</t>
+          <t>narrativeplace/osteriuccia_bivio</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>chora:Synecdoche</t>
+          <t>chora:Transformed</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>terzoli</t>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -11850,11 +11869,16 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>537</v>
+        <v>776</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>«Palazzo der Mappamonno»: Palazzo Venezia indicato per sineddoche dalla Sala del Mappamondo.</t>
+          <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11864,34 +11888,24 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Motivazione di LS (10/10/2026, D-087).</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>I-0009</t>
+          <t>I-0012</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11901,12 +11915,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_venezia</t>
+          <t>gazetteer/gaz_castel_porziano</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -11925,7 +11939,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>537</v>
+        <v>679</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -11934,17 +11948,17 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Il palazzo der Mappamonno è Palazzo Venezia, sede di Mussolini.</t>
+          <t>Castel Porcano è la deformazione di Castel Porziano, allora tenuta reale di caccia a sud di Roma (cfr. pp. 633–634).</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Fase 3d (D-092).</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11955,18 +11969,13 @@
       <c r="O164" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>ref_00437</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>I-0010</t>
+          <t>I-0013</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11976,17 +11985,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>narrativeplace/palazzo_del_mappamondo</t>
+          <t>narrativeplace/via_delle_oche</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_palazzo_chigi</t>
+          <t>gazetteer/gaz_via_delle_oche_milano</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>grassadonia|lagossi|marchetti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -12000,53 +12009,43 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>537</v>
+        <v>77</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Alternativa: Palazzo Chigi (Sala dei Mappamondi).</t>
+          <t>Via delle Oche è oggi via Bernardino Zenale, fra via San Vittore e corso Magenta, presso Santa Maria delle Grazie; il commento rinvia all'Adalgisa, p. 564, n. 53 («Via di Okk»).</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 537 (D-087).</t>
+          <t>Fase 3d (D-092).</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>lettura critica</t>
+          <t>prova referenziale</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>ref_00437</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>glm_1997a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>I-0011</t>
+          <t>I-0014</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12056,12 +12055,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>narrativeplace/vite</t>
+          <t>narrativeplace/rocca_orsina</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>gazetteer/gaz_via_della_vite</t>
+          <t>gazetteer/gaz_rocca_orsina</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12079,8 +12078,10 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H166" t="n">
-        <v>616</v>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>507–508</t>
+        </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -12089,17 +12090,17 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>«A la Vite» è probabilmente il ristorante Le Grotte, in via della Vite (rione Campo Marzio).</t>
+          <t>Rocca Orsina è la Rocca Orsini di Marino, di cui il palazzo Colonna occupa il sedime; Gadda la nomina anche in Fuga a Tor di Nona (RD 981).</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Fase 3d (D-092). Terzoli data la rocca alla fine del XV secolo (Paolo Orsini); altre fonti la danno al XIII–XIV: la datazione non incide sull'identificazione.</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12110,43 +12111,33 @@
       <c r="O166" t="inlineStr">
         <is>
           <t>validata</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>«probabilmente il ristorante Le Grotte, in via della Vite (nel rione Campo Marzio), uno dei più antichi e rinomati locali romani»</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>V-0006</t>
+          <t>I-0015</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>reference/ref_00493</t>
+          <t>narrativeplace/monte_nuncupale</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>reference/ref_00735</t>
+          <t>gazetteer/gaz_campidoglio</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>pinotti</t>
+          <t>terzoli</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12156,30 +12147,37 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>pinotti_2025</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
-        <v>78</v>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>507–508</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Il dattiloscritto legge «da Faraja», cioè il Gran Caffè Faraglia, all'angolo fra piazza Venezia e via Cesare Battisti, dove QPa 200 legge «a la Vite».</t>
+          <t>Ipotesi dubitativa del commento ("forse da identificare con il Campidoglio"); non adottata: il "su" del passo si accorda con l'orizzonte dei Colli Albani.</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Fase 3d (D-092).</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>prova testuale</t>
+          <t>lettura critica</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -12187,26 +12185,16 @@
           <t>validata</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>ref_00493</t>
-        </is>
-      </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>«da Faraja»</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>sostituzione</t>
+          <t>forse da identificare con il Campidoglio</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>N-0006</t>
+          <t>N-0007</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12216,12 +12204,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>narrativeplace/ditta_ciurlani</t>
+          <t>narrativeplace/castel_porcano</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>chora:OnomasticPun</t>
+          <t>chora:Paraetymology</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12239,24 +12227,22 @@
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>433–435, 644</t>
-        </is>
+      <c r="H168" t="n">
+        <v>679</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>«Ciurlani»: origine onomastica e gioco di parole con «truffaldino».</t>
+          <t>Gioco paraetimologico su Castel Porziano, con il rinvio a Circe e alla Guida Touring 1924, p. 569 («già Porciliano»); vale anche per «Castel Porcino».</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Loci critici (D-087).</t>
+          <t>Fase 3d (D-092).</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12269,436 +12255,12 @@
           <t>validata</t>
         </is>
       </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>S-osteriuccia_bivio</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>narrativeplace/osteriuccia_bivio</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>chora:Transformed</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H169" t="n">
-        <v>776</v>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Osteria registrata dalla guida del Touring sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie; il testo la rende "osteriuccia" senza nome né collocazione precisa: luogo trasformato, ancorato ai toponimi più prossimi.</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Motivazione di LS (10/10/2026, D-087).</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>prova referenziale</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>I-0012</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>identification</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>narrativeplace/castel_porcano</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_castel_porziano</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>terzoli</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H170" t="n">
-        <v>679</v>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Castel Porcano è la deformazione di Castel Porziano, allora tenuta reale di caccia a sud di Roma (cfr. pp. 633–634).</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Fase 3d (D-092).</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>lettura critica</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>I-0013</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>identification</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>narrativeplace/via_delle_oche</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_via_delle_oche_milano</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>terzoli</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
-        <v>77</v>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Via delle Oche è oggi via Bernardino Zenale, fra via San Vittore e corso Magenta, presso Santa Maria delle Grazie; il commento rinvia all'Adalgisa, p. 564, n. 53 («Via di Okk»).</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Fase 3d (D-092).</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>prova referenziale</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>I-0014</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>identification</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>narrativeplace/rocca_orsina</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_rocca_orsina</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>terzoli</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>507–508</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Rocca Orsina è la Rocca Orsini di Marino, di cui il palazzo Colonna occupa il sedime; Gadda la nomina anche in Fuga a Tor di Nona (RD 981).</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Fase 3d (D-092). Terzoli data la rocca alla fine del XV secolo (Paolo Orsini); altre fonti la danno al XIII–XIV: la datazione non incide sull'identificazione.</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>lettura critica</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>I-0015</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>identification</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>narrativeplace/monte_nuncupale</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>gazetteer/gaz_campidoglio</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>terzoli</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>507–508</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Ipotesi dubitativa del commento ("forse da identificare con il Campidoglio"); non adottata: il "su" del passo si accorda con l'orizzonte dei Colli Albani.</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Fase 3d (D-092).</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>lettura critica</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>forse da identificare con il Campidoglio</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>N-0007</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>naming</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>narrativeplace/castel_porcano</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>chora:Paraetymology</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>terzoli</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>terzoli_2015</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
-        <v>679</v>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Gioco paraetimologico su Castel Porziano, con il rinvio a Circe e alla Guida Touring 1924, p. 569 («già Porciliano»); vale anche per «Castel Porcino».</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Fase 3d (D-092).</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>lettura critica</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
+      <c r="R168" t="inlineStr">
         <is>
           <t>ref_00538|ref_00539</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="U168" t="inlineStr">
         <is>
           <t>gazetteer/gaz_castel_porziano</t>
         </is>
